--- a/09538984 MANIFEST.xlsx
+++ b/09538984 MANIFEST.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -519,12 +519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09538984V33I1</t>
+          <t>09538984V30I1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -533,40 +533,40 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Seebeck coefficient, Thermoelectric effect, Materials science, Condensed matter physics, Lattice constant, Thermal conductivity, Thermodynamics, Density functional theory, Chemistry, Computational chemistry, Physics, Optics, Composite material, Nanopore, Chromosomal translocation, Polymer, Scaling, Molecular dynamics, Dynamics (music), Traverse, Monomer, Mechanics, Classical mechanics, Nanotechnology, Geometry</t>
+          <t>Mesoscopic physics, Chemical physics, Biomolecule, Context (archaeology), Length scale, Micelle, Molecular dynamics, Hydrogen bond, Nanotechnology, Chemistry, Molecule, Materials science, Physics, Computational chemistry, Aqueous solution, Physical chemistry, Glucocorticoid receptor, Glucocorticoid, Stimulation, Hormone, Homeostasis, Mineralocorticoid, Receptor, Nuclear receptor, Annealing (glass)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mathematics, Nuclear magnetic resonance, Geology, Doping, Pulsed laser deposition, Hall effect, Electrical resistivity and conductivity, Epitaxy, Thin film, Charge carrier, Fermi level, Hysteresis, Metal, Metal–insulator transition, Analytical Chemistry (journal), Optoelectronics, Electron, Metallurgy, Femtosecond, Spintronics, Ultrashort pulse, Spin engineering, Magnetization dynamics, Spinplasmonics, Spin polarization</t>
+          <t>Scaling, Colloid, Kinetic energy, Colloidal particle, Simulated annealing, Ferromagnetism, Magnetization, Condensed matter physics, Diffraction, Metastability, Electron diffraction, Low-energy electron diffraction, Superstructure, Substrate (aquarium), Photoemission electron microscopy, Overlayer, Crystallography, Thin film, Spins, Optics, Electron microscope, Magnetic field, Diffusionless transformation, Martensite, Magnetic moment</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09538984V33I2</t>
+          <t>09538984V30I2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -575,40 +575,40 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Graphene, Gallium, Density functional theory, Ambipolar diffusion, Cluster (spacecraft), Materials science, Doping, Diffusion, van der Waals force, Atom (system on chip), Diffusion barrier, Chemical physics, Atomic physics, Condensed matter physics, Electron, Nanotechnology, Chemistry, Computational chemistry, Molecule, Optoelectronics, Physics, Thermodynamics, Superconductivity, Quantum Monte Carlo, Electric field</t>
+          <t>Picosecond, Laser, Raman spectroscopy, Raman scattering, Potassium titanyl phosphate, Crystal (programming language), Potassium, Materials science, Sum-frequency generation, Spectral line, Chemistry, Optics, Analytical Chemistry (journal), Nonlinear optics, Physics, Superconductivity, Magnetism, Pnictogen, Condensed matter physics, Context (archaeology), Liquid crystal, Phase (matter), Quantum mechanics, Rheology, Pickering emulsion</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Antiferromagnetism, Pairing, Hubbard model, Bilayer graphene, Monte Carlo method, Coulomb, Quantum mechanics, Bubble, Scaling, Displacement (psychology), Reciprocal lattice, Relaxation (psychology), Exponential function, Distribution function, Particle (ecology), Scattering, Magnetism, Phase (matter), Range (aeronautics), Order (exchange), Nuclear magnetic resonance, Computer science, Topological insulator, Band gap, Insulator (electricity)</t>
+          <t>Coalescence (physics), Emulsion, Polystyrene, Particle (ecology), Chemical engineering, Nanotechnology, Polymer science, Composite material, Nanoparticle, Polymer, Capsid, Charge (physics), Static electricity, RNA, Genome, Electrostatics, Coat protein, Protein stability, Solvency, Aqueous solution, Solubility, Solvent, Work (physics), Swelling, Hildebrand solubility parameter</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>183</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09538984V33I3</t>
+          <t>09538984V30I3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -617,40 +617,40 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Band gap, Phase transition, Drop (telecommunication), Condensed matter physics, Phase (matter), Hysteresis, Electronic band structure, Direct and indirect band gaps, Materials science, Chemistry, Physics, Telecommunications, Topological insulator, van der Waals force, Image warping, Lattice (music), Hexagonal lattice, Surface states, Dirac (video compression format), Hexagonal crystal system, Landau quantization, Quantum oscillations, Geometric phase, Magnetic field, Quantum Hall effect</t>
+          <t>Magnetism, Ultrashort pulse, Physics, Condensed matter physics, Optics, Surface tension, Mechanics, Laminar flow, Reynolds number, Turbulence, Mixing (physics), Thermodynamics, Materials science, Intramolecular force, Polymer, Scaling, Single chain, Stiffness, Gaussian, Chemical physics, Gaussian network model, Nanoparticle, Chain (unit), Persistence length, Bending stiffness</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>De Haas–van Alphen effect, Magnetization, Oscillation (cell signaling), Field (mathematics), Quantum mechanics, Fermi surface, Subspace topology, Topology (electrical circuits), Magnetic flux, Topological order, Statistical physics, Quantum, Mathematics, Mathematical analysis, Demagnetizing field, Ultrashort pulse, Entropy (arrow of time), Optics, Thermodynamics, Positronium, Positron, Electron, Hydrofluoric acid, Annihilation, Thermal conduction</t>
+          <t>Chemistry, Nanotechnology, Composite material, Computational chemistry, Geometry, Stereochemistry, Mathematics, Amorphous ice, Nucleation, Ice nucleus, Amorphous solid, Crystallography, Monte Carlo method, DNA, Folding (DSP implementation), Monomer, Ring (chemistry), Base pair, Biological system, Biology, Counterion, Observable, Planar, Charge density, Valence (chemistry)</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
-        <v>339</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>09538984V33I4</t>
+          <t>09538984V30I4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -659,40 +659,40 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Spintronics, Heterojunction, Condensed matter physics, van der Waals force, Dipole, Materials science, Electric field, Physics, Ferromagnetism, Quantum mechanics, Perovskite (structure), Photoluminescence, Phase transition, Tetragonal crystal system, Exciton, Orthorhombic crystal system, Phase (matter), Crystallography, Chemistry, Optoelectronics, Crystal structure, Bilayer graphene, Magnetic field, Bilayer, Momentum (technical analysis)</t>
+          <t>Polymer, Solvent, Dipole, Thermodynamics, Supercritical fluid, Dielectric, Context (archaeology), Chain (unit), Chemical physics, Solvent effects, Materials science, Chemistry, Polymer chemistry, Physics, Organic chemistry, Quantum mechanics, Computer science, Artificial intelligence, Machine learning, Terminology, Data science, Component (thermodynamics), Dimensionality reduction, Field (mathematics), Big data</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Landau quantization, Magnetoresistance, Cyclotron, Viscosity, Toolbox, Identification (biology), Artificial intelligence, Computer science, Image processing, Automation, Maxima and minima, Pattern recognition (psychology), Computer vision, Task (project management), Image (mathematics), Mathematics, Engineering, Superconductivity, Generalization, Order (exchange), Focalization, Critical phenomena, Exponential function, Photoconductivity, X-ray photoelectron spectroscopy</t>
+          <t>Data mining, Swelling, RADIUS, Phase transition, Colloid, Fourier transform, Phase (matter), Simple (philosophy), Colloidal particle, Capsid, RNA, Base pair, Biophysics, Genome, Biology, Virus, DNA, Genetics, Gene, Semiconductor, Band gap, Quasiparticle, Oxide, Electronic structure, Optoelectronics</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09538984V33I5</t>
+          <t>09538984V30I5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magnon, Angular momentum, Spin wave, Annihilation, Lattice (music), Magnetic field, Spin (aerodynamics), Homogeneous, Symmetry (geometry), Condensed matter physics, Graphene, Polariton, Antiferromagnetism, Ferromagnetism, Slab, Fermi level, Materials science, Physics, Magnetic moment, Fermi surface, Electron, Nanotechnology, Quantum mechanics, Superconductivity, Geophysics</t>
+          <t>Graphene, Electron, Physics, Classical fluids, Phase diagram, Motion (physics), Quantum, State of matter, Theoretical physics, Statistical physics, Condensed matter physics, Classical mechanics, Phase (matter), Quantum mechanics, Ultrashort pulse, Laser, Extreme ultraviolet lithography, Free-electron laser, Nanotechnology, Free electron model, Optics, Engineering physics, Materials science, Nuclear physics, BODIPY</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Specular reflection, Phonon, Reflection (computer programming), Crystal (programming language), Optics, Computer science, Time-dependent density functional theory, Density functional theory, Convergence (economics), Imaginary time, Ground state, Plane wave, Statistical physics, Quantum, Quantum dynamics, Doping, Metal–insulator transition, Magnetism, Electronic structure, Scattering, Crystallography, Metal, Chemistry, Planck constant, Chaotic</t>
+          <t>Ultrafast laser spectroscopy, Chromophore, Photochemistry, Chemistry, Photoinduced electron transfer, Electron transfer, Fluorescence, Ultrafast electron diffraction, Quenching (fluorescence), Absorption (acoustics), Time-resolved spectroscopy, Spectroscopy, Microchannel, Mechanics, Pressure drop, Scaling, Reynolds number, Displacement (psychology), Lubrication theory, Lubrication, Flow (mathematics), Fluid dynamics, Elasticity (physics), Volumetric flow rate, Deformation (meteorology)</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O6" t="n">
-        <v>212</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09538984V33I6</t>
+          <t>09538984V30I6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -743,40 +743,40 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Physics, Vortex, Condensed matter physics, Spinor, Angular momentum, Vorticity, Quantum mechanics, Merge (version control), Coulomb, Amplitude, Ground state, Electron, Boundary value problem, First order, Transition point, Materials science, Debye model, Bulk modulus, Ternary operation, Crystallography, Chemistry, Attenuation, Blueshift, Computational physics, Molecular physics</t>
+          <t>Magnet, Magnetic moment, Computer science, First principle, Artificial intelligence, Statistical physics, Materials science, Physics, Mechanical engineering, Density functional theory, Condensed matter physics, Engineering, Quantum mechanics, Superlattice, Ternary operation, Band gap, Nitride, Photoluminescence, Electric field, Monolayer, Polar, Electronic band structure, Wide-bandgap semiconductor, Lattice constant, Optoelectronics</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Optics, Mechanics, Polymer, Cationic polymerization, Methacrylate, Hydrophobic effect, Polar, Membrane, Functional polymers, Chemical physics, Polymer chemistry, Chemical engineering, Monomer, Copolymer, Organic chemistry, Permalloy, Ellipse, Dipole, Ferromagnetic resonance, Superposition principle, Ferromagnetism, Orientation (vector space), Magnetic field, Geometry, Mathematics</t>
+          <t>Optics, Nanotechnology, Diffraction, Layer (electronics), Polymer, Magnetic nanoparticles, Characterization (materials science), Coupling (piping), Focus (optics), Particle (ecology), Deformation (meteorology), Magnetic particle inspection, Polymer science, Composite material, Nanoparticle, Homochirality, Chirality (physics), Molecular dynamics, Enantiomer, Abiogenesis, Chemistry, Chemical physics, Computational chemistry, Stereochemistry, Astrobiology</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="O7" t="n">
-        <v>361</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09538984V33I7</t>
+          <t>09538984V30I7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -785,40 +785,40 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Chalcogenide, Band gap, Metastability, Gallium, Ternary operation, Materials science, Chalcopyrite, Copper, van der Waals force, Electronic band structure, Annealing (glass), Direct and indirect band gaps, Chemical physics, Condensed matter physics, Crystallography, Chemistry, Optoelectronics, Physics, Weyl semimetal, Ferromagnetism, Paramagnetism, Curie temperature, Magnetic domain, Phase transition, Semimetal</t>
+          <t>Multiferroics, Piezoelectricity, Ferroelectricity, Materials science, Symmetry (geometry), Polar, Condensed matter physics, Perpendicular, Work (physics), Physics, Dielectric, Optoelectronics, Composite material, Quantum mechanics, Mathematics, Warm dense matter, Quantum, State of matter, Degenerate energy levels, Electron, Wavelength-division multiplexing, Matter wave, Computational physics, Wavelength, Brownian motion</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Domain (mathematical analysis), Heterojunction, Photocatalysis, Photoexcitation, Band offset, Density functional theory, Charge carrier, Facet (psychology), Electron, Water splitting, Dielectric, Molecular physics, Computational chemistry, Atomic physics, Valence band, Catalysis, Anode, Lithium (medication), Potassium, Diffusion, Atom (system on chip), Ion, Sodium, Thermal diffusivity, Metal</t>
+          <t>Structure factor, Thermal diffusivity, Brownian dynamics, Wave vector, Dynamic structure factor, Diffusion, Rotational diffusion, Corundum, X-ray photoelectron spectroscopy, Chromium, Epitaxy, Electron diffraction, Single crystal, Chemical vapor deposition, Crystallography, Diffraction, Synchrotron, Scattering, Deposition (geology), Surface (topology), Analytical Chemistry (journal), Chemistry, Nanotechnology, Metallurgy, Layer (electronics)</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O8" t="n">
-        <v>191</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09538984V33I8</t>
+          <t>09538984V35I1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -827,40 +827,40 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Fermi surface, Ion, Electron, Chemistry, Physics, Superconductivity, Bilayer, Electric field, Band gap, Monolayer, Bilayer graphene, Stacking, Semiconductor, Alloy, Atom (system on chip), Artificial neural network, Materials science, Computer science, Metallurgy, Artificial intelligence, Embedded system, Raman spectroscopy, Curse of dimensionality, Ab initio</t>
+          <t>Electromotive force, Dissipative system, Physics, Spin (aerodynamics), Adiabatic process, Classical mechanics, Degrees of freedom (physics and chemistry), Charge (physics), Conservative force, Condensed matter physics, Quantum mechanics, Thermodynamics, Monolayer, Semiconductor, Materials science, Band gap, Direct and indirect band gaps, Tetragonal crystal system, Dipole, Electronic structure, Honeycomb structure, Optoelectronics, Nanotechnology, Chemistry, Crystallography</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Bounded function, Ab initio quantum chemistry methods, Phonon, High pressure, Analytical Chemistry (journal), Crystallography, Thermodynamics, Optics, Molecule, Mathematics, Fermion, Spin (aerodynamics), Ising model, Effective mass (spring–mass system), Fermi energy, Density of states, Quantum electrodynamics, Quantum mechanics, Zeeman effect, Spin Hall effect, Quantum spin Hall effect, Anisotropy, Spin–orbit interaction, Quantum Hall effect, Electrical conductor</t>
+          <t>Crystal structure, Heterojunction, Photocatalysis, Janus, Water splitting, Photocatalytic water splitting, Graphene, van der Waals force, Transition metal, Electric field, Nitride, Layer (electronics), Molecule, Catalysis, Instability, Vortex, Planar, Soliton, Computation, Transverse plane, Bose–Einstein condensate, Numerical analysis, Trap (plumbing), Computer simulation, Statistical physics</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>231</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>09538984V33I9</t>
+          <t>09538984V35I2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Extended X-ray absorption fine structure, Bond length, Crystallography, Valence (chemistry), Absorption (acoustics), Atom (system on chip), Chemistry, Materials science, Analytical Chemistry (journal), Crystal structure, Absorption spectroscopy, Physics, Germanene, Condensed matter physics, Berry connection and curvature, Point reflection, Rashba effect, Monolayer, Silicene, Graphene, Geometric phase, Ferromagnetism, Nanotechnology, Spintronics, Quantum mechanics</t>
+          <t>Heterojunction, Materials science, Condensed matter physics, van der Waals force, Magnetic anisotropy, Electric field, Semiconductor, Spintronics, Band gap, Anisotropy, Magnetic semiconductor, Magnetic field, Chemistry, Ferromagnetism, Optoelectronics, Magnetization, Physics, Optics, Molecule, Delafossite, Crucible (geodemography), Scanning electron microscope, Oxide, Fabrication, Crystal growth</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ferroelectricity, Ferroelasticity, Resonant ultrasound spectroscopy, Multiferroics, Phase transition, Orthorhombic crystal system, Mesoscopic physics, Anharmonicity, Nuclear magnetic resonance, Dielectric, Composite material, Silicon carbide, Silicon, Wafer, Carbide, Layer (electronics), Polishing, Shear (geology), Molecular dynamics, Optoelectronics, Renormalization, Lattice (music), Statistical physics, Density matrix renormalization group, Atomic orbital</t>
+          <t>Nanotechnology, Analytical Chemistry (journal), Crystallography, Metallurgy, Photocatalysis, Density functional theory, Crystal (programming language), Electronic band structure, Wide-bandgap semiconductor, Microwave, Crystal structure, High pressure, Computational chemistry, Thermodynamics, Catalysis, Organic chemistry, Thionine, Ion, Irradiation, DNA, Photosensitizer, Photochemistry, Electrode, Electrochemistry, Physical chemistry</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>09538984V33I10</t>
+          <t>09538984V35I3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -911,40 +911,40 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Hydrostatic pressure, Raman spectroscopy, Tetragonal crystal system, Hydrostatic equilibrium, Materials science, Lattice (music), Condensed matter physics, Chemical physics, Crystal structure, Thermodynamics, Chemistry, Crystallography, Optics, Physics, Delocalized electron, Heat-assisted magnetic recording, Magnetic moment, Copper, Electronic structure, Atomic orbital, Density functional theory, Ab initio, Magnetic anisotropy, Anisotropy, Boron</t>
+          <t>Electron, Delocalized electron, MXenes, Materials science, Fabrication, Chemical physics, Core electron, Atomic physics, Condensed matter physics, Nanotechnology, Chemistry, Physics, Black phosphorus, Graphene, Sensitivity (control systems), Analyte, Layer (electronics), Optoelectronics, Range (aeronautics), Computer science, Electronic engineering, Composite material, Engineering, Bilayer graphene, Electric field</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Electron, Computational chemistry, Magnetization, Magnetic field, Metallurgy, Cobaltite, Ionic bonding, Ion, Nanotechnology, Phosphorene, Electric field, Doping, Spin (aerodynamics), Graphene, Spin states, Magnetism, Enhanced Data Rates for GSM Evolution, Transverse plane, Spin polarization, Band gap, Supercooling, Thermal diffusivity, Crossover, Diffusion, Brownian motion</t>
+          <t>Zigzag, Fermi energy, Fermi level, Ribbon, Enhanced Data Rates for GSM Evolution, Molecular physics, Geometry, Quantum mechanics, Quantum dot, Hamiltonian (control theory), Exciton, Wannier function, Degeneracy (biology), Monolayer, Boron nitride, Mathematics, Anharmonicity, Phonon, Quartic function, Lattice (music), Thermal conductivity, Square lattice, Phase transition, Thermodynamics, Nucleation</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
-        <v>217</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09538984V33I11</t>
+          <t>09538984V35I4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -953,40 +953,40 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Density functional theory, Perspective (graphical), Field (mathematics), Statistical physics, Active matter, Non-equilibrium thermodynamics, Variety (cybernetics), Work (physics), Physics, Nanotechnology, Theoretical physics, Materials science, Computer science, Thermodynamics, Quantum mechanics, Mathematics, Heterojunction, Semiconductor, Quantum tunnelling, van der Waals force, Optoelectronics, Photodetector, Coupling (piping), Instability, Perturbation (astronomy)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Classical mechanics, Dynamics (music), Deformation (meteorology), Range (aeronautics), Ring (chemistry), Perturbation theory (quantum mechanics), Mechanics, Electrostatics, Chemistry, Spinor, Hamiltonian (control theory), Bose–Einstein condensate, Boson, Condensed matter physics, Quantum electrodynamics, Toroid, Vortex, Plasma, Monolayer, Strain (injury), Adsorption, Metal, Physical chemistry, Metallurgy, Spintronics</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
         <v>11</v>
       </c>
-      <c r="I12" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Electron, Spin polarization, Scattering, Asymmetry, Reflection (computer programming), Spin (aerodynamics), Polarization (electrochemistry), Figure of merit, Condensed matter physics, Physics, Optics, Atomic physics, Materials science, Chemistry, Nuclear physics, Quantum mechanics, Fokker–Planck equation, Statistical physics, Discretization, Eigenfunction, Eigenvalues and eigenvectors, Square root, Molecular dynamics, Flux (metallurgy), Operator (biology)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Work (physics), Grid, Mathematics, Applied mathematics, Mathematical analysis, Partial differential equation, Geometry, Hamiltonian (control theory), Renormalization, Luttinger liquid, Renormalization group, Fermion, Kinetic energy, Coulomb, Quantum electrodynamics, Quantum, Wannier function, Band gap, Hybrid functional, Electronic band structure, Atomic orbital, Spurious relationship, Electronic structure, Fermi level, Charge (physics)</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>20</v>
-      </c>
       <c r="O12" t="n">
-        <v>196</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>09538984V33I12</t>
+          <t>09538984V35I5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -995,40 +995,40 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Resonant ultrasound spectroscopy, Multiferroics, Paramagnetism, Materials science, Orthorhombic crystal system, Relaxation (psychology), Magnetization, Coupling (piping), Dielectric, Antiferromagnetism, Phase transition, Nuclear magnetic resonance, Chemistry, Ferroelectricity, Crystallography, Magnetic field, Physics, Crystal structure, Amorphous solid, Observable, Statistical physics, Exponent, Work (physics), Saturation (graph theory)</t>
+          <t>Bridging (networking), Thermal management of electronic devices and systems, Electronics, Computer science, Thermal, Nanotechnology, Dissipation, Focus (optics), Materials science, Thermal resistance, Mechanical engineering, Engineering physics, Biochemical engineering, Engineering, Physics, Electrical engineering, Thermodynamics, Paramagnetism, Magnetic field, Compressibility, Convection, Body force, Condensed matter physics, Ferrofluid, Magnetic pressure</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Grain size, Interpretation (philosophy), Random walk, Mathematics, Statistics, Thermodynamics, Computer science, Quantum mechanics, Spinel, Stoichiometry, X-ray photoelectron spectroscopy, Jahn–Teller effect, Single crystal, Catalysis, Absorption spectroscopy, Analytical Chemistry (journal), Ion, Physical chemistry, Quantum dot, Asymmetry, Electronic structure, Density functional theory, Coupling strength, Atomic orbital, Nanotechnology</t>
+          <t>Helmholtz free energy, Work (physics), Mechanics, Classical mechanics, Chemistry, Magnetization, Quantum mechanics, Diffraction, Synchrotron radiation, Beamline, Synchrotron, Phase transition, Crystal (programming language), Monochromator, Phase (matter), Crystallography, Synchrotron Radiation Source, Single crystal, X-ray crystallography, Optics, Optoelectronics, Mesoscopic physics, Superconductivity, Cooper pair, Quantum tunnelling</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>210</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>09538984V33I13</t>
+          <t>09538984V35I6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1037,40 +1037,40 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Raman spectroscopy, Dissipation, Raman scattering, Materials science, Spectroscopy, Optoelectronics, Coherent anti-Stokes Raman spectroscopy, Molecular physics, Optics, Chemistry, Physics, Ferrimagnetism, Demagnetizing field, Spin (aerodynamics), Coupling (piping), Magnetization, Femtosecond, Angular momentum, Momentum (technical analysis), Condensed matter physics, Antiferromagnetism, Phonon, Magnetic field, Thermal conductivity, Boltzmann equation</t>
+          <t>Graphene, Physisorption, Heterojunction, Thin film, Materials science, Oxide, Adsorption, Chemical bath deposition, Absorption (acoustics), Chemical vapor deposition, Chemical engineering, Nanotechnology, Optoelectronics, Chemistry, Physical chemistry, Monolayer, Band gap, Electronic structure, Ionic bonding, Dielectric, Phonon, Condensed matter physics, Crystallography, Physics, Ion</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Scattering, Anisotropy, Semimetal, Thermoelectric materials, Thermal conduction, Phonon scattering, Thermoelectric effect, Mean free path, Topology (electrical circuits), Band gap, Quantum mechanics, Massless particle, Graphene, Parametrization (atmospheric modeling), Dirac (video compression format), Constant (computer programming), Charge (physics), Spacetime, Space (punctuation), Electronic structure, Superconductivity, Topological insulator, Insulator (electricity), Electrical engineering, Engineering</t>
+          <t>Copper, Crystal structure, Hexagonal crystal system, Context (archaeology), Binary number, Mulliken population analysis, Chemical physics, Density functional theory, Computational chemistry, Mathematics, Metallurgy, Geography, Nanoparticle, Doping, Engineering, Plasmon, Nanowire, Aluminium, Silicon, Amorphous solid, Ultraviolet, Scanning electron microscope, Spectroscopy, Composite material, Bulk modulus</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>201</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>09538984V33I14</t>
+          <t>09538984V35I7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1079,40 +1079,40 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magnetic refrigeration, Paramagnetism, Critical exponent, Ferromagnetism, Curie temperature, Phase transition, Rietveld refinement, Magnetic field, Floquet theory, Wannier function, Graphene, Dirac fermion, Physics, Hamiltonian (control theory), Quantum mechanics, Fermion, Dirac (video compression format), Condensed matter physics, Mathematics, Nonlinear system, Materials science, Doping, Polar, Distortion (music), Thermal conduction</t>
+          <t>Heterojunction, Thermoelectric effect, Materials science, Nanotechnology, Thermoelectric materials, Engineering physics, Optoelectronics, Engineering, Physics, Algorithm, Topology (electrical circuits), Artificial intelligence, Computer science, Mathematics, Combinatorics, Humanities, Art, Vortex, Thermodynamics, Oxidizing agent, Bismuth, Selenide, Phase (matter), Environmental science, Chemistry</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Optoelectronics, Engineering physics, Composite material, Pnictogen, Superconductivity, Fermi surface, Brillouin zone, Magnetoresistance, Electron, Ansatz, Irradiation, Quantum, Spin–orbit interaction, Polarization (electrochemistry), Spin polarization, Chemistry, MAJORANA, Josephson effect, Majorana equation, Spin (aerodynamics), Dirac sea, Dislocation, Molecular dynamics, Ultimate tensile strength, Brittleness</t>
+          <t>Metallurgy, Selenium, Propagator, Coulomb, Dirac fermion, Dirac equation, Perturbation theory (quantum mechanics), Electron, Quantum mechanics, Graphene, Momentum (technical analysis), Quantum electrodynamics, Fermion, Phonon, Condensed matter physics, Bilayer, Superconductivity, Magnetic field, Realization (probability), Field (mathematics), Current (fluid), Doping, Critical field, Mechanics, Wurtzite crystal structure</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>210</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>09538984V33I15</t>
+          <t>09538984V35I8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1121,40 +1121,40 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Ternary operation, Cluster expansion, Chemical stability, Cluster (spacecraft), Phase diagram, Binary number, Stability (learning theory), Phonon, Thermal expansion, Materials science, Compressibility, Thermodynamics, Triple point, Phase transition, Phase (matter), Diamond anvil cell, Hysteresis, Diffraction, Volume (thermodynamics), Condensed matter physics, Crystallography, High pressure, Chemistry, Statistical physics, Maxima and minima</t>
+          <t>Condensed matter physics, Renormalization group, Phase transition, Physics, Critical phenomena, Ferromagnetism, Superconductivity, Multiferroics, Critical point (mathematics), Statistical physics, Theoretical physics, Quantum mechanics, Ferroelectricity, Mathematics, Spintronics, Chalcogenide, Magnetism, Curie temperature, Magnetic semiconductor, Materials science, Semiconductor, Optoelectronics, Topological insulator, Anisotropy, Surface plasmon</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Pair potential, Potential energy, Granularity, Range (aeronautics), Physics, Quantum mechanics, Mathematics, Computer science, Orthorhombic crystal system, Antiferromagnetism, Dielectric, Neutron diffraction, Magnetization, Hexagonal phase, Doping, Crystallite, Ion, Dopant, Analytical Chemistry (journal), Crystal structure, Magnetic field, Hexagonal crystal system, Transmission electron microscopy, Nanoparticle, Chemical physics</t>
+          <t>Plasmon, Dielectric, Optics, Superfluidity, Kinetic energy, Momentum (technical analysis), Liquid helium, Condensation, Bose–Einstein condensate, Superfluid helium-4, RADIUS, Quantum, Position and momentum space, Zero-point energy, Helium, Thermodynamics, Argon, Intercalation (chemistry), Honeycomb, Ion, Nanotechnology, Chemical engineering, Chemistry, Inorganic chemistry, Composite material</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
-        <v>219</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>09538984V33I16</t>
+          <t>09538984V35I9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1163,40 +1163,40 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Magnetic moment, Paramagnetism, Magnetism, Density functional theory, Physics, Electron magnetic dipole moment, Fermi level, Spin (aerodynamics), Magnetic dipole, Electron, Magnetic field, Quantum mechanics, Boron nitride, Delocalized electron, Antibonding molecular orbital, Materials science, Nitride, Boron, Metal, Crystallography, Atomic orbital, Computational chemistry, Nanotechnology, Chemistry</t>
+          <t>Nanophotonics, Nanotechnology, Fabrication, Materials science, Nanolithography, Field (mathematics), Optoelectronics, Asymmetry, Condensed matter physics, Photovoltaic system, Polarization (electrochemistry), Antiferroelectricity, Superposition principle, Poling, Voltage, Biasing, Photovoltaic effect, Sign (mathematics), Physics, Chemistry, Ferroelectricity, Electrical engineering, Quantum mechanics, Dielectric, Mathematics</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Metallurgy, Beamline, Undulator, Optics, NIST, Linear particle accelerator, Particle accelerator, Scattering, Beam (structure), Computer science, Monolayer, Nonmetal, Nanosheet, Doping, Adsorption, Molecule, Dopant, Catalysis, Inorganic chemistry, Physical chemistry, Organic chemistry, Optoelectronics, Electronic structure, Stacking, Atom (system on chip)</t>
+          <t>Orthorhombic crystal system, Crystallite, Corundum, Phase transition, Phase (matter), Stishovite, Compressive strength, Laser, Diffraction, Composite material, Mineralogy, Analytical Chemistry (journal), Thermodynamics, Optics, Metallurgy, Electric field, Topological insulator, Topology (electrical circuits), Spin–orbit interaction, Perpendicular, Coupling (piping), Geometry, Overlayer, Brillouin zone, Graphite</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O17" t="n">
-        <v>216</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09538984V33I17</t>
+          <t>09538984V35I10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1205,40 +1205,40 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nanoelectromechanical systems, Quantum, Electronic systems, Hamiltonian (control theory), Mechanical system, Quantum dot, Silicene, Condensed matter physics, Physics, Graphene, Vertex (graph theory), Electric field, Population, Quantum mechanics, Mathematics, Microrheology, Attraction, Plateau (mathematics), Brownian motion, Mean free path, Chemistry, Hard spheres, SPHERES, Range (aeronautics), Chemical physics</t>
+          <t>Algorithm, Materials science, Computer science, Raman spectroscopy, Phonon, Nanocrystalline material, Ternary operation, Crystallite, Spectroscopy, Characterization (materials science), Nanocrystal, Nanotechnology, Semiconductor, Condensed matter physics, Optoelectronics, Physics, Optics, Metallurgy, Fermion, Heavy fermion, Theoretical physics, Coherence (philosophical gambling strategy), Superconductivity, Scaling, Quantum mechanics</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Molecular physics, Rheology, Materials science, Optics, Scattering, Thermodynamics, Composite material, Nanosheet, Semiconductor, Band gap, Photovoltaic system, Heterojunction, Monolayer, Borophene, Honeycomb, Boron, Optoelectronics, Direct and indirect band gaps, Thermal stability, Honeycomb structure, Solar cell, Nanotechnology, Chemical engineering, Quantum oscillations, Fermi surface</t>
+          <t>Geometry, Mathematics, Thermoelectric effect, Seebeck coefficient, Thermoelectric generator, Thermoelectric cooling, Quantum tunnelling, Figure of merit, Thermoelectric materials, Thermodynamics, Intermetallic, Cluster (spacecraft), Crystallography, Molecular dynamics, Thermal stability, Voronoi diagram, Polyhedron, Chemistry, Alloy, Computational chemistry, Excitation, Skyrmion, Magnetic field, Lattice (music), Magnetic structure</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>214</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>09538984V33I18</t>
+          <t>09538984V35I11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1247,40 +1247,40 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Drag, Electrical resistivity and conductivity, Coulomb, Scattering, Plasmon, Valence (chemistry), Density of states, Physics, Materials science, Quantum mechanics, Electron, Thermodynamics, Electric field, Absorption (acoustics), Joule heating, Dielectric, Electrical impedance, Absorption spectroscopy, Chemistry, Molecular physics, Atomic physics, Optics, Optoelectronics, Tetragonal crystal system</t>
+          <t>Density functional theory, Electronic structure, Fermi level, Plasmon, Valence (chemistry), Electronic correlation, Spectral line, Photoemission spectroscopy, Spectroscopy, Electron, Binding energy, Electronic band structure, Atomic physics, Condensed matter physics, Physics, Quantum mechanics, Rubidium, Aspect ratio (aeronautics), Relaxation (psychology), Brillouin zone, Intensity (physics), Rayleigh scattering, Density ratio, Range (aeronautics), Dimensionless quantity</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Superstructure, Ab initio, Electronic structure, Ab initio quantum chemistry methods, Superconductivity, Electronic band structure, Symmetry (geometry), Crystallography, Crystal structure, Molecule, Mathematics, Passivation, Band gap, Density functional theory, Vacancy defect, Metal, Semiconductor, Computational chemistry, Nanotechnology, Instability, Nonlinear system, Liquid crystal, Flow (mathematics), Mechanics, Statistical physics</t>
+          <t>Chemistry, Thermodynamics, Optics, Mechanics, Materials science, Clathrate hydrate, Phonon, Excitation, Dispersion (optics), Analytical Chemistry (journal), Hydrate, Diamond, Thermal conductivity, Material properties of diamond, Thermal expansion, Composite number, Doping, Composite material, Optoelectronics, Perovskite (structure), Heterojunction, Mineralogy, Crystallography, Exciton, Polariton</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
-        <v>221</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>09538984V33I19</t>
+          <t>09538984V35I12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1289,40 +1289,40 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Helium, Nitrogen gas, Nitrogen, Relaxation (psychology), Materials science, Aerogel, Spin–lattice relaxation, Porosity, Lattice (music), Analytical Chemistry (journal), Nuclear magnetic resonance, Condensed matter physics, Chemistry, Atomic physics, Composite material, Paramagnetism, Physics, Amorphous solid, Metastability, Coordination number, Scattering, Phase (matter), Diffraction, Ionic bonding, Structure factor</t>
+          <t>Relaxation (psychology), Random walk, Statistical physics, Jump, Function (biology), Continuous-time random walk, Materials science, Mathematics, Physics, Statistics, Quantum mechanics, Psychology, Wafer, Sputter deposition, Optoelectronics, Sapphire, Molybdenum disulfide, Sputtering, Nanotechnology, Raman spectroscopy, Thin film, Optics, Composite material, Laser, Photocurrent</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Range (aeronautics), Thin film, Chemical physics, Crystallography, Optics, Nanotechnology, Ion, Frustration, Magnetization, Coupling (piping), Atmospheric temperature range, Ferromagnetism, Magneto, Curie temperature, Synchrotron, Thermodynamics, Magnetic field, Metallurgy, Physical chemistry, Interpretability, Artificial neural network, Context (archaeology), Experimental data, Process (computing), Uncertainty quantification</t>
+          <t>Photodiode, Spin–orbit interaction, Anisotropy, Diode, Coupling (piping), Electron, Spin (aerodynamics), Point reflection, Condensed matter physics, Molecular physics, Magnetoresistance, Magnetization, Oscillation (cell signaling), Semimetal, Magnetic monopole, Symmetry (geometry), Scattering, Magnetic field, Geometry, Chemistry, Nucleobase, Guanine, Thymine, Cytosine, DNA</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O20" t="n">
-        <v>219</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>09538984V33I20</t>
+          <t>09538984V35I13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1331,40 +1331,40 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Graphyne, Magnetism, Condensed matter physics, Magnetic moment, Atomic orbital, Spintronics, Materials science, Spin polarization, Paramagnetism, Spin–orbit interaction, Chemistry, Electron, Density functional theory, Physics, Ferromagnetism, Computational chemistry, Phonon, Semiconductor, Excited state, Band gap, Excitation, Relaxation (psychology), Polar, Spectroscopy, Transverse plane</t>
+          <t>Phonon, Janus, Boltzmann equation, Selenide, Effective mass (spring–mass system), Condensed matter physics, Scattering, Materials science, Thermoelectric effect, Indium, Electron mobility, Thermal conductivity, Nanotechnology, Phonon scattering, Engineering physics, Optoelectronics, Physics, Optics, Quantum mechanics, Anatase, Photocatalysis, Electron, Vacancy defect, Oxygen, Fermi level</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Optoelectronics, Atomic physics, Dispersity, SPHERES, Order (exchange), Crystallography, Polymer chemistry, Business, Phase diagram, Magnetic refrigeration, Multicritical point, Magnetization, Multiferroics, Magnetic field, Phase (matter), Atmospheric temperature range, Triple point, Field (mathematics), Thermodynamics, Quantum mechanics, Ferroelectricity, Impurity, Anatase, Dopant, Doping</t>
+          <t>Population, Ultraviolet, Photochemistry, Water splitting, Aqueous solution, Valence (chemistry), Analytical Chemistry (journal), Chemistry, Catalysis, Crystallography, Physical chemistry, Ferromagnetism, Domain (mathematical analysis), Dynamics (music), Spin (aerodynamics), Domain wall (magnetism), Classical mechanics, Mathematics, Magnetic field, Magnetization, Thermodynamics, Mathematical analysis, Scanning tunneling microscope, Scanning tunneling spectroscopy, Density of states</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>216</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09538984V33I21</t>
+          <t>09538984V35I14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1373,40 +1373,40 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H22" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X-ray photoelectron spectroscopy, Silicon, Adsorption, Acetophenone, Density functional theory, Materials science, Scanning tunneling microscope, Dimer, Chemistry, Crystallography, Computational chemistry, Nanotechnology, Physical chemistry, Optoelectronics, Organic chemistry, Chemical engineering, Hubbard model, Strongly correlated material, Spectral properties, Perspective (graphical), Vertex (graph theory), Electron, Scattering, Condensed matter physics, Topological insulator</t>
+          <t>Bilayer graphene, Graphene, Dirac fermion, Physics, Condensed matter physics, Massless particle, Superlattice, Dirac (video compression format), Magic angle, Quantum mechanics, Spectral line, Molybdenum, Nanotechnology, Materials science, Electronics, Engineering physics, Chemistry, Metallurgy, Superconductivity, Monolayer, Electron, Phonon, Anisotropy, Fermi level, Electronic band structure</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Antiferromagnetism, Magnetism, Physics, Spin (aerodynamics), Fermi energy, Fermi level, Monolayer, Quantum spin Hall effect, Band gap, Quantum Hall effect, Quantum anomalous Hall effect, Insulator (electricity), Magnetic field, Quantum mechanics, Convection, Viscosity, Component (thermodynamics), Transient (computer programming), Thermodynamics, Rayleigh number, Thermal, Colloid, Coupling (piping), Chemical physics, Natural convection</t>
+          <t>Saddle point, Cooper pair, Heterojunction, Ferroelectricity, Optoelectronics, Stacking, Transistor, Diode, Polarization (electrochemistry), Chip, Field-effect transistor, Computer science, Electrical engineering, Voltage, Telecommunications, Engineering, Skyrmion, Precession, Oscillation (cell signaling), Magnetic moment, Magnetic field, Spin (aerodynamics), Helicity, Moment (physics), Classical mechanics</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
-        <v>221</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>09538984V33I22</t>
+          <t>09538984V35I15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1415,40 +1415,40 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H23" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Quantum oscillations, Magnetic field, Landau quantization, Oscillation (cell signaling), Fermi surface, Gapless playback, Semimetal, Valence (chemistry), Photoluminescence, Photon upconversion, Materials science, Optoelectronics, Doping, Magnetization, Anisotropy, Magnetic anisotropy, Condensed matter physics, Thin film, Epitaxy, Analytical Chemistry (journal), Deposition (geology), Chemistry, Nanotechnology, Optics, Physics</t>
+          <t>Tetrazine, Chemistry, Combinatorial chemistry, Center (category theory), Active center, Metal, Organic chemistry, Crystallography, Inner core, Earth (classical element), Core (optical fiber), Diffusion, Alkaline earth metal, Chemical physics, Materials science, Geology, Physics, Geophysics, Thermodynamics, Metallurgy, Mathematical physics, Simple (philosophy), Dispersion (optics), Dynamics (music), Phase (matter)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Geology, Hamiltonian (control theory), Graphene, Subspace topology, Tight binding, Molecular physics, Electronic structure, Quantum mechanics, Mathematics, Mathematical analysis, MXenes, Annealing (glass), MAX phases, Spark plasma sintering, Carbide, Titanium carbide, Tantalum carbide, Nitride, Vacancy defect, Lamellar structure, Sintering, Titanium, Crystallography, Metallurgy, Layer (electronics)</t>
+          <t>Dispersion relation, Statistical physics, Condensed matter physics, Quantum mechanics, Rejuvenation, Amorphous metal, Ductility (Earth science), Quenching (fluorescence), Volume (thermodynamics), Relaxation (psychology), Composite material, Shear matrix, Liquid nitrogen, Thermal treatment, Thermal, Alloy, Creep, Optics, Pairing, Andreev reflection, Silicene, Valleytronics, Spin (aerodynamics), Conductance, Superconductivity</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>218</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>09538984V33I23</t>
+          <t>09538984V35I16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1457,40 +1457,40 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Viscoelasticity, Dissipative system, Mesoscopic physics, Uniqueness, Phenomenological model, Stability (learning theory), Phase (matter), Rheology, X-ray photoelectron spectroscopy, Transformative learning, Snapshot (computer storage), Nanotechnology, Computer science, Engineering physics, Materials science, Physics, Nuclear magnetic resonance, Sociology, Magnetic refrigeration, Alloy, Isothermal process, Magnetic shape-memory alloy, Magnetization, Adiabatic process, Condensed matter physics</t>
+          <t>Polyamorphism, Amorphous solid, Materials science, Tetrahedron, Chemical physics, Coordination number, Octahedron, Density functional theory, Work (physics), High pressure, Local structure, Electronic structure, Diffraction, Crystallography, Condensed matter physics, Nanotechnology, Engineering physics, Crystal structure, Thermodynamics, Chemistry, Physics, Optics, Computational chemistry, Antiferromagnetism, Lattice (music)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Magnetic hysteresis, Shape-memory alloy, Martensite, Hysteresis, Copper, Metallurgy, Thermodynamics, Magnetic field, Microstructure, Magnetic anisotropy, Substrate (aquarium), Scattering, Phonon scattering, Substrate coupling, Phonon, Semiconductor, Electron mobility, Coupling (piping), Optoelectronics, Optics, Layer (electronics), Composite material, Exciton, Radiative transfer, Perturbation theory (quantum mechanics)</t>
+          <t>Dipole, Magnetic field, Ferromagnetism, Lorentz transformation, Hexagonal lattice, Quantum mechanics, Phonon, Superconductivity, Anharmonicity, Softening, Soft modes, Dispersion relation, Ferroelectricity, Dielectric, Adhesion, Aluminium, Diffusion, Silicon, Thermal, Solid surface, Composite material, Chemical engineering, Metallurgy, Analytical Chemistry (journal), Thin film</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>223</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>09538984V33I24</t>
+          <t>09538984V35I17</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1499,40 +1499,40 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H25" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dissipative particle dynamics, Dissipative system, Slip (aerodynamics), Statistical physics, Polymer, Mechanics, Core (optical fiber), Materials science, Knot (papermaking), Classical mechanics, Physics, Thermodynamics, Composite material, Scrambling, Quantum decoherence, Mott insulator, Lyapunov exponent, Quantum mechanics, Non-equilibrium thermodynamics, Mesoscopic physics, Quantum, Mathematics, Tetragonal crystal system, Superconductivity, Critical field</t>
+          <t>Materials science, Boron, Crystallography, Atom (system on chip), Transition metal, Chemical bond, Valence electron, Covalent bond, Electron, Chemistry, Octahedron, Condensed matter physics, Band gap, Electronic band structure, Density functional theory, Halide, Polar, Perovskite (structure), Polarization (electrochemistry), Distortion (music), Physics, Crystal structure, Quantum mechanics, Inorganic chemistry, Physical chemistry</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Diffraction, Synchrotron radiation, Symmetry (geometry), Field (mathematics), Transformation (genetics), Perovskite (structure), Thermal stability, Band gap, Halide, Thermogravimetry, Analytical Chemistry (journal), Differential scanning calorimetry, Chemistry, Mineralogy, Crystallography, Inorganic chemistry, Optoelectronics, Organic chemistry, Context (archaeology), Computer science, Phase (matter), Data science, Nanotechnology, Theoretical physics, Epistemology</t>
+          <t>k-nearest neighbors algorithm, Range (aeronautics), Stiffness, Perspective (graphical), Order (exchange), Stability (learning theory), Dual (grammatical number), Computer science, Artificial intelligence, Composite material, Business, Chemical physics, Colloid, Surface charge, Colloidal particle, Surface (topology), Charged particle, Charge (physics), Nanotechnology, Ion, Geometry, Organic chemistry, Saturn, Astrophysics, Satellite</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>215</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>09538984V33I25</t>
+          <t>09538984V35I18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1541,40 +1541,40 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H26" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I26" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Mesoscopic physics, Frustration, Copolymer, Materials science, Block (permutation group theory), Soft matter, Self-assembly, Geometrical frustration, Nanotechnology, Scale (ratio), Chemical physics, Physics, Polymer, Condensed matter physics, Chemistry, Mathematics, Quantum mechanics, Composite material, Geometry, Physical chemistry, Colloidal gold, Biomolecule, Nanoparticle, Adsorption, Aqueous solution</t>
+          <t>Scalability, Organic molecules, Nanotechnology, Molecule, Substrate (aquarium), Materials science, Organic reaction, Kinetic control, Selectivity, Catalysis, Computer science, Chemistry, Combinatorial chemistry, Chemical physics, Organic chemistry, Boron, Heteroatom, Borophene, Cluster (spacecraft), Doping, Fullerene, Nanomaterials, Computational chemistry, Graphene, Ring (chemistry)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Molecule, Asparagine, Combinatorial chemistry, Organic chemistry, Crystallography, Electronic structure, Density functional theory, Thermodynamics, Computational chemistry, Transformation (genetics), Phase (matter), Atom (system on chip), Monte Carlo method, Alloy, Computer science, Quasiparticle, Covalent bond, Polyvinylpyrrolidone, Fourier transform infrared spectroscopy, Potassium permanganate, Thermal stability, Polyvinyl alcohol, Scanning electron microscope, Chemical engineering, Nuclear chemistry</t>
+          <t>Skyrmion, Physics, Topology (electrical circuits), Winding number, MAJORANA, Topological order, Quantum mechanics, Spin (aerodynamics), Hamiltonian (control theory), Condensed matter physics, Superconductivity, Quantum, Kelvin probe force microscope, Semiconductor, Spectroscopy, Atomic force microscopy, Force spectroscopy, Band bending, Microscopy, Resolution (logic), Optoelectronics, Optics, Relaxation (psychology), Superposition principle, Dielectric</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>09538984V33I26</t>
+          <t>09538984V35I19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1583,40 +1583,40 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H27" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I27" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Dipole, Electrolyte, Valency, Chemistry, Solvent, Ion, Adsorption, Chemical physics, Electron, Halide, Thermodynamics, Physical chemistry, Inorganic chemistry, Physics, Electrode, Organic chemistry, Quantum mechanics, Nanocrystal, Materials science, Polyethylene, Polymer, Intermolecular force, Crystallization, Crystallinity, Nanotechnology</t>
+          <t>Diagonal, Condensed matter physics, Transverse plane, Dispersion (optics), Magnetoresistance, Materials science, Physics, Mathematics, Quantum mechanics, Geometry, Engineering, Magnetic field, Structural engineering, Epitaxy, Heterojunction, Scanning tunneling microscope, Substrate (aquarium), Optoelectronics, Layer (electronics), Chemical vapor deposition, Crystallography, Nanotechnology, Chemistry, Spintronics, Ring (chemistry)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Molecule, Composite material, Molecular beam epitaxy, Epitaxy, Monolayer, Bilayer, Substrate (aquarium), Spintronics, Scanning tunneling microscope, Reflection high-energy electron diffraction, Electron diffraction, Optoelectronics, Condensed matter physics, Diffraction, Layer (electronics), Ferromagnetism, Optics, Antiferromagnetism, Superlattice, Angular momentum, Vortex, Sign (mathematics), Niobium, Interstitial defect, Impurity</t>
+          <t>Magnetic flux, Coupling (piping), Flux (metallurgy), Spin (aerodynamics), Quantum, Loop (graph theory), Persistent current, Electron, Topology (electrical circuits), Electrical engineering, Ferromagnetism, Graphene, Raman spectroscopy, Photoexcitation, Excitation, Raman scattering, Spectroscopy, Optics, Doping, Lattice (music), Perovskite (structure), Cuprate, Atomic orbital, Superconductivity, Antiferromagnetism</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>213</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>09538984V33I27</t>
+          <t>09538984V35I20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1625,40 +1625,40 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H28" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I28" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Thermal conductivity, Phonon, Interatomic potential, Boltzmann equation, Condensed matter physics, Dispersion (optics), Conductivity, Thermodynamics, Materials science, Lattice (music), Thermal, Chemistry, Molecular dynamics, Statistical physics, Computational chemistry, Physics, Physical chemistry, Optics, Antiferromagnetism, Electrical resistivity and conductivity, Kondo effect, Doping, Kondo insulator, Seebeck coefficient, Fermi level</t>
+          <t>Catalysis, MXenes, Platinum, Tin, Hydrogen, Materials science, Gibbs free energy, Chemical physics, Chemical engineering, Hydrogen atom, Hydrogen production, Substrate (aquarium), Nanotechnology, Physical chemistry, Chemistry, Thermodynamics, Alkyl, Organic chemistry, Metallurgy, Ferroelectricity, Antiferroelectricity, Epitaxy, Dipole, Optoelectronics, Engineering physics</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Spin (aerodynamics), Phase diagram, Fermi liquid theory, Phase (matter), Electron, Superconductivity, Superlattice, Heterojunction, Dislocation, Burgers vector, Epitaxy, Thin film, Lattice constant, Crystallography, Diffraction, Composite material, Nanotechnology, Optoelectronics, Layer (electronics), Jellium, Mesoscopic physics, Colloid, Counterion, Chemical physics, Valence (chemistry)</t>
+          <t>Engineering, Dielectric, Ferromagnetism, Condensed matter physics, Doping, Spintronics, Skyrmion, Point reflection, Chirality (physics), Anisotropy, Physics, Symmetry breaking, Quantum mechanics, Spontaneous symmetry breaking, Quantum nonlocality, Plasmon, Surface plasmon, Localized surface plasmon, Excitation, Scattering, Surface plasmon polariton, Nanophotonics, Optics, Quantum, Heterojunction</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O28" t="n">
-        <v>218</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>09538984V33I28</t>
+          <t>09538984V35I21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1667,40 +1667,40 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Catalysis, Rhodium, Particulates, Deposition (geology), Palladium, Diesel particulate filter, Chemistry, X-ray absorption fine structure, Chemical engineering, Gasoline, Catalytic converter, Metallurgy, Materials science, Organic chemistry, Neutron, Neutron scattering, Neutron temperature, Proton, Boron, Range (aeronautics), Amino acid, Thermal conductivity, Phonon, Nanowire, Condensed matter physics</t>
+          <t>Condensed matter physics, Pseudogap, Cuprate, Superconductivity, Physics, Scanning tunneling microscope, Quantum oscillations, Vortex, Scanning tunneling spectroscopy, Fermi surface, Superfluidity, Quantum tunnelling, Magnetic field, Quantum mechanics, Soliton, Topological quantum number, Spin (aerodynamics), Anisotropy, Gallium, Electrical resistivity and conductivity, Lattice (music), Critical field, Fermi level, Magnetization, Coupling (piping)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Atomic mass, Resonator, Conductivity, Nanotechnology, Optoelectronics, Physics, Atomic physics, Beamline, Spectroscopy, Spectrometer, Diamond, XANES, Emission spectrum, Soft X-ray emission spectroscopy, Fluorescence spectroscopy, Optics, X-ray spectroscopy, Photon energy, Photon, Time-resolved spectroscopy, Fluorescence, Spectral line, Interatomic potential, Crystal structure, Crystallography</t>
+          <t>Materials science, Electron, Nuclear physics, Ferromagnetic resonance, Spintronics, Magnetization dynamics, Electric field, Torque, Excitation, Ferromagnetism, Microwave, Magnetic anisotropy, Spin Hall effect, Resonance (particle physics), Spin polarization, Atomic physics, Algorithm, Computer science, Topological defect, Equivalence (formal languages), Plane (geometry), Topology (electrical circuits), Range (aeronautics), Geometry, Mathematics</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
-        <v>219</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>09538984V33I29</t>
+          <t>09538984V35I22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1709,40 +1709,40 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H30" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I30" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Ferrimagnetism, Magnetism, Superconductivity, Magnetic moment, Atomic orbital, Ground state, Electronic structure, Spin (aerodynamics), Density functional theory, Graphene, Magnetization, Materials science, Chemistry, Physics, Magnetic field, Atomic physics, Nanotechnology, Quantum mechanics, Computational chemistry, Electron, Neutron diffraction, Magnetic susceptibility, Crystallography, Paramagnetism</t>
+          <t>Condensed matter physics, Magnetic refrigeration, Paramagnetism, Magnetoresistance, Materials science, Phase transition, Phase (matter), Magnetism, Order and disorder, Spin (aerodynamics), Spin glass, Magnetic field, Chemistry, Physics, Magnetization, Thermodynamics, Quantum mechanics, Molecular dynamics, Crystal (programming language), Statistical physics, Chemical physics, Nanotechnology, Computational chemistry, Computer science, Tetragonal crystal system</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Lithium (medication), Atmospheric temperature range, Stoichiometry, Space group, Diffraction, X-ray crystallography, Crystal structure, Physical chemistry, Thermodynamics, Ferroelectricity, Ab initio, Strain (injury), Ab initio quantum chemistry methods, Optoelectronics, Dielectric, Molecule, Spintronics, Valleytronics, Ferromagnetism, Spin polarization, Monolayer, Manganese, Strain engineering, Antiferromagnetism, Polarization (electrochemistry)</t>
+          <t>Strain (injury), Band gap, Effective mass (spring–mass system), Metastability, Zigzag, Electron mobility, Semiconductor, Strain engineering, Ultimate tensile strength, Crystallography, Optoelectronics, Crystal structure, Composite material, Electron, Field (mathematics), Fermi energy, Dirac (video compression format), Mesoscopic physics, Discretization, Hamiltonian (control theory), Zeeman effect, Quantum, Tight binding, Electronic structure, Mathematics</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>218</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>09538984V33I30</t>
+          <t>09538984V35I23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1751,40 +1751,40 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H31" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I31" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Supercapacitor, Materials science, Electrode, Nanotechnology, Transition metal, Electrochemistry, Energy storage, Electrochemical energy storage, Optoelectronics, Power (physics), Chemistry, Physics, Catalysis, Solvation, Polarizability, Chemical physics, Implicit solvation, Solvation shell, Polarizable continuum model, Density functional theory, Ab initio, Electrochemical potential, Computational chemistry, Thermodynamics, Physical chemistry</t>
+          <t>Figure of merit, Transition metal, Density functional theory, Spintronics, Materials science, Condensed matter physics, Phosphorene, Ferromagnetism, Monolayer, Nanotechnology, Heterojunction, Valleytronics, Doping, Strain engineering, Semiconductor, Optoelectronics, Chemistry, Computational chemistry, Physics, Topological insulator, Ambipolar diffusion, van der Waals force, Quantum Hall effect, Realization (probability), Magnetic field</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Ion, Molecule, Skyrmion, Obstacle, Function (biology), Work (physics), Topology (electrical circuits), Condensed matter physics, Mathematics, Quantum mechanics, Combinatorics, Superconductivity, Spectroscopy, Absorption (acoustics), Absorption spectroscopy, X-ray absorption spectroscopy, Thin film, Analytical Chemistry (journal), Optics, Composite material, Dissipative system, Non-equilibrium thermodynamics, Robustness (evolution), Statistical physics, Complex system</t>
+          <t>Graphene, Topology (electrical circuits), Quantum mechanics, Electron, Electrical engineering, Phase (matter), Phase change, Engineering physics, Boron nitride, Ferroelectricity, Bilayer, Electric field, Distortion (music), Boron, Dielectric, Membrane, Binding energy, Antiferromagnetism, Spectral line, Fermi level, Photoemission spectroscopy, Anderson impurity model, Kondo effect, Atomic physics, Electrical resistivity and conductivity</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>208</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>09538984V33I31</t>
+          <t>09538984V35I24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1793,40 +1793,40 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H32" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I32" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Domain wall (magnetism), Condensed matter physics, Materials science, Excitation, Anisotropy, Magnetic domain, Perpendicular, Acoustic wave, Domain (mathematical analysis), STRIPS, Surface (topology), Physics, Acoustics, Optics, Magnetic field, Magnetization, Composite material, Geometry, Epitaxy, Optoelectronics, Photoconductivity, Heterojunction, Fluence, Saturation (graph theory), Layer (electronics)</t>
+          <t>Monolayer, Epitaxy, Materials science, Semiconductor, Condensed matter physics, Band gap, Heterojunction, Crystallography, Nanotechnology, Optoelectronics, Chemistry, Layer (electronics), Physics, Angle-resolved photoemission spectroscopy, Antiferromagnetism, Electronic structure, Density functional theory, Photoemission spectroscopy, Electronic band structure, Hexagonal crystal system, Magnetic structure, X-ray photoelectron spectroscopy, Nuclear magnetic resonance, Magnetic field, Magnetization</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Laser, Nanotechnology, In situ, Soft materials, Morphology (biology), Soft X-rays, Scattering, Soft matter, Soft chemistry, Soft tissue, Chemistry, Geology, Physical chemistry, Organic chemistry, Paleontology, Electric field, Adhesion, Adhesive, Ionic bonding, Surface force, Cylinder, Field (mathematics), Mechanics, Mechanical engineering, Ion</t>
+          <t>Quantum mechanics, Cumulant, Mathematics, Hubbard model, Statistics, Quasicrystal, Ultrasonic sensor, Type (biology), Mathematical analysis, Acoustics, Geology, Ground state, Multiplet, Jahn–Teller effect, Specific heat, Degeneracy (biology), Heat capacity, Entropy (arrow of time), Context (archaeology), Thermodynamics, Ion, Atomic physics, Spectral line, Quasiparticle, Pairing</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O32" t="n">
-        <v>218</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>09538984V33I32</t>
+          <t>09538984V35I25</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1835,40 +1835,40 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H33" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Seebeck coefficient, Band gap, Hamiltonian (control theory), Topology (electrical circuits), Materials science, Physics, Thermoelectric effect, Quantum mechanics, Mathematics, Quantum, Computer science, Atomic orbital, Curvature, Cubic harmonic, Berry connection and curvature, Slater-type orbital, Geometry, Linear combination of atomic orbitals, Geometric phase, Raman spectroscopy, Polymer, Scale (ratio), Composite material, Chemical physics</t>
+          <t>Spintronics, Materials science, Nanotechnology, Piezoelectricity, Electronics, Monolayer, Semiconductor, Schottky barrier, Engineering physics, Condensed matter physics, Optoelectronics, Physics, Electrical engineering, Engineering, Diode, Ferromagnetism, Ultrashort pulse, Characterization (materials science), Chemical physics, Femtosecond, Delocalized electron, Chemistry, Optics, Single crystal, High pressure</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Chemistry, Optics, Topological insulator, Compressed sensing, Nanotechnology, Artificial intelligence, Colloidal gold, Nanoparticle, Ferromagnetism, Torque, Spin-transfer torque, Conductance, Current (fluid), Electrical engineering, Engineering, Magnetic field, Magnetization, Thermodynamics, Electrocatalyst, Dielectric spectroscopy, Porosity, Platinum, Rotating disk electrode, Electrochemistry, Electrode</t>
+          <t>Crystallography, Thermodynamics, Hermitian matrix, Zeeman effect, Eigenvalues and eigenvectors, Fermi Gamma-ray Space Telescope, Coalescence (physics), Spin–orbit interaction, Quantum mechanics, Degenerate energy levels, Magnetic field, Graphene, Terahertz radiation, Lasing threshold, Waveguide, Electromagnetic radiation, Laser, Scattering, Enhanced Data Rates for GSM Evolution, Gallium, Topology (electrical circuits), Mathematics, Telecommunications, Computer science, Polaron</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
-        <v>221</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>09538984V33I33</t>
+          <t>09538984V35I26</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1877,40 +1877,40 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H34" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I34" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Polarization (electrochemistry), Ultrashort pulse, Electron, Laser, Transverse plane, Bilayer graphene, Femtosecond, Perpendicular, Physics, Condensed matter physics, Optics, Atomic physics, Materials science, Graphene, Chemistry, Solvation, Measure (data warehouse), Nanopore, Adsorption, Sorption isotherm, Thermodynamics, Physical chemistry, Nanotechnology, Molecule, Computer science</t>
+          <t>Extended X-ray absorption fine structure, Neon, Diamond anvil cell, Materials science, Hydrostatic pressure, Synchrotron radiation, Absorption spectroscopy, Absorption edge, Beamline, Synchrotron, X-ray absorption spectroscopy, Octahedron, K-edge, Spectroscopy, Surface-extended X-ray absorption fine structure, Absorption (acoustics), Analytical Chemistry (journal), Crystallography, Optics, Chemistry, Atomic physics, Band gap, Diffraction, Crystal structure, Argon</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Organic chemistry, Conductance, Magnetic field, Planar, Scattering, Field (mathematics), Boundary (topology), Ballistic conduction, Spin valve, Zigzag, Spin (aerodynamics), Quantum tunnelling, Coupling (piping), Ferromagnetism, Spin–orbit interaction, Spin polarization, Magnetization, Geometry, Quantum mechanics, Supersolid, Phase diagram, Boson, Kinetic energy, Quantum, Quantum Monte Carlo</t>
+          <t>Thermodynamics, Physics, Beam (structure), Optoelectronics, Composite material, Fermion, Spintronics, Condensed matter physics, Monolayer, Spin (aerodynamics), Topology (electrical circuits), Symmetry (geometry), Fermi level, Quantum mechanics, Geometry, Nanotechnology, Ferromagnetism, Crystallization, Selenium, Amorphous solid, High pressure, Ambient pressure, Metallurgy, Chromatography, Coupling (piping)</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O34" t="n">
-        <v>220</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>09538984V33I34</t>
+          <t>09538984V35I27</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1919,40 +1919,40 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H35" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I35" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Phonon, Thermal conductivity, Thermal conduction, Dielectric, Quantum, Thermal, Kubo formula, Heat current, Bimetallic strip, Electrocatalyst, Solvation, Catalysis, Electrochemistry, Electron transfer, Chemical physics, Adsorption, Hydrogen, Chemistry, Valence electron, Nanostructure, Reactivity (psychology), Valence (chemistry), Materials science, Physical chemistry, Nanotechnology</t>
+          <t>Non-equilibrium thermodynamics, Statistical physics, Physics, Active matter, Dynamical systems theory, Density functional theory, Adiabatic process, Computer science, Theoretical physics, Classical mechanics, Quantum mechanics, Materials science, Chemical vapor deposition, van der Waals force, Bilayer, Monolayer, Exciton, Photoluminescence, Stacking, Dielectric, Heterojunction, Nanotechnology, Chemical physics, Bilayer graphene, Graphene</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Electrode, Electron, Molecule, Physics, Atomic orbital, Propagator, Spin (aerodynamics), Condensed matter physics, Coulomb, Magnon, Orbital overlap, Spin–orbit interaction, Quantum mechanics, Atomic physics, Ferromagnetism, Zigzag, Quantum entanglement, Graphene, Dynamics (music), Quantum dynamics, Statistical physics, Mathematics, Quantum phase transition, Quantum discord, Anisotropy</t>
+          <t>Optoelectronics, Condensed matter physics, Chemistry, Magic angle spinning, Crystallography, NMR spectra database, Solid-state nuclear magnetic resonance, Neutron diffraction, Coordination number, Fast ion conductor, Nuclear magnetic resonance spectroscopy, Crystal structure, Phosphorus-31 NMR spectroscopy, Amorphous solid, Ionic bonding, Titanium, Ion, Nuclear magnetic resonance, Spectral line, Physical chemistry, Stereochemistry, Lupinus, Biology, Geography, Botany</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
-        <v>217</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>09538984V33I35</t>
+          <t>09538984V35I28</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1961,40 +1961,40 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I36" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Superconductivity, Materials science, Condensed matter physics, Crystallography, Engineering physics, Chemistry, Physics, Wurtzite crystal structure, Ternary operation, Nitride, Niobium nitride, Semiconductor, Crystal structure, Band gap, Zinc, Optoelectronics, Inorganic chemistry, Nanotechnology, Metallurgy, Computer science, Laser linewidth, Quantum dot, Halide, Perovskite (structure), Metal</t>
+          <t>Semiconductor, Band bending, Bending, Condensed matter physics, Phosphorene, Materials science, Brillouin zone, Plane (geometry), Scattering, Electron, Electron mobility, Band gap, Optoelectronics, Optics, Physics, Composite material, Geometry, Algorithm, Topology (electrical circuits), Crystallography, Computer science, Chemistry, Mathematics, Combinatorics, Guanine</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Quantum mechanics, Laser, Aurivillius, FETI, Ceramic, Dielectric, Lattice (music), Relaxation (psychology), Composite material, Thermodynamics, Ferroelectricity, XANES, Brillouin zone, Spectral line, Absorption (acoustics), Exciton, Quasiparticle, Absorption spectroscopy, Semimetal, Atomic physics, Molecular physics, Optics, Density functional theory, Order (exchange), Third order</t>
+          <t>Proton, DNA damage, Atomic physics, DNA, Ionization, Ion, Photochemistry, Chemical physics, Organic chemistry, Biochemistry, Ising model, Percolation (cognitive psychology), Critical exponent, Phase transition, Exponent, Phase boundary, Boundary (topology), Percolation theory, Percolation threshold, Phase (matter), Quantum mechanics, Mathematical analysis, Metal, Bar (unit), Nitride</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>09538984V33I36</t>
+          <t>09538984V35I29</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H37" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I37" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Manganate, Strontium, Octahedron, Volume (thermodynamics), Volume expansion, Nuclear magnetic resonance, Materials science, Crystallography, Chemistry, Physics, Crystal structure, Thermodynamics, Internal medicine, Medicine, Contrast (vision), Phase contrast microscopy, X-Ray Phase-Contrast Imaging, Phase-contrast imaging, Phase (matter), Optics, Enhanced Data Rates for GSM Evolution, Computer science, Computer vision, Dissipative system, Viscoelasticity</t>
+          <t>Softening, Materials science, Vibration, Stiffness, Hardening (computing), Boundary value problem, Mechanics, Nanostructure, Nano-, Statistical physics, Nanotechnology, Composite material, Mathematics, Physics, Acoustics, Mathematical analysis, Fluoride, Ion, Ionic bonding, Fast ion conductor, Electrical conductor, Ionic conductivity, Lithium (medication), Chemistry, Chemical physics</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Degrees of freedom (physics and chemistry), Inertial frame of reference, Scalar (mathematics), Relaxation (psychology), Equations of motion, Conservation law, Quasiperiodic function, Irrational number, Superlattice, Condensed matter physics, Lattice (music), Coupling strength, Coupling (piping), Mathematics, Geometry, Telecommunications, Neutron reflectometry, Specular reflection, Reflectometry, Scattering, Neutron scattering, Neutron, Polymer, Small-angle neutron scattering, Nuclear physics</t>
+          <t>Inorganic chemistry, Physical chemistry, Electrolyte, Organic chemistry, Electrode, Liquidus, Quenching (fluorescence), Thermodynamics, Thermal expansion, Rare earth, Atmospheric temperature range, Thermal, Absorption (acoustics), Analytical Chemistry (journal), Mineralogy, Metallurgy, Alloy, Fluorescence, Optics, Quackery, Computer science, Data science, World Wide Web, Medicine, Alternative medicine</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="O37" t="n">
-        <v>217</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>09538984V33I37</t>
+          <t>09538984V35I30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2045,40 +2045,40 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I38" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Brownian motion, Exponent, Non-equilibrium thermodynamics, Curse of dimensionality, Algebraic number, Concentric, Projector, SPHERES, Exchange bias, Materials science, Condensed matter physics, Nanoparticle, Anisotropy, Magnetic anisotropy, Nuclear magnetic resonance, Nanotechnology, Magnetization, Physics, Magnetic field, Optics, Fermion, Symmetry (geometry), Charge (physics), Topology (electrical circuits), Topological quantum number</t>
+          <t>Condensed matter physics, Density functional theory, Muon spin spectroscopy, Raman spectroscopy, Metal–insulator transition, Phase transition, Transition metal, Nickel, Chemistry, Materials science, Metal, Physics, Computational chemistry, Quantum mechanics, Graphene, Zigzag, Polarization (electrochemistry), Strain (injury), Transmission (telecommunications), Extensional definition, Shear (geology), Nanotechnology, Geometry, Geology, Composite material</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Topological order, Charge density, Complement (music), Antiferromagnetism, Ferromagnetism, Magnetic moment, Saturation (graph theory), Phase transition, Rare earth, Cubic crystal system, Phase (matter), Quantum mechanics, Neutron diffraction, Inelastic neutron scattering, Magnetic structure, Spin wave, Neutron scattering, Scattering, Diffraction, Terahertz radiation, Excitation, Beamline, Synchrotron radiation, Detector, Far infrared</t>
+          <t>Telecommunications, Computer science, Mathematics, Biology, Seismology, Pseudopotential, Transverse plane, Autocorrelation, Radial distribution function, Statistical physics, Molecular physics, Molecular dynamics, Computational physics, Exciton, van der Waals force, Valleytronics, Oscillator strength, Biexciton, Chemical physics, Ferromagnetism, Physical chemistry, Spintronics, Molecule, Antiferromagnetism, Monolayer</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O38" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>09538984V33I38</t>
+          <t>09538984V35I31</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2087,40 +2087,40 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H39" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I39" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Ferroelectricity, Materials science, Lattice (music), Photovoltaic system, Physics, Engineering, Optoelectronics, Electrical engineering, Dielectric, Scaling, Statistical physics, Ising model, Critical point (mathematics), Critical phenomena, Non-equilibrium thermodynamics, Critical exponent, Phase transition, Mathematics, Quantum mechanics, Mathematical analysis, Photoconductivity, Ultrashort pulse, Crystallite, Optics</t>
+          <t>Granularity, Active matter, Field (mathematics), Statistical physics, Brownian motion, Physics, Theoretical physics, Computer science, Mathematics, Quantum mechanics, Diamond anvil cell, Diamond, High pressure, Limit (mathematics), Materials science, Realization (probability), Nanotechnology, Mechanical engineering, Engineering physics, Engineering, Metallurgy, Superconductivity, Phonon, Condensed matter physics, Graphene</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Laser, Metallurgy, Monolayer, Reactivity (psychology), Chlorine, Phosphine, Resist, Adsorption, Molecule, Dopant, Density functional theory, Doping, Boron, Chemistry, Hydrogen, Silicon, Chlorine atom, Inorganic chemistry, Physical chemistry, Catalysis, Computational chemistry, Nanotechnology, Medicinal chemistry, Layer (electronics), Organic chemistry</t>
+          <t>Thin film, Nanostructure, Chemical physics, Rare earth, Metal, Earth (classical element), Relaxation (psychology), Nickel, Psychology, Mathematical physics, Andreev reflection, Zigzag, Graphene nanoribbons, Quantum wire, Quantum, Ultrashort pulse, Plasmon, Pulse (music), Electron, Magnetic field, Monolayer, Amplitude, Optics, Optoelectronics, Laser</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>09538984V33I39</t>
+          <t>09538984V35I32</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2129,40 +2129,40 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H40" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I40" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Harmonic, Resonator, Coupling (piping), Thermal conductivity, Superconductivity, Harmonic oscillator, Conductance, Condensed matter physics, Electronic circuit, Quantum system, Quantum, Transistor, Physics, Materials science, Topology (electrical circuits), Optoelectronics, Quantum mechanics, Electrical engineering, Engineering, Voltage, Stability (learning theory), Surface (topology), Chemistry, Chemical engineering, Computer science</t>
+          <t>Polyelectrolyte, Non-equilibrium thermodynamics, Pulmonary surfactant, Chemistry, Thermodynamics, Ion-association, Chemical physics, Statistical physics, Physics, Physical chemistry, Aqueous solution, Polymer, Organic chemistry, Pseudopotential, Diffusion, Viscosity, Materials science, Work (physics), Phase (matter), Liquid phase, Liquid liquid, Exponent, Condensed matter physics, Chromatography, Spin wave</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Mathematics, Geometry, Topological insulator, Unitary state, Topological entropy in physics, MAJORANA, Lattice (music), Topological degeneracy, Symmetry protected topological order, Josephson effect, Theoretical physics, Topological order, Topological quantum number, Ribbon, Amorphous solid, Distribution (mathematics), Composite material, Crystallography, Mathematical analysis, Nuclear physics, Engineering physics, Honeycomb, Competition (biology), Charge density wave, Charge (physics)</t>
+          <t>Aperiodic graph, Fractal, Superlattice, Magnetic field, Spin (aerodynamics), Spectral line, Mathematics, Quantum mechanics, Ferromagnetism, Mathematical analysis, Vacancy defect, Strain (injury), Monolayer, Nanotechnology, Medicine, Density functional theory, Melting point, Copper, Dielectric, Dielectric function, Computational chemistry, Metallurgy, Optoelectronics, Composite material, Political science</t>
         </is>
       </c>
       <c r="N40" t="n">
         <v>15</v>
       </c>
       <c r="O40" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>09538984V33I40</t>
+          <t>09538984V35I33</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2171,40 +2171,40 @@
         </is>
       </c>
       <c r="G41" t="n">
+        <v>35</v>
+      </c>
+      <c r="H41" t="n">
         <v>33</v>
       </c>
-      <c r="H41" t="n">
-        <v>40</v>
-      </c>
       <c r="I41" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Electric field, Ferroelectricity, Ultrashort pulse, Amplitude, Pulse (music), Pulse duration, Phase (matter), Condensed matter physics, Materials science, Phase transition, Physics, Optics, Optoelectronics, Dielectric, Quantum mechanics, Interatomic potential, Phonon, Thermal conductivity, Anharmonicity, Thermoelectric materials, Molecular dynamics, Atmospheric temperature range, Anisotropy, Thermodynamics, Chemistry</t>
+          <t>Hermitian matrix, Theoretical physics, Topology (electrical circuits), Physics, Mathematics, Quantum mechanics, Combinatorics, Vanadium, Inorganic chemistry, Oxide, Catalysis, Transition metal, Cobalt, Electrochemistry, Chemistry, Redox, Materials science, Vanadium oxide, Physical chemistry, Electrode, Organic chemistry, Vortex, Supersolid, Fugacity, Condensed matter physics</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Computational chemistry, Thin film, Nanotechnology, Polaron, Monolayer, Transition metal, Spin (aerodynamics), Ising model, Magnetic susceptibility, Antiferromagnetism, Neutron diffraction, Context (archaeology), Magnetic field, Single crystal, Magnetism, Raman spectroscopy, Sulfide, Infrared, Spectral line, Reflectivity, Coupling (piping), Gallium, Lattice (music), Molecular physics, Composite material</t>
+          <t>Meteorology, Phase (matter), Phase diagram, Thermodynamics, Crystallographic defect, Metastability, Voronoi diagram, Symmetry (geometry), Frenkel defect, Diffusion, Band gap, Chemical physics, Geometry, Scanning tunneling microscope, X-ray photoelectron spectroscopy, Photoemission spectroscopy, Epitaxy, Substrate (aquarium), Semiconductor, Orthorhombic crystal system, Electronic structure, Angle-resolved photoemission spectroscopy, Spectroscopy, Thin film, Nanotechnology</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O41" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>09538984V33I41</t>
+          <t>09538984V35I34</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2213,40 +2213,40 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H42" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I42" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Phase diagram, Rare earth, Phase (matter), Condensed matter physics, Materials science, Physics, Quantum mechanics, Metallurgy, Channel (broadcasting), Bottleneck, Dissipative particle dynamics, Particle (ecology), Mechanics, Motion (physics), Topology (electrical circuits), Geometry, Computer science, Classical mechanics, Engineering, Geology, Telecommunications, Mathematics, Electrical engineering, Magnonics, Magnon</t>
+          <t>Orthosilicate, Materials science, Ion, Electrode, Lithium (medication), Manganese, Inorganic chemistry, Chemical engineering, Metallurgy, Chemistry, Nanotechnology, Physical chemistry, Tetraethyl orthosilicate, Engineering, Organic chemistry, Bismuth, Stacking, Stearate, Thin film, Mineralogy, Composite material, Geology, History, Computer science, Condensed matter physics</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Engineering physics, Nanotechnology, Zeeman effect, Spin (aerodynamics), Anisotropy, Magnetic field, Topological insulator, Epitaxy, Raman spectroscopy, X-ray photoelectron spectroscopy, Thin film, Nucleation, Ferromagnetism, Scanning tunneling microscope, Crystallite, Substrate (aquarium), Crystallography, Optoelectronics, Optics, Chemistry, Nuclear magnetic resonance, Layer (electronics), Dielectric, Ergodic theory, Ferroelectricity</t>
+          <t>Topological insulator, Surface states, Degenerate energy levels, Quantum well, Semiconductor, Heterojunction, Band gap, Quantum Hall effect, Substrate (aquarium), Cadmium telluride photovoltaics, Physics, Optoelectronics, Electron, Surface (topology), Optics, Quantum mechanics, Delocalized electron, Charge (physics), Hamiltonian (control theory), Electronic structure, Molecular dynamics, Coupling (piping), Tight binding, Statistical physics, Chemical physics</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O42" t="n">
-        <v>211</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>09538984V33I42</t>
+          <t>09538984V35I35</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2255,40 +2255,40 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H43" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I43" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Skyrmion, Antiferromagnetism, Transformation (genetics), Nanostructure, Condensed matter physics, Materials science, Process (computing), Nanotechnology, Physics, Chemistry, Computer science, Synchrotron radiation, Radiation, Diffraction, Optics, Scattering, Spectroscopy, Beamline, Synchrotron, Computational physics, Beam (structure), Electrification, Adsorption, Interface (matter), Contact electrification</t>
+          <t>Computer science, Software, The Internet, Code (set theory), Join (topology), Source code, Property (philosophy), Internet portal, Data science, Computational science, Software engineering, Management science, World Wide Web, Engineering, Mathematics, Programming language, Ferroelectricity, Heterojunction, Condensed matter physics, Monolayer, Materials science, van der Waals force, Polarization (electrochemistry), Nanotechnology, Optoelectronics</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Charge (physics), Surface charge, Electrostatics, Ion, Superconductivity, Solid solution, Coupling (piping), Lattice (music), Perturbation (astronomy), Crystal (programming language), Density of states, Metal, Crystal structure, Epitaxy, Terahertz radiation, Thin film, Optoelectronics, Rydberg formula, Laser linewidth, Plasmon, Exciton, Atomic physics, Phonon, Principal quantum number, Electron density</t>
+          <t>Chemistry, Physics, Quantum mechanics, Dielectric, Molecule, Physical chemistry, Langevin dynamics, Radius of gyration, Exponent, RADIUS, Polymer, Gyration, Scaling, Nano-, Confined space, Dynamics (music), Container (type theory), Mechanics, Statistical physics, Geometry, Composite material, Mesoscopic physics, Electron, Quantum point contact, Atomic physics</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O43" t="n">
-        <v>215</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>09538984V33I43</t>
+          <t>09538984V35I36</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2297,40 +2297,40 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H44" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I44" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Arrhenius equation, Diffusion, Liquidus, Self-diffusion, Analytical Chemistry (journal), Atmospheric temperature range, Materials science, Nickel, Activation energy, Relaxation (psychology), Viscosity, Quasielastic neutron scattering, Thermodynamics, Chemistry, Neutron scattering, Physical chemistry, Scattering, Small-angle neutron scattering, Alloy, Metallurgy, Magnetoresistance, Magneto, Condensed matter physics, Nuclear magnetic resonance, Physics</t>
+          <t>Perovskite (structure), Photovoltaic system, Charge (physics), Interface (matter), Photoluminescence, Optoelectronics, Materials science, Solar cell, Restructuring, Engineering physics, Chemistry, Electrical engineering, Physics, Engineering, Crystallography, Dielectric, Thin film, Layer (electronics), Doping, Ferroelectricity, Composite material, Nanotechnology, Heterojunction, Ohmic contact, Monolayer</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Magnetic field, Quantum mechanics, Magnon, Ground state, Degeneracy (biology), Degenerate energy levels, Wave function, Antiferromagnetism, Anisotropy, Bound state, Magnetic refrigeration, Magnetization, Process (computing), Computer science, Connection (principal bundle), Electrochemistry, Amorphous solid, Carbon fibers, Carbon film, Chemical engineering, Amorphous carbon, Thin film, Nanotechnology, Composite material, Electrode</t>
+          <t>Absorption (acoustics), Electronic structure, Condensed matter physics, Stacking, Ultraviolet, Band gap, Transverse plane, Transistor, Spin (aerodynamics), Voltage, Quantum mechanics, Structural engineering, Hexafluoropropylene, Bilayer, Polymer, Analytical Chemistry (journal), Membrane, Organic chemistry, Copolymer, Law, Political science, Constitutional law, Ribbon, Dirac (video compression format), Fermi level</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O44" t="n">
-        <v>221</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>09538984V33I44</t>
+          <t>09538984V35I37</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H45" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I45" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Spinel, Stoichiometry, Diffusion, Oxygen, Crystallography, Materials science, Manganese, X-ray crystallography, Chemistry, Physical chemistry, Thermodynamics, Physics, Diffraction, Metallurgy, Condensed matter physics, Quantum spin liquid, Antiferromagnetism, Spins, Fermion, Spin (aerodynamics), Electron, Phonon, Heat capacity, Quantum mechanics, Spin polarization</t>
+          <t>Thermoelectric effect, Thermoelectric materials, Environmentally friendly, Work (physics), Materials science, Substitution (logic), Nanotechnology, Interference (communication), Engineering physics, Computer science, Mechanical engineering, Engineering, Physics, Telecommunications, Thermodynamics, Mesoscopic physics, Scattering, Interferometry, Geometric phase, Beam splitter, Mach–Zehnder interferometer, Graphene, Electron, Weak localization, Graphene nanoribbons</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Kinematics, Potentiostat, Curvature, Potential energy, Interatomic potential, Computer science, Molecular dynamics, Energy (signal processing), Algorithm, Biological system, Classical mechanics, Geometry, Mathematics, Computational chemistry, Electrochemistry, Azulene, Aromaticity, Adsorption, Naphthalene, Surface modification, Density functional theory, Ab initio, Chemical physics, Molecule, Photochemistry</t>
+          <t>Magnetic field, Condensed matter physics, Optics, Quantum mechanics, Magnetoresistance, Dynamics (music), Polymer, Block (permutation group theory), Dielectric, Dielectric spectroscopy, Chemical physics, Chemistry, Composite material, Mathematics, Optoelectronics, Physical chemistry, Acoustics, Geometry, Ultrafast laser spectroscopy, Characterization (materials science), Spectroscopy, Transient (computer programming), Absorption spectroscopy, Absorption (acoustics), Analytical Chemistry (journal)</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O45" t="n">
-        <v>216</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>09538984V33I45</t>
+          <t>09538984V35I38</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2381,40 +2381,40 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I46" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Superconductivity, Neutron scattering, Cuprate, Isotropy, Spin (aerodynamics), Resonance (particle physics), Scattering, Coupling (piping), Magnon, Brillouin zone, Spin wave, Condensed matter physics, Physics, Anisotropy, Spins, Antiferromagnetism, Heisenberg model, Field (mathematics), Quantum mechanics, Ferromagnetism, Crystal structure prediction, Symmetry (geometry), Crystal (programming language), Curse of dimensionality, Crystal structure</t>
+          <t>Amorphous solid, Nanocrystalline material, Mesoscopic physics, Materials science, Chalcogenide, Molecular physics, Diffraction, Transmission electron microscopy, Optics, Chemical physics, Crystallography, Chemistry, Optoelectronics, Nanotechnology, Physics, Condensed matter physics, Fumed silica, Rheology, Particle (ecology), Bubble, Colloid, Microstructure, Composite material, Particle size, Chemical engineering</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Algorithm, Computer science, Artificial intelligence, Mathematics, Geometry, Chemistry, Crystallography, Magnetism, Perovskite (structure), Spin–orbit interaction, Transition metal, Realization (probability), Magnetic moment, Atomic orbital, Singlet state, Electron, Materials science, Thermodynamics, Monolayer, Topology (electrical circuits), Layer (electronics), Nanotechnology, Combinatorics, Band gap, Electron energy loss spectroscopy</t>
+          <t>Anode, MXenes, Monolayer, Doping, Battery (electricity), Open-circuit voltage, Ion, Graphene, Diffusion, Conductivity, Analytical Chemistry (journal), Density functional theory, Voltage, Electrode, Physical chemistry, Electrical engineering, Computational chemistry, Organic chemistry, Thermodynamics, Algorithm, Substrate (aquarium), Rotation (mathematics), Geometry, Artificial intelligence, Computer science</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O46" t="n">
-        <v>215</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>09538984V33I46</t>
+          <t>09538984V35I39</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2423,40 +2423,40 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I47" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ferroelectricity, Materials science, Metal, Phase (matter), Condensed matter physics, Electrical resistivity and conductivity, Phase transition, Dielectric, Metallurgy, Optoelectronics, Chemistry, Dopant, Aluminium, Halide, Density functional theory, Silicon, Molecule, Atomic units, Scanning tunneling microscope, Inorganic chemistry, Nanotechnology, Computational chemistry, Doping, Organic chemistry, Quasiparticle</t>
+          <t>Monolayer, Materials science, Thermoelectric effect, Anisotropy, Condensed matter physics, Engineering physics, Crystallography, Nanotechnology, Optics, Physics, Thermodynamics, Chemistry, Phase transition, Electrolyte, Ionic liquid, Amorphous solid, Glass transition, Chemical physics, Physical chemistry, Organic chemistry, Polymer, Silicene, Transfer matrix, Graphene, Hamiltonian (control theory)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Physics, Quantum critical point, Critical point (mathematics), Quantum phase transition, Spin (aerodynamics), Fixed point, Condensation, Quantum, Quantum mechanics, Thermodynamics, Superconductivity, Mathematics, Passivation, Hydrogen sulfide, Hydrogen, Type (biology), Chemical engineering, Sulfur, Layer (electronics), Geology, Engineering, Pyrrhotite, Antiferromagnetism, Magnetization, Vacancy defect</t>
+          <t>Transmission coefficient, Transfer-matrix method (optics), Dirac (video compression format), Bound state, Matrix (chemical analysis), Transmission (telecommunications), Quantum mechanics, Mathematics, Computer science, Mathematical optimization, Zigzag, Antiparallel (mathematics), Spintronics, Graphyne, Molecular electronics, Density functional theory, Spin (aerodynamics), Spin states, Molecule, Computational chemistry, Ferromagnetism, Magnetic field, Electron mobility, Band gap, HOMO/LUMO</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>218</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>09538984V33I47</t>
+          <t>09538984V35I40</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2465,40 +2465,40 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H48" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I48" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Gadolinium gallium garnet, Gallium, Gadolinium, Magnon, Spin (aerodynamics), Excitation, Magnetic field, Field (mathematics), Platinum, Palladium, Helmholtz free energy, Copper, Constant (computer programming), Common emitter, Plasmon, Quantum, Energy transport, Nanostructure, Physics, Optoelectronics, Condensed matter physics, Materials science, Nanotechnology, Quantum mechanics, Engineering physics</t>
+          <t>Topological insulator, Topology (electrical circuits), Square lattice, Tetrahedron, Square root, Physics, Diamond, Hamiltonian (control theory), Condensed matter physics, Materials science, Mathematics, Geometry, Combinatorics, Ising model, Ohmic contact, Heterojunction, Spintronics, Ferromagnetism, Schottky barrier, Fermi level, Schottky diode, Graphene, Density functional theory, Magnetic semiconductor, Magnetic moment</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Supercooling, Nucleation, Crystallization, Thermodynamics, Shearing (physics), Shear rate, Phase diagram, Viscosity, Liquid crystal, Phase (matter), Chemistry, Organic chemistry, Surface (topology), Computer science, Mathematics, Geometry, Lattice (music), Topology (electrical circuits), Quantum phase transition, Phase transition, Combinatorics, Electric field, Charge carrier, Charge (physics), Electrical resistivity and conductivity</t>
+          <t>Semiconductor, Nanotechnology, Optoelectronics, Electron, Chemistry, Computational chemistry, Diode, Layer (electronics), Scanning tunneling microscope, Dopant, X-ray photoelectron spectroscopy, Nitrogen, Scanning tunneling spectroscopy, Doping, Atomic units, Analytical Chemistry (journal), Chemical engineering, Organic chemistry, Phase (matter), Phase imaging, Space (punctuation), Optics, Computer science, Precession, Antiferromagnetism</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O48" t="n">
-        <v>216</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>09538984V33I48</t>
+          <t>09538984V35I41</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2507,40 +2507,40 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H49" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I49" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Monolayer, Adsorption, Molybdenum, Diselenide, Molecule, Materials science, Inorganic chemistry, Transformer oil, Chemistry, Transformer, Nanotechnology, Organic chemistry, Metallurgy, Electrical engineering, Selenium, Phosphorene, Heterojunction, Absorbance, Optoelectronics, Photocatalysis, Band gap, Absorption (acoustics), Electron acceptor, Visible spectrum, Absorption edge</t>
+          <t>Epitaxy, Materials science, Anisotropy, Condensed matter physics, Superconductivity, Physics, Optics, Nanotechnology, Latin Americans, Soft matter, Political science, Engineering, Law, Substrate (aquarium), Oxide, Oxygen, Mixing (physics), Chemistry, Metal, Monolayer, Vanadium, Stoichiometry, Context (archaeology), Cationic polymerization, Vanadium oxide</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Strain (injury), Photochemistry, Optics, Physics, Composite material, Catalysis, Perspective (graphical), Sample (material), Scattering, Synchrotron, Spectroscopy, Engineering physics, Computer science, Astronomy, Metamaterial, Microstructure, Mathematics, Plasmon, Graphene nanoribbons, Condensed matter physics, Quasiparticle, Enhanced Data Rates for GSM Evolution, Electron, Graphene, Superconductivity</t>
+          <t>Chemical physics, Inorganic chemistry, Chemical engineering, Crystallography, Physical chemistry, Helium, Thermal conductivity, Liquid helium, Interfacial thermal resistance, Superfluidity, Helium-4, Superfluid helium-4, Lambda point refrigerator, Thermal resistance, Thermodynamics, Work (physics), Thermal, Helium-3, Phase (matter), Atomic physics, Composite material, Pyroelectricity, Figure of merit, Responsivity, Optoelectronics</t>
         </is>
       </c>
       <c r="N49" t="n">
         <v>17</v>
       </c>
       <c r="O49" t="n">
-        <v>213</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>09538984V33I49</t>
+          <t>09538984V35I42</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2549,40 +2549,40 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H50" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I50" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Heterojunction, Nanotechnology, Spintronics, Photonics, Materials science, Template, Optoelectronics, Computer science, Physics, Brillouin Spectroscopy, Phospholipid, Suspension (topology), Chemistry, Vesicle, Atmospheric temperature range, Analytical Chemistry (journal), Membrane, Phase (matter), Aqueous solution, Spectroscopy, Thermodynamics, Chromatography, Brillouin scattering, Optics, Organic chemistry</t>
+          <t>Linear polarization, Polarization (electrochemistry), Anisotropy, Photoelectric effect, Spectroscopy, Atomic physics, Linear dichroism, Photoemission spectroscopy, Undulator, Optics, Materials science, Molecular physics, Physics, Condensed matter physics, X-ray photoelectron spectroscopy, Chemistry, Nuclear magnetic resonance, Laser, Crystallography, Singularity, Curvature, Absorption (acoustics), Topology (electrical circuits), Mathematics, Geometry</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Electron, Semiconductor, Kondo effect, Quantum well, Thermal conduction, Laser, Quantum mechanics, Zeeman effect, Superconductivity, Antiferromagnetism, Magnetism, Spins, Magnon, Magnetic moment, Critical field, Magnetic field, Field (mathematics), Ion, Ferromagnetism, Nuclear physics, Liquid crystal, Isotropy, Bistability, Surface tension</t>
+          <t>Combinatorics, Statistical mechanics, Statistical physics, Mechanics, Classical mechanics, Spintronics, Graphene, Honeycomb, Coupling (piping), Spin (aerodynamics), Nanotechnology, Ferromagnetism, Algorithm, Computer science, Crystallite, Analytical Chemistry (journal), Spinel, Lattice constant, Nanoparticle, Dielectric, Debye model, Ferrite (magnet), Composite material, Diffraction, Metallurgy</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O50" t="n">
-        <v>216</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>09538984V33I50</t>
+          <t>09538984V35I43</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2591,40 +2591,40 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I51" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Spin (aerodynamics), Order (exchange), Work (physics), Physics, Group (periodic table), Rotation (mathematics), Condensed matter physics, Mathematics, Quantum mechanics, Geometry, Thermodynamics, Business, Ultrashort pulse, Laser, Optoelectronics, Black phosphorus, Materials science, Semiconductor, Optics, Diffraction, X-ray crystallography, Crystallography, High pressure, Chemistry, Engineering physics</t>
+          <t>Antisymmetric relation, Physics, Symmetry (geometry), Piezoelectricity, Transverse plane, Condensed matter physics, Electric field, Amplitude, Barium titanate, Optics, Quantum mechanics, Geometry, Acoustics, Mathematics, Algorithm, Materials science, Computer science, Modular design, Programming language, Janus, Spintronics, Heterojunction, Semiconductor, Spin (aerodynamics), Monolayer</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Overpotential, Electron transfer, Steric effects, Polarization (electrochemistry), Elementary reaction, Reaction rate, Dipole, Kinetics, Solvent effects, Computational chemistry, Chemical physics, Physical chemistry, Solvent, Catalysis, Electrode, Stereochemistry, Electrochemistry, Organic chemistry, Poling, Ion, Thermal, Limiting, Anisotropy, Confusion, Dislocation</t>
+          <t>Fermi level, Nanotechnology, Optoelectronics, Magnetoresistance, Ferromagnetism, Lattice (music), Magnetic field, Tetragonal crystal system, Vacancy defect, Superconductivity, Crystallographic defect, Stoichiometry, Instability, Phonon, Crystallography, Chemistry, Crystal structure, Mechanics, Physical chemistry, Halide, Perovskite (structure), Halogen, Bromine, Chlorine, Solar cell</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O51" t="n">
-        <v>214</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>09538984V34I1</t>
+          <t>09538984V35I44</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2633,40 +2633,40 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="I52" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Scanning tunneling microscope, Kelvin probe force microscope, Work function, Copper, Cerium oxide, Catalysis, Oxide, Redox, Copper oxide, Chemistry, Low-energy electron diffraction, Transition metal, Cerium, Inorganic chemistry, Metal, Materials science, Crystallography, Nanotechnology, Electron diffraction, Atomic force microscopy, Diffraction, Reverse Monte Carlo, Neutron diffraction, Deuterium, Neutron scattering</t>
+          <t>Skyrmion, Condensed matter physics, Magnetic field, Hall effect, Magnetoresistance, Electrical resistivity and conductivity, Lorentz force, Electron, Materials science, Magnetization, Magnet, Physics, Superconductivity, Quantum computer, Spin (aerodynamics), Quantum mechanics, Quantum, Mean squared displacement, Statistical physics, Phase diagram, Invariant (physics), Scale invariance, Radial distribution function, Molecular dynamics, Distribution function</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Monte Carlo method, Scattering, Phase (matter), Rietveld refinement, Molecule, Pair distribution function, Biological small-angle scattering, Small-angle neutron scattering, Crystal structure, Physics, Atomic physics, Optics, Organic chemistry, Quantum mechanics, Condensed matter physics, Phonon, Electron mobility, Semiconductor, Mobility model, Optoelectronics, Electrical resistivity and conductivity, Variable-range hopping, Doping, Ion, Raman spectroscopy</t>
+          <t>Distribution (mathematics), Diagram, Lennard-Jones potential, Thermodynamics, Phase (matter), Mathematical physics, Mathematics, Mathematical analysis, Statistics, Constraint (computer-aided design), Mechanics, Mechanical system, Kinematics, Classical mechanics, Active matter, Intensity (physics), Chemistry, Mechanical engineering, Engineering, Antiferromagnetism, Figure of merit, Scattering, Magnetic moment, Charge (physics), Moment (physics)</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O52" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>09538984V34I2</t>
+          <t>09538984V35I45</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2675,40 +2675,40 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I53" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Dosimeter, Irradiation, Materials science, Ion, Doping, Electron, Saturation (graph theory), Copper, Radiochemistry, Analytical Chemistry (journal), Radiation, Atomic physics, Chemistry, Optics, Physics, Nuclear physics, Optoelectronics, Metallurgy, Mathematics, Supercooling, Metastability, Amorphous solid, Polyamorphism, Polymorphism (computer science), Phase (matter)</t>
+          <t>Oxide, Microsecond, Desorption, Chemical physics, Hydrogen, Chemistry, Impurity, Outgassing, Adsorption, Density functional theory, Materials science, Analytical Chemistry (journal), Physical chemistry, Computational chemistry, Vicinal, Angle-resolved photoemission spectroscopy, Molecular beam epitaxy, Band gap, Graphene nanoribbons, X-ray photoelectron spectroscopy, Graphene, Condensed matter physics, Electronic band structure, Wide-bandgap semiconductor, Optoelectronics</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Phase transition, Artificial neural network, Glass transition, Thermodynamics, Chemical physics, Computer science, Crystallography, Artificial intelligence, Organic chemistry, Composite material, Polymer, van der Waals force, Component (thermodynamics), Adsorption, Density functional theory, Range (aeronautics), Hybrid functional, Fock space, Dispersion (optics), Metal, Condensed matter physics, Molecule, Quantum mechanics, Physical chemistry, Hydrostatic pressure</t>
+          <t>Epitaxy, Electronic structure, Nanotechnology, Nuclear magnetic resonance, Physics, Layer (electronics), Coulomb, Boundary (topology), Geometry, Topology (electrical circuits), Quantum mechanics, Mathematics, Mathematical analysis, Combinatorics, Electron, Coupling (piping), Spin (aerodynamics), Orbit (dynamics), Arc (geometry), NODAL, Mathematical physics, Biology, Genetics, Engineering, Aerospace engineering</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O53" t="n">
-        <v>218</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>09538984V34I3</t>
+          <t>09538984V35I46</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2717,40 +2717,40 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I54" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Antiferromagnetism, Magnetoresistance, Tetragonal crystal system, Electrical resistivity and conductivity, Hall effect, Magnetization, Magnetism, Skyrmion, Magnetic field, Materials science, Physics, Crystal structure, Chemistry, Crystallography, Quantum mechanics, Monolayer, Oxide, Transition metal, Redox, Lattice (music), Metal, Mixing (physics), Corundum, Chemical physics</t>
+          <t>Dielectric, Multiferroics, Condensed matter physics, Materials science, Dielectric spectroscopy, Dipole, Dielectric response, Ferroelectricity, Physics, Optoelectronics, Quantum mechanics, Ferromagnetism, Antiferromagnetism, Oxide, Magnetism, Monolayer, Density functional theory, Metal, Electronic structure, Substrate (aquarium), Phase (matter), Layer (electronics), Deposition (geology), Thin film, Chemical physics</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Inorganic chemistry, Mineralogy, Catalysis, Permeation, Kinetic energy, Diffusion, Particle (ecology), Work (physics), Nanotechnology, Atomic physics, Thermodynamics, Membrane, Zeeman effect, Quantum oscillations, Landau quantization, Electron, Line (geometry), Spectral line, Superconductivity, Fermi surface, Geometry, Maxima and minima, Energy landscape, Potential energy, Gaussian</t>
+          <t>Crystallography, Nanotechnology, Chemistry, Metallurgy, Computational chemistry, Cluster analysis, Statistical physics, Supercooling, Representation (politics), Phase space, Biological system, Computer science, Artificial intelligence, Thermodynamics, Strain (injury), Dynamical heterogeneity, Composite material, Biology, Glass transition, Anatomy, Neutron diffraction, Enthalpy, Momentum transfer, Range (aeronautics), Short range order</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O54" t="n">
-        <v>222</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>09538984V34I4</t>
+          <t>09538984V35I47</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2759,40 +2759,40 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="I55" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Surface tension, van der Waals force, Molecular dynamics, Binary number, Cauchy stress tensor, Work (physics), Computation, Tensor (intrinsic definition), Surface stress, Force field (fiction), Surface (topology), Statistical physics, Stress (linguistics), Chemistry, Field (mathematics), Thermodynamics, Chemical physics, Classical mechanics, Computational chemistry, Physics, Physical chemistry, Molecule, Mathematics, Geometry, Quantum mechanics</t>
+          <t>Materials science, Algorithm, Computer science, Photocathode, Adsorption, Nanowire, Thin film, Work function, Atomic orbital, Absorption (acoustics), Analytical Chemistry (journal), Layer (electronics), Nanotechnology, Electron, Physical chemistry, Chemistry, Physics, Composite material, Scanning tunneling microscope, HOMO/LUMO, Copper, Density functional theory, Chemical physics, Molecule, Dispersion (optics)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Surface energy, Organic chemistry, Conductivity, Trapping, Ion, Diffusion, Spectral line, Materials science, Electrospinning, Nanofiber, Superconductivity, Nanotechnology, Composite material, Polymer, Condensed matter physics, Fermi level, Photoemission spectroscopy, Mott insulator, Ground state, Electronic structure, Angle-resolved photoemission spectroscopy, Electronic band structure, Band gap, Valence (chemistry), Density of states</t>
+          <t>Intermolecular force, Passivation, Band gap, Molecular physics, Crystallography, Computational chemistry, Optics, Optoelectronics, Heterojunction, Discretization, Classification of discontinuities, Convergence (economics), Dielectric, Fermi gas, Poisson's equation, Effective mass (spring–mass system), Condensed matter physics, Mathematical analysis, Mathematics, Quantum mechanics, Coulomb blockade, Quantum dot, Coulomb, Coulomb's constant, Dwell time</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O55" t="n">
-        <v>216</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>09538984V34I5</t>
+          <t>09538984V35I48</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2801,40 +2801,40 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I56" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Rotation formalisms in three dimensions, Ferromagnetism, Condensed matter physics, Quasiparticle, Nonlinear system, Physics, Formalism (music), Magnetoresistance, Non-equilibrium thermodynamics, Electric field, Quadratic equation, Hall effect, Photocurrent, Quantum mechanics, Mathematics, Magnetic field, Geometry, Monolayer, Materials science, Phonon, Exciton, Poisson's ratio, Dielectric, Ultimate tensile strength, Molecular physics</t>
+          <t>Antiferromagnetism, Lattice (music), Hexagonal lattice, Ferromagnetism, Magnetization, Condensed matter physics, Physics, Materials science, Magnetic field, Quantum mechanics, Overpotential, Water splitting, Oxygen evolution, Catalysis, Transition metal, Doping, Population, Nanotechnology, Chemical engineering, Chemistry, Physical chemistry, Optoelectronics, Photocatalysis, Electrochemistry, Monolayer</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Nanotechnology, Composite material, Chemistry, Optoelectronics, Poisson distribution, Space charge, Diffusion, Space (punctuation), Ion, Field (mathematics), Distribution (mathematics), Charge (physics), Weyl semimetal, Semimetal, Chiral anomaly, Bismuth, Electrical resistivity and conductivity, Weak localization, Anomaly (physics), Massless particle, Alloy, Fermion, Metallurgy, Phenylene, Annealing (glass)</t>
+          <t>Epitaxy, Superlattice, Scanning tunneling microscope, Semiconductor, Chalcogen, Substrate (aquarium), Coupling (piping), Crystallography, Layer (electronics), Raman spectroscopy, Titanium dioxide, Adsorption, Formaldehyde, Analytical Chemistry (journal), Toluene, Xylene, Thin film, Spectroscopy, Surface roughness, Scanning electron microscope, Organic chemistry, Optics, Composite material, Point reflection, Berry connection and curvature</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O56" t="n">
-        <v>212</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>09538984V34I6</t>
+          <t>09538984V35I49</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2843,40 +2843,40 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="I57" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Doping, Monoclinic crystal system, Thermoelectric effect, Condensed matter physics, Phonon, Hydrostatic pressure, Materials science, Ternary operation, Structural stability, Lattice (music), Thermoelectric materials, Crystal structure, Chemistry, Physics, Crystallography, Thermodynamics, Band gap, Phosphor, Lanthanide, Semiconductor, Electronic structure, Valence (chemistry), Electronic band structure, Impurity, Direct and indirect band gaps</t>
+          <t>Quantum dot, Semiconductor, Nanomaterials, Materials science, Heterojunction, Multiple exciton generation, Optoelectronics, Absorption (acoustics), Photon, Nanotechnology, Quantum well, Nanocrystal, Band gap, Two-photon absorption, Nonlinear optics, Nonlinear system, Physics, Optics, Laser, Quantum mechanics, Cluster (spacecraft), Random hexamer, Molecular dynamics, Dimer, Chemical physics</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Perovskite (structure), Optoelectronics, Ion, Monolayer, Vacancy defect, Dopant, Ferromagnetism, Density functional theory, Crystallographic defect, Chemical physics, Nanotechnology, Computational chemistry, Magnetization, Phase diagram, Anisotropy, Magnetic anisotropy, Phase (matter), Phase transition, Field (mathematics), Magnetic field, Optics, Hydraulics, Electrical conduit, Non-Newtonian fluid, Fluid dynamics</t>
+          <t>Chemistry, Surface (topology), Crystallography, Computational chemistry, Geometry, Ferroelectricity, Group (periodic table), Condensed matter physics, Dielectric, Algorithm, Artificial intelligence, Computer science, Translational symmetry, Fermion, Angular momentum, Phase transition, Vanadium dioxide, Ascorbic acid, Vanadium, Phase (matter), Carbon dioxide, Inorganic chemistry, Food science, Thermodynamics, Organic chemistry</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>09538984V34I7</t>
+          <t>09538984V35I50</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2885,40 +2885,40 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H58" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="I58" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Superexchange, Antiferromagnetism, Chemistry, Hybrid functional, Condensed matter physics, Ferromagnetism, Wave function, Exchange interaction, Valence (chemistry), Density functional theory, Atomic physics, Physics, Computational chemistry, Valleytronics, Zeeman effect, Berry connection and curvature, Polarization (electrochemistry), Magnetization, Magnetic field, Semiconductor, Doping, Curvature, Pauli exclusion principle, Kinetic energy, Electronic structure</t>
+          <t>van der Waals force, Heterojunction, Stacking, Thermal conductivity, Condensed matter physics, Materials science, Monolayer, Phonon, Anisotropy, Chemistry, Nanotechnology, Physics, Optics, Composite material, Molecule, Vanadium, Doping, Dopant, Selenium, Band gap, Chemical vapor deposition, Density functional theory, Analytical Chemistry (journal), Optoelectronics, Computational chemistry</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Electron, Chalcopyrite, Band gap, Materials science, Quantum mechanics, Charge (physics), Calibration, Stability (learning theory), Characterization (materials science), Charge density, Series (stratigraphy), Bilayer, Heterojunction, Epitaxy, Anisotropy, Lattice (music), Coupling (piping), Substrate (aquarium), Focus (optics), Domain (mathematical analysis), Phase (matter), Phase transition, Ferroelectricity, Field (mathematics), Dielectric</t>
+          <t>Metallurgy, Tensor (intrinsic definition), Hamiltonian (control theory), Spin (aerodynamics), Quantum mechanics, Mathematics, Geometry, Icosahedral symmetry, Crystallography, Algorithm, Computer science, Quantum Hall effect, Cadmium telluride photovoltaics, Thermal, Enhanced Data Rates for GSM Evolution, Quantum well, Dissipation, Magnetic field, Thermodynamics, Glass transition, Jump, Internal energy, Thermal expansion, Silica glass, Structural change</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O58" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>09538984V34I8</t>
+          <t>09538984V36I1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2927,40 +2927,40 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Quantum entanglement, Physics, Adiabatic process, Critical point (mathematics), Point reflection, Homogeneous space, Symmetry breaking, Quantum mechanics, Phase transition, Entropy (arrow of time), Statistical physics, Condensed matter physics, Quantum, Mathematics, Geometry, Relaxation (psychology), Dipole, Dynamics (music), Glass transition, Langevin equation, Langevin dynamics, Crossover, Limiting oxygen index, Polyurethane, Cone calorimeter</t>
+          <t>Anharmonicity, Superconductivity, Kinetic isotope effect, Metallic hydrogen, Anisotropy, Hydrogen, Deuterium, Condensed matter physics, Phase diagram, Solid hydrogen, Phase (matter), Materials science, Phase transition, Chemistry, Chemical physics, Physics, Atomic physics, Heterojunction, Antiferromagnetism, Magnetoresistance, Ferromagnetism, Electron, Spins, Magnetic field, Occupancy</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Fourier transform infrared spectroscopy, Thermal stability, Graphite, Thermal decomposition, Composite number, Combustion, Fire retardant, Silicene, Plasmon, Gapless playback, Excitation, Coupling (piping), Graphene, Band gap, Quasiparticle, Heterojunction, Specular reflection, Transmission (telecommunications), Reflection (computer programming), Effective mass (spring–mass system), Dirac (video compression format), Quantum well, HOMO/LUMO, Materials science, Doping</t>
+          <t>Hydrate, Clathrate hydrate, Molecular dynamics, Modulus, Stability (learning theory), Computer science, Machine learning, Computational chemistry, Engineering, Composite material, Band gap, Direct and indirect band gaps, Monolayer, Wide-bandgap semiconductor, Thermal conductivity, Optoelectronics, Electronic band structure, Conductivity, Nanotechnology, Nanoclusters, Cluster (spacecraft), Heteroatom, Boron, Doping, Density functional theory</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O59" t="n">
-        <v>215</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>09538984V34I9</t>
+          <t>09538984V36I2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2969,40 +2969,40 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H60" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Organelle, Mitochondrion, Microtubule, Cytoskeleton, Confocal, Confocal microscopy, Curvature, Function (biology), Memoir, Art, History, Art history, Magnetic refrigeration, Magnetization, Magnetism, Ferromagnetism, Paramagnetism, Monte Carlo method, Sign (mathematics), Topology (electrical circuits), Surface states, Surface (topology), Semimetal, Topological order, Mode (computer interface)</t>
+          <t>Positron, Work function, Scattering, Atomic physics, Tungsten, Kinetic energy, Reflection (computer programming), Diffraction, Physics, Materials science, Nuclear physics, Optics, Electron, Nanotechnology, Saturation current, Diode, Schottky diode, Optoelectronics, Photodiode, Heterojunction, Semiconductor, Reverse leakage current, Photoconductivity, Schottky barrier, Saturation (graph theory)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Band gap, Topological entropy in physics, Groove (engineering), Orientation (vector space), Flat surface, Contact angle, Solar cell, Photovoltaic system, Perovskite (structure), Organic solar cell, Stability (learning theory), Perovskite solar cell, Brillouin zone, Software portability, Computation, Synchronization (alternating current), Nonlinear system, Computer science, Overhead (engineering), Decomposition, Set (abstract data type), Computational science, Algorithm, Optics, Physics</t>
+          <t>Contact geometry, Rectifier (neural networks), Electrical engineering, Geometry, Voltage, Hamiltonian (control theory), Anisotropy, Semimetal, Condensed matter physics, Optical conductivity, Thermal conduction, Valence (chemistry), Band gap, Conductivity, Topology (electrical circuits), Quantum mechanics, Mathematics, Anharmonicity, Lattice (music), Rectification, Thermal, Harmonic oscillator, Ballistic conduction, Work (physics), Thermodynamics</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>218</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>09538984V34I10</t>
+          <t>09538984V36I3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3011,40 +3011,40 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>van der Waals force, Microwave, Transmon, Condensed matter physics, Fabrication, Materials science, Quantum computer, Qubit, Quantum, Optoelectronics, Physics, Quantum mechanics, Molecule, Magnetoelectric effect, Magnetic field, Magnetic moment, Polarization (electrochemistry), Coupling (piping), Polarization density, Nuclear magnetic resonance, Magnetization, Multiferroics, Ferroelectricity, Chemistry, Dielectric</t>
+          <t>Plasmon, Parity (physics), Physics, Antisymmetric relation, Condensed matter physics, Degenerate energy levels, Dispersion relation, Surface plasmon polariton, Topological insulator, Surface plasmon, Quantum mechanics, Mathematical physics, MOSFET, Transistor, Materials science, Optoelectronics, Semiconductor, Electron mobility, Band gap, Field-effect transistor, Non-equilibrium thermodynamics, Nanotechnology, Voltage, Chern class, Gapless playback</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Composite material, Strain (injury), Superconductivity, Phonon, Hydrostatic equilibrium, Work (physics), Infinitesimal strain theory, Dispersion (optics), Fermi level, Hydrostatic pressure, Thermoelectric effect, Thermal conductivity, Thermoelectric materials, Topological insulator, Topology (electrical circuits), Phase (matter), Boltzmann equation, Seebeck coefficient, Thermodynamics, Nanosheet, Ferromagnetism, Formula unit, Monolayer, Band gap, Moment (physics)</t>
+          <t>Lattice (music), Topological order, Topology (electrical circuits), Quantum, Geometry, Combinatorics, Conductance, Zero-point energy, Zero (linguistics), Andreev reflection, Energy (signal processing), Superconductivity, MAJORANA, Mathematics, Floquet theory, Harmonics, Circular dichroism, Spectroscopy, Chemistry, Crystallography, Nonlinear system, Engineering, Electrical engineering, Copper indium gallium selenide solar cells, Passivation</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O61" t="n">
-        <v>216</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>09538984V34I11</t>
+          <t>09538984V36I4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3053,40 +3053,40 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H62" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Mesoscopic physics, Magnetization, Relaxation (psychology), Field (mathematics), Brownian dynamics, Magnetization dynamics, Brownian motion, Electron mobility, Monolayer, Condensed matter physics, Chalcogenide, Janus, Semiconductor, Materials science, Density functional theory, Band gap, Electronic structure, Anisotropy, Asymmetry, Electric field, Nanotechnology, Optoelectronics, Chemistry, Physics, Computational chemistry</t>
+          <t>Superlattice, Phonon, Condensed matter physics, Materials science, Thermal, Physics, Thermodynamics, Master equation, Markov process, Markov chain, Balance equation, Statistical physics, Simple (philosophy), Quantum, Density matrix, Function (biology), Matrix (chemical analysis), Lindblad equation, Quantum mechanics, Mathematics, Markov model, Chemistry, Interface (matter), Kinetic energy, Semiconductor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Optics, Silicene, Polarization (electrochemistry), Transverse plane, Ray, Perpendicular, Spin–orbit interaction, Spin (aerodynamics), Quantum mechanics, Silicon, Solvation, Intermolecular force, Hydrogen bond, Molecule, Resolution (logic), Space (punctuation), Domain (mathematical analysis), Molecular dynamics, Quasiperiodic function, Delocalized electron, Phase transition, Topology (electrical circuits), Topological order, Phase (matter), Quantum phase transition</t>
+          <t>Conductance, Type (biology), Mechanics, Classical mechanics, Optoelectronics, Polyhedron, Facet (psychology), Symmetry (geometry), Cubic crystal system, Geometry, Crystallography, Octahedron, Combinatorics, Crystal structure, Density functional theory, Bilayer, Spectral line, Electronic structure, Molecular physics, Computational chemistry, Actinide, Uranium, Spectroscopy, Vertex (graph theory), Plutonium</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
-        <v>212</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>09538984V34I12</t>
+          <t>09538984V36I5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3095,40 +3095,40 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I63" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Thermodynamics, Shear modulus, Relaxation (psychology), Gibbs free energy, Heat capacity, Materials science, Amorphous metal, Modulus, Kinetics, Entropy (arrow of time), Shear (geology), Entropy production, Physics, Classical mechanics, Composite material, Component (thermodynamics), Computer science, Process (computing), Artificial neural network, Set (abstract data type), Artificial intelligence, Neuroevolution, Atom (system on chip), Molecular dynamics, Machine learning</t>
+          <t>Algorithm, Machine learning, Materials science, Artificial intelligence, Computer science, Wake, Physics, Vortex, Wavefront, Vortex ring, Transverse plane, Kelvin wave, Classical mechanics, Mechanics, Optics, Meteorology, Electronic structure, Condensed matter physics, Selenide, Coulomb, Chalcogenide, Semiconductor, Phase transition, Hybrid functional, Density functional theory</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Algorithm, Graphene, Condensed matter physics, Impurity, Massless particle, Perpendicular, Current (fluid), Modulation (music), Ring (chemistry), Charge carrier, Chemistry, Quantum mechanics, Ising model, Boltzmann machine, Quantum, Restricted Boltzmann machine, Spin (aerodynamics), Quantum annealing, Tensor (intrinsic definition), Spin network, Quantum network, MAJORANA, Quasiparticle, Bound state, Fermion</t>
+          <t>Electron, Optoelectronics, Chemistry, Computational chemistry, Quantum mechanics, Pairing, Superconductivity, Antisymmetric relation, Atomic orbital, Point reflection, Orbital hybridisation, Lattice (music), Homogeneous, Statistical physics, Molecular orbital theory, CASTEP, Debye model, Bulk modulus, Shear modulus, Elastic modulus, Band gap, Direct and indirect band gaps, Thermodynamics, Composite material, Paramagnetism</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
-        <v>212</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>09538984V34I13</t>
+          <t>09538984V36I6</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3137,40 +3137,40 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H64" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I64" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Superconductivity, Electrical resistivity and conductivity, Magnetoresistance, Saturation (graph theory), Granularity, Amorphous solid, Magnetic field, Quantum critical point, Josephson effect, Supercurrent, Ferromagnetism, Topological insulator, Pi Josephson junction, Insulator (electricity), Exchange interaction, Photocatalysis, Materials science, Visible spectrum, Electron paramagnetic resonance, Morphology (biology), Chemical engineering, Photochemistry, Cerium oxide, Nanoparticle, Cerium</t>
+          <t>Phosphorene, Heterojunction, Materials science, van der Waals force, Monolayer, Anode, Semiconductor, Microelectronics, Optoelectronics, Nanotechnology, Chemical physics, Chemistry, Physical chemistry, Molecule, Electrode, Sputtering, Cluster (spacecraft), Atom (system on chip), Metal, Molecular dynamics, Cluster size, Orientation (vector space), Surface (topology), Ion, Atomic physics</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Irradiation, Oxide, Nanotechnology, Chemistry, Organic chemistry, Catalysis, Optoelectronics, Paramagnetism, Spin glass, Annealing (glass), Crystallite, Frustration, Glass transition, Political science, Anharmonicity, Phonon, Thermal, Dissipation, Relaxation (psychology), Thermal conductivity, Scale (ratio), Dilution, Condensed matter physics, Antiferromagnetism, Magnet</t>
+          <t>Crystallography, Molecular physics, Thin film, Computational chemistry, Metallurgy, Physics, Geometry, MAJORANA, Square lattice, Lattice (music), Fermion, Zero-point energy, Condensed matter physics, Topology (electrical circuits), Quantum mechanics, Ising model, Mathematics, Superlattice, Conductance, Graphene, Gaussian, Fermi Gamma-ray Space Telescope, Fermi energy, Fermi level, Electron</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O64" t="n">
-        <v>220</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>09538984V34I14</t>
+          <t>09538984V36I7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3179,40 +3179,40 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H65" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I65" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Phonon, Quantum phase transition, Quantum critical point, Surface phonon, Coupling (piping), Quantum, Phase transition, Quantum phases, Superconductivity, Perovskite (structure), Tin, Crystallization, Thin film, Solubility, Nucleation, Diffraction, Heusler compound, Spintronics, Lattice (music), Ternary operation, Topological order, Topology (electrical circuits), Ambient pressure, Thermoelectric effect, Demagnetizing field</t>
+          <t>Quantum, Boltzmann constant, Boltzmann machine, Computer science, Physics, Quantum mechanics, Artificial intelligence, Materials science, Algorithm, Phosphorene, Exciton, Scaling, Quasiparticle, Graphene, Condensed matter physics, Band gap, Semiconductor, Binding energy, Biexciton, Dielectric, Density functional theory, Kohn–Sham equations, Ionic bonding, Electronic structure, Statistical physics</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Ferromagnetism, Hysteresis, Magnetic domain, Magnetic hysteresis, Magnetic anisotropy, Anisotropy, Micromagnetics, Rheology, Particle (ecology), Phase (matter), Complex fluid, Range (aeronautics), Component (thermodynamics), Transport phenomena, Molecular dynamics, Colloid, Epitaxy, Deposition (geology), Dimension (graph theory), Monomer, SPHERES, Growth rate, Process (computing), Spin (aerodynamics), Spin Hall effect</t>
+          <t>Ion, Excitation, Plasmon, Inelastic scattering, Silicon, Scattering, Atomic physics, Optics, Optoelectronics, Transition metal, Chemistry, Chemical physics, Crystallography, Computational chemistry, Catalysis, Spintronics, Monolayer, Ferromagnetism, Magnetic moment, Curie temperature, Fermi level, Magnetism, Direct and indirect band gaps, Nanotechnology, Superconductivity</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="O65" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>09538984V34I15</t>
+          <t>09538984V36I8</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3221,40 +3221,40 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H66" t="n">
+        <v>8</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Spintronics, Magnetic semiconductor, Antiferromagnetism, Semiconductor, Condensed matter physics, Spin (aerodynamics), Materials science, Spin polarization, Heterojunction, Stacking, Doping, Nanotechnology, Engineering physics, Optoelectronics, Physics, Ferromagnetism, Nuclear magnetic resonance, Electron, Phosphor, Photoluminescence, Ceramic, Mineralogy, Transparent ceramics, Analytical Chemistry (journal), Composite material</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Chemistry, Environmental chemistry, Quantum spin Hall effect, Quantum Hall effect, Quantum, Magnetic field, Topology (electrical circuits), Quantum mechanics, Superconductivity, Ternary operation, Ambient pressure, Lanthanide, Crystal structure, Phonon, Crystal (programming language), Crystallography, Thermodynamics, Computer science, Ion, Acceptor, Band gap, Rutile, Conductivity, Ionization energy, Shallow donor</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
         <v>15</v>
       </c>
-      <c r="I66" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Binding energy, Wave function, X-ray photoelectron spectroscopy, Valence (chemistry), Range (aeronautics), Electric field, Effective nuclear charge, Charge (physics), Chemical bond, Perovskite (structure), Thin film, Strain engineering, Substrate (aquarium), Oxide, Epitaxy, Orientation (vector space), Octahedron, Viscoelasticity, Vortex, Rheology, Cylinder, Azimuth, Viscosity, Elasticity (physics), Transient (computer programming)</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Heterojunction, Responsivity, Photodetector, Charge carrier, Absorption (acoustics), Interface (matter), van der Waals force, Quadratic equation, Ideal (ethics), Phonon, Topology (electrical circuits), Monolayer, Quantum, Dirac (video compression format), Spectrum (functional analysis), Point (geometry), Adsorption, Ethylene glycol, Work function, Denticity, Molecule, Ethylene, Rutile, Formic acid, Berry connection and curvature</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>20</v>
-      </c>
       <c r="O66" t="n">
-        <v>218</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>09538984V34I16</t>
+          <t>09538984V36I9</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3263,40 +3263,40 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H67" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I67" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Graphyne, Graphene, Heterojunction, Ohmic contact, Quantum tunnelling, Schottky barrier, van der Waals force, Fermi level, Dissociation (chemistry), Hydrogen peroxide, Density functional theory, Adsorption, Heterolysis, Decomposition, Oxygen, Vicinal, Peroxide, Magnetite, Oxidizing agent, Formic acid, Analytical Chemistry (journal), Scanning tunneling microscope, Infrared spectroscopy, Single crystal, Soft matter</t>
+          <t>Floquet theory, Gapless playback, Topological insulator, Topology (electrical circuits), Physics, Homogeneous space, Boundary (topology), Order (exchange), Periodic boundary conditions, Condensed matter physics, Boundary value problem, Geometry, Quantum mechanics, Mathematics, Mathematical analysis, Heterojunction, Materials science, Thermal conduction, Oxygen, Pulsed laser deposition, Activation energy, Electrical resistivity and conductivity, Thin film, Optoelectronics, Chemistry</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Multiscale modeling, Computer simulation, Bilayer, Oxide, X-ray photoelectron spectroscopy, Desorption, Dopant, Cobalt, Multifractal system, Singularity, Anderson impurity model, Universality (dynamical systems), Scaling, Anderson localization, Hermitian matrix, Critical exponent, Eigenvalues and eigenvectors, Renormalization group, Adiabatic process, Phonon, Condensed matter physics, Exciton, Physics, Condensation, Adiabatic theorem</t>
+          <t>Nanotechnology, Composite material, Electrical engineering, Valleytronics, Graphene, Atomic orbital, Density functional theory, Electron, Cascade, Ferromagnetism, Orthorhombic crystal system, Crystallography, Crystallite, Antiferromagnetism, Ferroelectricity, Crystal structure, Transition temperature, X-ray crystallography, Diffraction, Dielectric, Metastability, Valence electron, High pressure, Inert, Argon</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
-        <v>215</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>09538984V34I17</t>
+          <t>09538984V36I10</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H68" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I68" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Warm dense matter, Stopping power, Kinetic energy, Projectile, Range (aeronautics), Limit (mathematics), Computation, Inertial confinement fusion, Fusion, Binding energy, Density functional theory, Oxygen, X-ray photoelectron spectroscopy, Photoemission spectroscopy, Atom (system on chip), Electronic structure, Characterization (materials science), Oxygen atom, Triclinic crystal system, Monoclinic crystal system, Phase transition, Compressibility, Raman spectroscopy, Hydrostatic pressure, Diffraction</t>
+          <t>Aqueous solution, van der Waals force, Polymer, Electrolyte, Intermolecular force, Chemical physics, Phosphazene, Chemistry, Polyelectrolyte, Materials science, Molecule, Chemical engineering, Physical chemistry, Organic chemistry, Nial, Spinel, Photocatalysis, Anhydrous, Nickel, Catalysis, Non-blocking I/O, Inorganic chemistry, Salt (chemistry), Nuclear chemistry, Metallurgy</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Isothermal process, Magnetic circular dichroism, Nanoclusters, Magnetization, Chromium, Magnetic moment, Spins, Vanadium, Ion, X-ray magnetic circular dichroism, Ferrimagnetism, Antiferromagnetism, Quantum fluctuation, Hamiltonian (control theory), Ground state, Density matrix renormalization group, Quantum, Renormalization, Renormalization group, Impurity, Saddle point, Magnetic impurity, Saddle, Anderson impurity model, Eckert number</t>
+          <t>Intermetallic, Alloy, Scaling, Dielectric, Polar, Dielectric loss, Spectral line, Degenerate energy levels, Condensed matter physics, Hardening (computing), Physics, Mathematics, Composite material, Geometry, Optoelectronics, Muon spin spectroscopy, Pairing, Superconductivity, Muon, Penetration depth, Superfluidity, London penetration depth, Magnetic field, Nuclear physics, Quantum mechanics</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O68" t="n">
-        <v>208</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>09538984V34I18</t>
+          <t>09538984V36I11</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3347,40 +3347,40 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H69" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I69" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Superconductivity, State (computer science), Range (aeronautics), Energy (signal processing), Open research, Focus (optics), Measure (data warehouse), Magnetic field, Deformation (meteorology), Bending, Scaling, Dynamics (music), Non-equilibrium thermodynamics, Field (mathematics), Representation (politics), Sigmoid function, Differentiable function, Thermal diffusivity, Molecular dynamics, Phase (matter), Thermoluminescence, Vibration, Molecular vibration, Semiconductor, Adiabatic process</t>
+          <t>Relaxation (psychology), Glass transition, Dielectric, Polymer, Cole–Cole equation, Materials science, Dielectric spectroscopy, Spectroscopy, Sequence (biology), Nuclear magnetic resonance, Chemistry, Physical chemistry, Physics, Composite material, Vibration, Equipartition theorem, Rotation around a fixed axis, Acceleration, Kinetic energy, Amplitude, Classical mechanics, Normal mode, Particle (ecology), Translational motion, Mechanics</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Absorption (acoustics), Molecular physics, Materials science, Condensed matter physics, Chemistry, Chemical physics, Atomic physics, Raman spectroscopy, Luminescence, Physics, Optics, Optoelectronics, Thermodynamics, Quantum mechanics, Composite material, Heterojunction, Band gap, Semiconductor materials, Electronic band structure, Semiconductor device, Microwave, Berry connection and curvature, Valleytronics, Hamiltonian (control theory), Spin polarization</t>
+          <t>Spectral density, Optics, Quantum mechanics, Mathematics, Quantum tunnelling, Heterojunction, Semiconductor, Ferroelectricity, Condensed matter physics, Charge carrier, Rectangular potential barrier, Electron, Tunnel junction, Optoelectronics, Nanotechnology, Tin, Monolayer, Anisotropy, Binary number, Crystallography, Metallurgy, van der Waals force, Photocatalysis, Water splitting, Photocatalytic water splitting</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O69" t="n">
-        <v>206</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>09538984V34I19</t>
+          <t>09538984V36I12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3389,40 +3389,40 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H70" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I70" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Crystal (programming language), Convolutional neural network, Band gap, Artificial neural network, Graph, Normalization (sociology), Magnetism, Electronic structure, Density functional theory, Magnetic structure, Electronic systems, Feature (linguistics), Superconductivity, Knight shift, Density of states, Fermi level, Coupling (piping), Relaxation (psychology), Resonance (particle physics), Electrical resistivity and conductivity, Eutectic system, Volume (thermodynamics), Alloy, Percolation (cognitive psychology), Crossover</t>
+          <t>Percolation threshold, Percolation (cognitive psychology), Percolation critical exponents, Quantum tunnelling, Percolation theory, Topological insulator, Physics, Continuum percolation theory, Directed percolation, Topology (electrical circuits), Quantum, Statistical physics, Condensed matter physics, Quantum mechanics, Mathematics, Combinatorics, Conductivity, Electrical resistivity and conductivity, Spintronics, Spin (aerodynamics), Fermi energy, Current (fluid), Degeneracy (biology), Degenerate energy levels, Symmetry (geometry)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Critical point (mathematics), Transition point, Brillouin zone, Surface (topology), Reciprocal lattice, Charge density, Surface reconstruction, Amplitude, Superlattice, Electronic band structure, Surface states, Phonon, Semimetal, Symmetry (geometry), Tensor (intrinsic definition), Parametrization (atmospheric modeling), Monolayer, Work (physics), Force constant, Decoupling (probability), Eigenvalues and eigenvectors, Irradiation, Inverse, Crystallographic defect, Lattice (music)</t>
+          <t>Magnetic field, Conductance, Symmetry breaking, Electron, Geometry, Ferromagnetism, Andreev reflection, Superconductivity, Bound state, Graphene nanoribbons, Anisotropy, Zigzag, Graphene, Phosphorene, Monolayer, Materials science, Heterojunction, Field-effect transistor, Metal, Optoelectronics, Transistor, Nanotechnology, Metallurgy, Electrical engineering, Voltage</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O70" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>09538984V34I20</t>
+          <t>09538984V36I13</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3431,40 +3431,40 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H71" t="n">
+        <v>13</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Metastability, Monte Carlo method, Materials science, Plane (geometry), Work (physics), Sequence (biology), Atomic physics, Molecular physics, Condensed matter physics, Crystallography, Physics, Chemistry, Thermodynamics, Geometry, Mathematics, Quantum mechanics, Statistics, Annealing (glass), Band gap, Photoluminescence, Amorphous solid, Grain size, Microstructure, Thin film, Atmospheric temperature range</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Impurity, Analytical Chemistry (journal), Optoelectronics, Nanotechnology, Composite material, Spin (aerodynamics), Charge (physics), Magnetic field, Pairing, Andreev reflection, Ferromagnetism, Ising model, Superconductivity, Amplitude, Insulator (electricity), Quantum tunnelling, Rectification, Phonon, Carbon nanotube, Thermal, Diamond, Thermal resistance, Molecule, Optical rectification, Chemical physics</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
         <v>20</v>
       </c>
-      <c r="I71" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Electrical resistivity and conductivity, Hall effect, Bar (unit), Anomaly (physics), Transverse plane, Epitaxy, Relaxation (psychology), Lanthanum, Superconductivity, Tetragonal crystal system, Phase transition, Compressibility, Lanthanide, Phase (matter), Halide, Luminescence, Fluorescence, Exciton, Encryption, Light emission, Photoluminescence, Pairing, Hamiltonian (control theory), Homogeneous space, Zigzag</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Lattice (music), Topology (electrical circuits), Fermi resonance, Raman spectroscopy, Phthalic anhydride, Resonance (particle physics), Raman scattering, Fermi level, Diamond anvil cell, Analytical Chemistry (journal), Mechanics, Lattice Boltzmann methods, Drag, Pseudopotential, Physics, Classical mechanics, Condensed matter physics, Coulomb, Hermitian matrix, Hubbard model, Parity (physics), Kinetic energy, Quantum mechanics, Molecule, Quantum</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>21</v>
-      </c>
       <c r="O71" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>09538984V34I21</t>
+          <t>09538984V36I14</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3473,40 +3473,40 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H72" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I72" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Acceptor, Molecule, Heterojunction, X-ray photoelectron spectroscopy, Synchrotron radiation, Absorption spectroscopy, Chemistry, Absorption (acoustics), Electronic structure, Materials science, Optoelectronics, Atomic physics, Physics, Optics, Computational chemistry, Nuclear magnetic resonance, Condensed matter physics, Oxide, Ionic liquid, Nanoparticle, Adsorption, Ionic bonding, Metal, Corrosion, Quantum entanglement</t>
+          <t>Photocatalysis, Semiconductor, Materials science, Nanotechnology, Engineering physics, Optoelectronics, Chemistry, Physics, Catalysis, Electron, Nuclear physics, Electrocatalyst, Transition metal, Desorption, Water splitting, Gibbs free energy, Alkaline water electrolysis, Oxygen evolution, Density functional theory, Inorganic chemistry, Selenide, Hydrogen, Chemical engineering, Reactivity (psychology), Electrolysis</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Square lattice, Lattice (music), Frustration, Entropy (arrow of time), Electronic correlation, Fermion, Hubbard model, Quantum tunnelling, Quantum, Discontinuity (linguistics), Molecular dynamics, Dissociation (chemistry), Asymmetry, Phase transition, Propagator, Quasiparticle, Plutonium, Valence (chemistry), Electron, Density functional theory, Density of states, Electronic band structure, Quantum mechanics, Nuclear physics, Casimir effect</t>
+          <t>Adsorption, Physical chemistry, Metallurgy, Computational chemistry, Electrochemistry, Thermodynamics, Electrolyte, Electrode, Organic chemistry, Yukawa potential, Dispersity, Condensed matter physics, Quantum mechanics, Polymer chemistry, Samarium, Dielectric, Doping, Barium titanate, Composite number, Cobalt, Barium, Ferrite (magnet), Permittivity, Barium ferrite, Composite material</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
-        <v>217</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>09538984V34I22</t>
+          <t>09538984V36I15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3515,40 +3515,40 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H73" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I73" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Solid solution, Interatomic potential, Molecular dynamics, Standard enthalpy of formation, Component (thermodynamics), Thermal, Jargon, Public relations, Reading (process), Countdown, Corporate governance, Management, Political science, Engineering, Business, Polariton, Femtosecond, Exciton, Excitation, Materials science, Polarization (electrochemistry), Quasiparticle, Photoluminescence, Picosecond, Optoelectronics</t>
+          <t>Aperiodic graph, Hamiltonian (control theory), Physics, Bloch wave, Geometric phase, Phase transition, Quantum phase transition, Critical point (mathematics), Quantum mechanics, Quantum, Condensed matter physics, Band gap, Mathematics, Mathematical analysis, Quasiparticle, Berry connection and curvature, Brillouin zone, Spintronics, Topology (electrical circuits), Phonon, Ferromagnetism, Superconductivity, Heterojunction, Photoluminescence, Epitaxy</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Laser, Molecular physics, Atomic physics, Condensed matter physics, Optics, Physics, Chemistry, Superconductivity, Shearing (physics), Anisotropy, Granular material, Compaction, Configuration entropy, Supercooling, Entropy (arrow of time), Cube (algebra), Linear dichroism, Zigzag, Dichroism, Absorption edge, Circular dichroism, Band gap, Crystallography, Maxima and minima, Attenuation</t>
+          <t>Disproportionation, Optoelectronics, Materials science, Semiconductor, Chemistry, Nanotechnology, Catalysis, van der Waals force, Cluster (spacecraft), Magnet, Spin (aerodynamics), Liquid state, Quantum spin liquid, Chemical physics, Spin polarization, Thermodynamics, Electron, Molecule, Antiferromagnetism, Magnetization, Magnetic domain, Polarization density, Magnetic field, Magnetoelectric effect, Magnetic moment</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
-        <v>216</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>09538984V34I23</t>
+          <t>09538984V36I16</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3557,40 +3557,40 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H74" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I74" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Perturbation theory (quantum mechanics), Virial coefficient, Virial theorem, Formalism (music), Density functional theory, Measure (data warehouse), Perturbation (astronomy), Consistency (knowledge bases), Hybrid functional, Materials science, Ferroelectricity, Epitaxy, Transmission electron microscopy, Lamella (surface anatomy), Orthorhombic crystal system, Condensed matter physics, Monoclinic crystal system, Crystallography, Thin film, Polarization (electrochemistry), Optics, Layer (electronics), Optoelectronics, Composite material, Dielectric</t>
+          <t>Ergodicity, Quantum chaos, Quantum, Statistical physics, Connection (principal bundle), Perspective (graphical), Theoretical physics, Physics, Quantum dynamics, Quantum mechanics, Mathematics, Computer science, Artificial intelligence, Faraday efficiency, Anode, Materials science, Galvanic cell, Galvanic anode, Dendrite (mathematics), Aqueous solution, Plating (geology), Stripping (fiber), Galvanic corrosion, Chemical engineering, Electrochemistry</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Crystal structure, Nanotechnology, Chemistry, Physics, Spintronics, Berry connection and curvature, Topological insulator, Quantum spin Hall effect, Brillouin zone, Quantum Hall effect, Topology (electrical circuits), Band gap, Janus, Topological order, Superconductivity, Ambient pressure, Ionic bonding, Hydrogen, Quantum, High pressure, Ion, Chemical physics, Engineering physics, Quantum mechanics, Thermodynamics</t>
+          <t>Electrode, Metallurgy, Chemistry, Corrosion, Composite material, Cathodic protection, Catalysis, Homogeneous space, Topology (electrical circuits), Monolayer, Surface (topology), Chemical physics, Density functional theory, Nanotechnology, Computational chemistry, Physical chemistry, Geometry, Conductance, Condensed matter physics, Phase diagram, Topological insulator, Anderson localization, Phase transition, Metal–insulator transition, Phase (matter)</t>
         </is>
       </c>
       <c r="N74" t="n">
         <v>15</v>
       </c>
       <c r="O74" t="n">
-        <v>212</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>09538984V34I24</t>
+          <t>09538984V36I17</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3599,40 +3599,40 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H75" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I75" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Superconductivity, Paramagnetism, Phase diagram, Ferromagnetism, Magnetic field, Fermi surface, Critical field, Physics, Magnetism, Phase (matter), Quantum mechanics, Blisters, Graphene, Polymer, Adhesion, Curing (chemistry), Molecular dynamics, Monolayer, Pyrochlore, Spin ice, Heat capacity, Frustration, Magnetic susceptibility, Geometrical frustration</t>
+          <t>Consciousness, Mythology, Epistemology, Perception, Philosophy, Psychology, Linguistics, Psychoanalysis, Sociology, History, Theology, Graphene, Plasmon, Materials science, Optical conductivity, Moiré pattern, Heterojunction, Bilayer graphene, Optoelectronics, Condensed matter physics, Nanotechnology, Optics, Physics, Anharmonicity, Superconductivity</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Spin glass, Magnetic refrigeration, Quasiparticle, Excited state, Coulomb, Electron, Excitation, Plasmon, Atomic orbital, Materials science, Atomic physics, Thermal diffusivity, Cluster (spacecraft), Rotational diffusion, Brownian motion, Brownian dynamics, Phase transition, Work (physics), Chemical physics, Chemistry, Range (aeronautics), Thermodynamics, Molecule, Photoionization, Impurity</t>
+          <t>Quantum decoherence, Phonon, Soft modes, Quantum, Quantum mechanics, Theoretical physics, Ferroelectricity, Computer science, Vanadium, Voltage, Flow battery, Electrolyte, Battery (electricity), Energy storage, Density functional theory, Renewable energy, Redox, Process engineering, Chemistry, Electrode, Electrical engineering, Computational chemistry, Thermodynamics, Power (physics), Physical chemistry</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O75" t="n">
-        <v>216</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>09538984V34I25</t>
+          <t>09538984V36I18</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3641,40 +3641,40 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H76" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I76" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Spin polarization, Polarization (electrochemistry), Oxide, Adsorption, Ferromagnetism, Density functional theory, Transition metal, Nanoparticle, Hydrostatic pressure, Fermi level, Phase transition, Electronic band structure, Electronic structure, Diffraction, Lattice constant, Chemical vapor deposition, van der Waals force, Heterojunction, Stacking, Deposition (geology), MAJORANA, Bound state, Oscillation (cell signaling), Superconductivity, Coupling (piping)</t>
+          <t>Liquid crystal, Isotropy, Topological defect, Planar, Exponent, Condensed matter physics, Scaling, Phase (matter), Physics, Steady state (chemistry), Materials science, Classical mechanics, Mechanics, Optics, Geometry, Chemistry, Mathematics, Quantum mechanics, Spectroscopy, Anisotropy, Reflection (computer programming), Chemical physics, Interface (matter), Statistical physics, Computer science</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Magnetic field, Quantum, Conductance, Plasmon, Optical conductivity, Fermion, Random phase approximation, Wavelength, Surface plasmon, Absorption (acoustics), Dielectric, Computer science, Heat capacity, Condensed matter physics, Pairing, Materials science, Physics, Topology (electrical circuits), Thermodynamics, Optics, Phase diagram, Lattice (music), Paramagnetism, Phonon, Phase (matter)</t>
+          <t>Physical chemistry, Stiffness, Polymer, Dynamics (music), Chromosomal translocation, Composite material, Thermodynamics, Amorphous solid, Phase transition, Glass transition, Entropy (arrow of time), Heat capacity, Gibbs free energy, Organic chemistry, Monatomic ion, Electron diffraction, Hydrogen, Diffraction, Gas electron diffraction, Reflection high-energy electron diffraction, Hydrogen atom, Atomic physics, Valence electron, Neutron diffraction, X-ray crystallography</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O76" t="n">
-        <v>213</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>09538984V34I26</t>
+          <t>09538984V36I19</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3683,40 +3683,40 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H77" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I77" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Chemical physics, Ionic bonding, Ionic liquid, Nanopore, Capacitance, Phase transition, Range (aeronautics), Materials science, Lattice (music), Electrostatics, Capacitive sensing, Nanotechnology, Ion, Condensed matter physics, Physics, Chemistry, Computer science, Physical chemistry, Organic chemistry, Exciton, Phonon, Spin-flip, Scattering, Relaxation (psychology), Spin (aerodynamics)</t>
+          <t>Spintronics, Skyrmion, Chirality (physics), Point reflection, Condensed matter physics, Ferromagnetism, Nonlinear system, Physics, Spin (aerodynamics), Symmetry breaking, Nanotechnology, Materials science, Chiral symmetry breaking, Quantum mechanics, Wetting, Orientation (vector space), Adhesion, Aluminium, Crystallography, Chemistry, Chemical physics, Composite material, Geometry, Heterojunction, van der Waals force</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Phonon scattering, Quantum mechanics, Phenomenology (philosophy), Translational symmetry, Symmetry (geometry), Theoretical physics, Geometry, Mathematics, Surface phonon, Polariton, Surface plasmon polariton, Surface plasmon, Plasmon, Dielectric, Localized surface plasmon, Optoelectronics, Orthoferrite, Magnetic structure, Multiferroics, Neutron diffraction, Ground state, Spin structure, Magnetic field, Diffraction, Atmospheric temperature range</t>
+          <t>Semiconductor, Strain engineering, Optoelectronics, Anisotropy, Optics, Silicon, Photon, Quantum dot, Transverse plane, Spin–orbit interaction, Coupling (piping), Electron, Nanowire, Asymmetry, Graphene, Nanocrystalline material, Raman spectroscopy, Crystallite, Chemical vapor deposition, Rhodamine 6G, Substrate (aquarium), Chemical engineering, Molecule, Organic chemistry, Metallurgy</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O77" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>09538984V34I27</t>
+          <t>09538984V36I20</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3725,40 +3725,40 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H78" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I78" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Nanowire, Condensed matter physics, Scattering, Dirac (video compression format), Semimetal, Scaling, Conductance, Physics, Phase (matter), Weak localization, Topology (electrical circuits), Phase transition, Band gap, Materials science, Quantum mechanics, Magnetoresistance, Magnetic field, Mathematics, Geometry, Mesoscopic physics, Anisotropy, Colloid, Colloidal particle, Field (mathematics), Surface (topology)</t>
+          <t>Ferromagnetism, Spintronics, Doping, Materials science, Dopant, Magnetism, Condensed matter physics, Nanotechnology, Transition metal, Density functional theory, Engineering physics, Optoelectronics, Chemistry, Physics, Computational chemistry, Reciprocity (cultural anthropology), Reciprocal, Diagonal, Toroid, Symmetry (geometry), Classical mechanics, Quantum mechanics, Geometry, Mathematics, Hall effect</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Topological insulator, Topological order, Topological entropy in physics, Symmetry protected topological order, Antiferromagnetism, Topological quantum number, Electron, Topological degeneracy, Quantum, Hamiltonian (control theory), Statistical physics, Entropy (arrow of time), Computer science, Quantum system, Density functional theory, Applied mathematics, Mathematical optimization, Luttinger liquid, Raman spectroscopy, Viscosity, Shear (geology), Fermi liquid theory, Fermi Gamma-ray Space Telescope, Thermodynamics, Composite material</t>
+          <t>Magnetic field, Scattering, Planar, Topological insulator, Computer science, Phonon, Electron, Phonon scattering, Electric field, Kinetic energy, Quantum, Ultrashort pulse, Quantum dot, Polarization (electrochemistry), Circular polarization, Monolayer, RADIUS, Molecular physics, Optics, Laser, Hafnia, Ferroelectricity, Epitaxy, Vacancy defect, Strain (injury)</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O78" t="n">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>09538984V34I28</t>
+          <t>09538984V36I21</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3767,40 +3767,40 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H79" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I79" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Phosphorene, Doping, Spintronics, Anode, Magnetism, Atom (system on chip), Monolayer, Zigzag, Condensed matter physics, Magnetization, Frustration, Ground state, Valence (chemistry), Materials science, Lattice (music), Hexagonal lattice, Hexagonal crystal system, Synchrotron, Atmospheric temperature range, Cluster (spacecraft), Crystallography, Chemistry, Physics, Magnetic field, Thermodynamics</t>
+          <t>Metaphosphate, Phosphate glass, Glass transition, Materials science, Poling, Crystallization, Phosphate, Ion, Polarization (electrochemistry), Composite material, Mineralogy, Chemical engineering, Chemistry, Optoelectronics, Dielectric, Doping, Polymer, Ferroelectricity, Oxide, Atomic orbital, Electronic structure, Perovskite (structure), Semiconductor, Metal, Band gap</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Quantum mechanics, Antiferromagnetism, Ferromagnetism, Perovskite (structure), Basis set, Mulliken population analysis, Phase (matter), Hamiltonian (control theory), Computational chemistry, Density functional theory, Mathematics, Spins, Monte Carlo method, Anisotropy, Spin glass, Magnet, Random field, Spin (aerodynamics), Topology (electrical circuits), Qubit, Quantum computer, Computer science, Quantum simulator, Quantum, Swap (finance)</t>
+          <t>Condensed matter physics, Lattice constant, Thin film, Nanotechnology, Crystallography, Diffraction, Optics, Electron, Physics, Heterojunction, Polar, Chemical physics, Quantum mechanics, Quantum dot, Graphene, Harmonics, RADIUS, Cutoff, Harmonic, Quantum dot laser, Pulse (music), Quantum well, Laser, Hexagonal crystal system, Double layered</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O79" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>09538984V34I29</t>
+          <t>09538984V36I22</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3809,40 +3809,40 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H80" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I80" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Monolayer, Work function, Superconductivity, Fermi level, Density functional theory, Condensed matter physics, Dipole, Chemical physics, Density of states, Chemistry, Work (physics), Materials science, Metal, Nanotechnology, Computational chemistry, Physics, Thermodynamics, Organic chemistry, Electron, Stacking, Delocalized electron, Electron mobility, Superlattice, Organic semiconductor, Molecule</t>
+          <t>Exchange interaction, Physics, Isotropy, Statistical physics, Heisenberg model, Magnetism, Density functional theory, Theoretical physics, Coulomb, Perturbation theory (quantum mechanics), Quantum mechanics, Ferromagnetism, Electron, Chalcogenide, Materials science, Metal, Nanotechnology, Metallurgy, Magnetic field, Molecular dynamics, Graphene, Bilayer, Composite material, Condensed matter physics, Bilayer graphene</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Barium, Orthorhombic crystal system, Halide, Crystal structure, Bromide, Barium chloride, High pressure, Ambient pressure, Chloride, Inorganic chemistry, Crystallography, Metallurgy, Engineering physics, Cerium, Isostructural, Phase transition, Transition metal, Phase (matter), Quantum mechanics, Hubbard model, Antiferromagnetism, Lattice (music), Quercetin, Hydrogen bond, Dilution</t>
+          <t>Chemistry, Computational chemistry, Membrane, Phosphorene, Quantum tunnelling, Magnetoresistance, Spintronics, Band gap, Floquet theory, Attosecond, Laser, Dephasing, Atomic physics, Optics, Ultrashort pulse, Lattice constant, Magnetic moment, Alloy, Structural stability, Electronic structure, Phonon, Density of states, Enthalpy, Electronic band structure, Thermodynamics</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="O80" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>09538984V34I30</t>
+          <t>09538984V36I23</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3851,40 +3851,40 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H81" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I81" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Magnetoresistance, Silicene, Quantum tunnelling, Conductance, Spin polarization, Polarization (electrochemistry), Magnetic field, Materials science, Chemistry, Physics, Graphene, Nanotechnology, Electron, Quantum mechanics, Spintronics, Electric field, Heterojunction, Giant magnetoresistance, Ferromagnetism, Nanodot, Nanomagnet, Magnetization, Ferroelectricity, Coercivity</t>
+          <t>Physisorption, Chemisorption, Realization (probability), Tetraphenylporphyrin, Chemistry, Density functional theory, Computational chemistry, Nanotechnology, Catalysis, Organic chemistry, Materials science, Mathematics, Porphyrin, Anharmonicity, Phonon, Thermal conductivity, Raman spectroscopy, Thin film, Condensed matter physics, Raman scattering, Phonon scattering, Atmospheric temperature range, Scattering, Optics, Physics</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Dielectric, Optoelectronics, MAJORANA, Superconductivity, Topology (electrical circuits), Quantization (signal processing), Mathematics, Topological insulator, Zeeman effect, Phase transition, Thin film, Excitation, Refractive index, Metal–insulator transition, Transition point, Band gap, Metal, Fluorine, Carbon fibers, Chemical physics, Cluster (spacecraft), Composite material, Refrigerator car, Heat engine, Joule (programming language)</t>
+          <t>Composite material, Thermodynamics, Solvation, Steric effects, Lithium (medication), Molecular dynamics, Electrolyte, Solvation shell, Chemical physics, Alkyl, Solvent, Ion, Physical chemistry, Hamiltonian (control theory), Nanowire, Eigenvalues and eigenvectors, Quantum mechanics, Chirality (physics), Coupling constant, Heterojunction, Superconductivity, Magnet, Curvature, Spin (aerodynamics), Constant (computer programming)</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O81" t="n">
-        <v>228</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>09538984V34I31</t>
+          <t>09538984V36I24</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3893,40 +3893,40 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H82" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I82" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Condensed matter physics, Transition metal, Synchrotron, Phase transition, Fermi surface, Materials science, Electronic structure, Lattice constant, Electronic band structure, Fermi level, Diffraction, Electron, Physics, Chemistry, Superconductivity, Optics, Quantum mechanics, Antiferromagnetism, Spin (aerodynamics), Unitary state, Line (geometry), Space (punctuation), Group (periodic table), Magnetic structure, Magnetic field</t>
+          <t>Floquet theory, Hermitian matrix, Boundary (topology), Topology (electrical circuits), Physics, Mathematics, Mathematical analysis, Quantum mechanics, Nonlinear system, Statistical mechanics, Statistical physics, Artificial neural network, Classical mechanics, Computer science, Artificial intelligence, Van Hove singularity, Tungsten, Superconductivity, Condensed matter physics, Singularity, Materials science, Geometry, Electron, Metallurgy, Phonon</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Mathematics, Computer science, Magnetization, Geometry, Magnetoresistance, Electrical resistivity and conductivity, Dirac fermion, Hall effect, Magnetic susceptibility, Fermion, Phonon, Molecular dynamics, Statistical physics, Work (physics), Kinetic energy, Cohesion (chemistry), Thermodynamics, Refractory metals, Classical mechanics, Photonic crystal, Theoretical physics, Wannier function, Energy density, Topology (electrical circuits), Operator (biology)</t>
+          <t>Thermal conduction, Aperiodic graph, Modulation (music), Heat transfer, Full width at half maximum, Zero-point energy, Zero (linguistics), Substrate (aquarium), Motion (physics), Quantum, Point (geometry), Adsorption, Chemistry, Physical chemistry, Type (biology), Phase (matter), Crystallography, Geology, Paleontology, Organic chemistry, Radioluminescence, Kinetics, Dosimeter, Irradiation, Scintillator</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O82" t="n">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>09538984V34I32</t>
+          <t>09538984V36I25</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3935,40 +3935,40 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H83" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I83" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Ambient pressure, Metastability, Phase transition, Neutron diffraction, Ammonium bromide, Chemistry, Phase (matter), Bromide, Phase diagram, Ammonium, Diffraction, Crystallography, Thermodynamics, Analytical Chemistry (journal), Crystal structure, Inorganic chemistry, Organic chemistry, Physics, Optics, Mesoscopic physics, Parametric statistics, Statistical physics, Computer science, Topology (electrical circuits), Mathematical optimization</t>
+          <t>Magnetization, Orbit (dynamics), Torque, Spin (aerodynamics), Condensed matter physics, Physics, Materials science, Engineering, Quantum mechanics, Aerospace engineering, Magnetic field, Thermodynamics, Mesoporous material, Mesoporous silica, Mesoporous organosilica, Nanotechnology, Void (composites), Nanoparticle, Composite material, Chemistry, Organic chemistry, Hermitian matrix, Topology (electrical circuits), Realization (probability), Skin effect</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Mathematics, Quantum mechanics, Phonon, Materials science, Condensed matter physics, Mineralogy, Molecular dynamics, Metadynamics, Enantiomer, Brownian dynamics, Configuration space, Cluster (spacecraft), Curse of dimensionality, Energy landscape, Computational chemistry, Chemical physics, Brownian motion, Stereochemistry, Swelling, Irradiation, Work (physics), Ion, Thin film, Mechanics, Molecular physics</t>
+          <t>Euclidean geometry, Parity (physics), Lattice (music), Reciprocal, Theoretical physics, Mathematics, Geometry, Combinatorics, Photoelectric effect, Heterojunction, Optoelectronics, Engineering physics, Hubbard model, Pauli exclusion principle, Superconductivity, Decoupling (probability), Singularity, t-J model, Charge (physics), Renormalization group, Van Hove singularity, Cuprate, Fermi level, Electron, Dual (grammatical number)</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O83" t="n">
-        <v>204</v>
+        <v>227</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>09538984V34I33</t>
+          <t>09538984V36I26</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3977,40 +3977,40 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H84" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I84" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Topology (electrical circuits), Seebeck coefficient, Weyl semimetal, Semimetal, Condensed matter physics, Physics, Topological insulator, van der Waals force, Fermi level, Thermoelectric materials, Electronic band structure, Thermoelectric effect, Quantum mechanics, Electron, Band gap, Mathematics, Raman spectroscopy, Plasmon, Semiconductor, Characterization (materials science), Materials science, Nanotechnology, Spectroscopy, Optoelectronics, Optics</t>
+          <t>Hamiltonian (control theory), Floquet theory, Physics, Homogeneous space, Band gap, Point reflection, Topology (electrical circuits), Zero-point energy, Condensed matter physics, Quantum mechanics, Geometry, Mathematics, Polyaniline, Graphene, Supercapacitor, Materials science, Nanocomposite, Conductive polymer, Electrode, Nanotechnology, Capacitance, Polyaniline nanofibers, Graphene foam, Composite material, Polymer</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Graphene nanoribbons, Zigzag, Conductance, Quantum tunnelling, Quantum dot, Bound state, Graphene, Pseudogap, Superconductivity, Cuprate, Liquid crystal, Doping, Electrical resistivity and conductivity, Superfluidity, Limit (mathematics), Term (time), Statistical physics, Theoretical physics, Deposition (geology), Ion beam, Irradiation, Ion, Chemistry, Geology, Gating</t>
+          <t>Graphene oxide paper, Chemistry, Monolayer, Balance (ability), Plane (geometry), Detailed balance, Statistical physics, Combinatorics, Biology, Neuroscience, Scattering, Atom (system on chip), Debye, Computer science, Optics, Charge (physics), Quantum, Graphene nanoribbons, Charge ordering, Mott insulator, Checkerboard, Antiferromagnetism, Doping, Semiclassical physics, Lattice (music)</t>
         </is>
       </c>
       <c r="N84" t="n">
         <v>13</v>
       </c>
       <c r="O84" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>09538984V34I34</t>
+          <t>09538984V36I27</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H85" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I85" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Stacking, Density functional theory, Materials science, Heterojunction, Optoelectronics, Band gap, Absorption (acoustics), van der Waals force, Absorption spectroscopy, Monolayer, Direct and indirect band gaps, Nanotechnology, Chemistry, Optics, Computational chemistry, Physics, Molecule, Condensed matter physics, Magnetic moment, Skyrmion, Spin glass, Curie temperature, Spin (aerodynamics), Phase diagram, Metal</t>
+          <t>Topology (electrical circuits), Electronic band structure, Physics, Brillouin zone, Nanotechnology, Condensed matter physics, Materials science, Nanowire, Surface plasmon, Surface plasmon polariton, Nanophotonics, Wavenumber, Dispersion (optics), Plasmon, Electrical conductor, Dispersion relation, Optics, Conductivity, Surface wave, Refractive index, Surface conductivity, Tensor (intrinsic definition), Cylinder, Optoelectronics, Geometry</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Phase (matter), Ferromagnetism, Thermodynamics, Metallurgy, Anharmonicity, Atmospheric temperature range, Heat capacity, Phonon, Work (physics), Specific heat, Thermal expansion, Second sound, Entropy (arrow of time), Thermal, Speed of sound, Sound (geography), Microfluidics, Mechanics, Flow (mathematics), Particle (ecology), RADIUS, Channel (broadcasting), Nanopore, Range (aeronautics), Fluid dynamics</t>
+          <t>Composite material, Quantum mechanics, Phase (matter), Equation of state, Thermodynamics, Chemistry, Planar, Set (abstract data type), Hall conductivity, Weyl semimetal, Semimetal, Hall effect, Theoretical physics, Electrical resistivity and conductivity, Computer science, Computer graphics (images), MAJORANA, Fermion, Superconductivity, Dirac fermion, Fermi surface, Dissipative system, Quantum, Statistical physics, Ferrimagnetism</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O85" t="n">
-        <v>171</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>09538984V34I35</t>
+          <t>09538984V36I28</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4061,40 +4061,40 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I86" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Zirconolite, Ceramic, Breeder (animal), Thermodynamics, Materials science, Stoichiometry, Fusion power, Phase (matter), Physical chemistry, Blanket, Chemistry, Nuclear physics, Pyrochlore, Metallurgy, Physics, Plasma, Heterojunction, Excitation, Semiconductor, Electron, Ion, Charge carrier, Atomic physics, Exciton, Density functional theory</t>
+          <t>Photodetector, Quantum efficiency, Optoelectronics, Quantum, Materials science, Computer science, Physics, Quantum mechanics, Quasicrystal, Topology (electrical circuits), Order (exchange), Topological order, Topological insulator, Topological defect, Amorphous solid, Boundary (topology), Condensed matter physics, Mathematics, Chemistry, Crystallography, Spinel, X-ray photoelectron spectroscopy, Interpretation (philosophy), Spectral line, Core (optical fiber)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Chemical physics, Condensed matter physics, Molecular physics, Optoelectronics, Computational chemistry, Addendum, Ground state, Cubic crystal system, Face (sociological concept), Quantum mechanics, Philosophy, Political science, Law, Josephson effect, Magnetoelectric effect, Josephson energy, Josephson phase, Pi Josephson junction, Superconductivity, Multiferroics, Dielectric, Ferroelectricity, Pairing, Anisotropy, Effective mass (spring–mass system)</t>
+          <t>Inverse, Mineralogy, Nuclear magnetic resonance, Optics, Metallurgy, Geometry, Ferromagnetism, Kinetics, Liquid crystal, Classical mechanics, Vortex, Mechanics, Superconductivity, Electrical resistivity and conductivity, Critical field, Trigonal crystal system, Magnetization, Magnetic field, Stoichiometry, Field (mathematics), Crystal structure, Thermoelastic damping, Tungsten, Thermodynamics, Bulk modulus</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O86" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>09538984V34I36</t>
+          <t>09538984V36I29</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4103,40 +4103,40 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H87" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I87" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Political science, Skyrmion, Square lattice, Condensed matter physics, Physics, Exchange interaction, Lattice (music), Mean field theory, Ferromagnetism, Ising model, Isoelectric point, Chemistry, Protonation, Protein adsorption, Adsorption, Myoglobin, Surface charge, Crystallography, Lysozyme, Charge density, Chemical physics, Physical chemistry, Organic chemistry, Biochemistry, Ion</t>
+          <t>Hematite, Chemistry, Valence (chemistry), Anatase, Titanium dioxide, Chemical physics, Adsorption, Photocatalysis, Impurity, Cluster (spacecraft), Oxygen, Nanotechnology, Inorganic chemistry, Catalysis, Materials science, Mineralogy, Physical chemistry, Metallurgy, Clutch, Oblique case, Avian clutch size, Mechanics, Physics, Biology, Philosophy</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Carbon fibers, Materials science, Anisotropy, Tower, Shear modulus, Density functional theory, Reinforced carbon–carbon, Modulus, Electronic structure, Composite material, Nanotechnology, Structural engineering, Composite number, Computational chemistry, Engineering, Optics, Hamiltonian (control theory), Band gap, Semimetal, Electronic band structure, Brillouin zone, Tight binding, Direct and indirect band gaps, Valence (chemistry), Ultimate tensile strength</t>
+          <t>Ecology, Reproduction, Dielectric, Nanocrystalline material, Cobalt, Grain boundary, Yttrium, Doping, Coercivity, Analytical Chemistry (journal), Copper, Condensed matter physics, Oxide, Optoelectronics, Microstructure, Spin (aerodynamics), Quantum dot, Quantum tunnelling, Magnetization, Spin valve, Spin engineering, Spins, Ferromagnetism, Spin polarization, Tunnel magnetoresistance</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O87" t="n">
-        <v>172</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>09538984V34I37</t>
+          <t>09538984V36I30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4145,40 +4145,40 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H88" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I88" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Hubbard model, Wave function, Bethe ansatz, Ansatz, Ground state, Variational Monte Carlo, Lattice (music), Artificial neural network, Statistical physics, Physics, Fermi Gamma-ray Space Telescope, Function (biology), Variational method, Monte Carlo method, Dimension (graph theory), Quantum mechanics, Mathematics, Computer science, Quantum, Combinatorics, Artificial intelligence, Photoelectrolysis, Materials science, Heterojunction, Energetics</t>
+          <t>Creep, Condensed matter physics, Domain wall (magnetism), Perpendicular, Magnetic field, Magnetic domain, Field (mathematics), Physics, Domain (mathematical analysis), Transient (computer programming), Kerr effect, Materials science, Geometry, Magnetization, Thermodynamics, Mathematics, Computer science, Quantum mechanics, Nonlinear system, Monolayer, Semiconductor, Poisson distribution, Semiconductor materials, Poisson's ratio, Chemistry</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Monolayer, Transition metal, Density functional theory, Photocatalysis, Band gap, Chemical physics, Nanotechnology, Oxygen evolution, Water splitting, Optoelectronics, Physical chemistry, Chemistry, Computational chemistry, Thermodynamics, Catalysis, Electrochemistry, Electrolysis, Adsorption, Crystal (programming language), Vacancy defect, Doping, Crystallography, Phase diagram, Magnet, Diagram</t>
+          <t>Nanotechnology, Optoelectronics, Statistics, Band gap, Electronic structure, Direct and indirect band gaps, Fermi level, Semimetal, Phonon, Valence (chemistry), Electron, Thermoelectric effect, Coupling (piping), Nanoscopic scale, Zigzag, Thermoelectric materials, Density functional theory, Composite material, Computational chemistry, NODAL, Type (biology), Line (geometry), Atomic physics, Medicine, Internal medicine</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O88" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>09538984V34I38</t>
+          <t>09538984V36I31</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4187,40 +4187,40 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H89" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I89" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Knot (papermaking), Flexural rigidity, Rigidity (electromagnetism), Persistence length, Monte Carlo method, Writhe, Geometry, DNA, Physics, Bend radius, Probability distribution, Phase space, Monotonic function, Classical mechanics, Mathematics, Bending, Materials science, Mathematical analysis, Quantum mechanics, Chemistry, Molecule, Thermodynamics, Twist, Statistics, Hyperfine structure</t>
+          <t>Silicate glass, Soda lime, Silicate, Ion, Lime, Soda-lime glass, Mineralogy, Materials science, Ion exchange, Chemical engineering, Inorganic chemistry, Chemistry, Metallurgy, Composite material, Engineering, Organic chemistry, Monolayer, Impurity, Boron, Phosphide, Hexagonal crystal system, Condensed matter physics, Coherent potential approximation, Chemical physics, Nanotechnology</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Antiferromagnetism, Ferromagnetism, Condensed matter physics, Scanning tunneling microscope, Atomic orbital, Bilayer, Crystallography, Atomic physics, Membrane, Oxide, Nanotechnology, Chemical engineering, Engineering, Metallurgy, Biochemistry, Ternary operation, Layer (electronics), Phase (matter), Mineralogy, Computer science, Organic chemistry, Benchmark (surveying), Benchmarking, Molecular dynamics, Artificial intelligence</t>
+          <t>Crystallography, Physics, Electronic structure, Catalysis, Epitaxy, Exciton, Non-blocking I/O, Recombination, Layer (electronics), Optoelectronics, Topological insulator, Scattering, Orbit (dynamics), Spin (aerodynamics), Surface states, Spin–orbit interaction, Magnetization, Surface (topology), Plane (geometry), Quantum mechanics, Magnetic field, Geometry, Polymer, Chain (unit), Dynamics (music)</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O89" t="n">
-        <v>181</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09538984V34I39</t>
+          <t>09538984V36I32</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4229,40 +4229,40 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H90" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I90" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Drag, Condensed matter physics, Physics, Graphene, Coulomb, Photon, Parasitic drag, Quantum mechanics, Electron, Mechanics, Eutectic system, Outer core, Inner core, Thermodynamics, Melting point, Diamond anvil cell, Melting curve analysis, Chemistry, Core (optical fiber), Equation of state, Phase (matter), Materials science, High pressure, Crystallography, Microstructure</t>
+          <t>Nanoclusters, Graphite, Atom (system on chip), Hydrogen, Hydrogen atom, Chemical physics, Chemistry, Nanotechnology, Materials science, Organic chemistry, Excited state, Ultrafast laser spectroscopy, Analytical Chemistry (journal), Band gap, Spectroscopy, Electron, Absorption (acoustics), Aqueous solution, Atomic physics, Physical chemistry, Optoelectronics, Physics, Semiconductor, Condensed matter physics, Semiconductor materials</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Skyrmion, Anisotropy, Dynamics (music), Racetrack memory, Boundary (topology), Range (aeronautics), Topological quantum number, Spin (aerodynamics), Mathematical analysis, Mathematics, Computer science, Monatomic ion, Ground state, Density functional theory, Ab initio, Atomic physics, Stacking, Raman spectroscopy, Semiconductor, Band gap, Composite material, Optoelectronics, Optics, Spin valve, Zigzag</t>
+          <t>Antiferromagnetism, Pairing, Hamiltonian (control theory), Quantum entanglement, Topology (electrical circuits), Spin (aerodynamics), Superconductivity, Topological order, Classical XY model, Quantum mechanics, Quantum, Phase transition, Mathematics, Raman spectroscopy, Depolarization, Ferroelectricity, Ergodic theory, Solid solution, Atmospheric temperature range, Phonon, Polarization (electrochemistry), Thermodynamics, Dielectric, Optics, Halide</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O90" t="n">
-        <v>133</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>09538984V34I40</t>
+          <t>09538984V36I33</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4271,40 +4271,40 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H91" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I91" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Materials science, Van der Pauw method, Seebeck coefficient, Thermoelectric effect, Electrical resistivity and conductivity, Thin film, Charge carrier, Thermoelectric materials, Thermal conduction, Nanotechnology, Optoelectronics, Composite material, Hall effect, Thermal conductivity, Quantum dot, Nanostructure, Band gap, Electron, Condensed matter physics, Potential well, Slab, Quantum, Density functional theory, Physics, Quantum mechanics</t>
+          <t>Thermoelectric effect, Condensed matter physics, Nernst effect, Superlattice, Spin (aerodynamics), Thermoelectric materials, Magnetization, Engineering physics, Heat current, Seebeck coefficient, Nernst equation, Work (physics), Magnetic field, Materials science, Physics, Thermal conductivity, Quantum mechanics, Thermodynamics, Electrode, Perspective (graphical), Anisotropy, In situ, Strain (injury), Quantum, Optics</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Graphene, Bilayer graphene, Chemical physics, Molecular physics, Chemistry, Computational chemistry, Length scale, Soft matter, Universality (dynamical systems), Dimensionless quantity, Statistical physics, Scale (ratio), Bond length, Component (thermodynamics), Thermodynamics, Molecule, Mechanics, Algorithm, Computer science, Molecular dynamics, Beryllium, Dissociation (chemistry), Hydrogen, Trapping, Kinetic energy</t>
+          <t>Geometry, Mathematics, Biology, Monolayer, Boosting (machine learning), Phase change, Phase-change material, Interface (matter), Thermal, Chemical engineering, Nanotechnology, Composite material, Computer science, Engineering, Artificial intelligence, Parsing, Hermitian matrix, Skin effect, Pure mathematics, Ferroelectricity, Polarization (electrochemistry), Band gap, Chemistry, Optoelectronics, Dielectric</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O91" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>09538984V34I41</t>
+          <t>09538984V36I34</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4313,40 +4313,40 @@
         </is>
       </c>
       <c r="G92" t="n">
+        <v>36</v>
+      </c>
+      <c r="H92" t="n">
         <v>34</v>
       </c>
-      <c r="H92" t="n">
-        <v>41</v>
-      </c>
       <c r="I92" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Amorphous solid, Argon, Molecular dynamics, Dynamics (music), Materials science, Porosity, Chemical engineering, Composite material, Chemistry, Crystallography, Computational chemistry, Organic chemistry, Physics, Engineering, Acoustics, Focused ion beam, Transmission electron microscopy, Ion beam, Acceleration voltage, Halide, Electron beam-induced deposition, Perovskite (structure), Ion, Beam (structure), Ion beam deposition</t>
+          <t>Energetics, Metastability, Kinetic energy, Grain boundary, Materials science, Thermodynamics, Chemical physics, Chemistry, Physics, Classical mechanics, Metallurgy, Microstructure, Renormalization group, Fermion, Tensor (intrinsic definition), Group (periodic table), Mathematical physics, Functional renormalization group, Theoretical physics, Mathematics, Particle physics, Quantum mechanics, Pure mathematics, Non-equilibrium thermodynamics, Statistical mechanics</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Picosecond, Analytical Chemistry (journal), Optoelectronics, Optics, Nanotechnology, Cathode ray, Electron, Scanning transmission electron microscopy, Inorganic chemistry, Laser, Condensed matter physics, Chemical physics, Quantum dot, Light-emitting diode, Diode, Electroluminescence, Layer (electronics), Superconductivity, X-ray photoelectron spectroscopy, Single crystal, Surface states, Magnetoresistance, Diffraction, Topology (electrical circuits), Magnetic field</t>
+          <t>Statistical physics, Entropy (arrow of time), Laws of thermodynamics, Second law of thermodynamics, Observable, Fluctuation theorem, Quantum thermodynamics, Quantum, Maximum entropy thermodynamics, Joint quantum entropy, Phosphorene, Zigzag, Condensed matter physics, Monolayer, Exciton, Black phosphorus, Hamiltonian (control theory), Anisotropy, Band gap, Semiconductor, Optoelectronics, Nanotechnology, Silicide, Oxide, Chemical engineering</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O92" t="n">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09538984V34I42</t>
+          <t>09538984V36I35</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4355,40 +4355,40 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H93" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I93" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Fermi Gamma-ray Space Telescope, Physics, Semimetal, Fermi surface, Condensed matter physics, Fermi level, Quantum oscillations, Spin (aerodynamics), Topology (electrical circuits), Fermi energy, Coupling (piping), Quantum mechanics, Band gap, Materials science, Mathematics, Superconductivity, Electron, Magnetoresistance, Oscillation (cell signaling), Scattering, Anisotropy, Single crystal, Electrical resistivity and conductivity, Hall effect, Electron scattering</t>
+          <t>Superconductivity, High pressure, Materials science, Condensed matter physics, Physics, Thermodynamics, Gynecology, Chemistry, Humanities, Art, Medicine, Graphene, Superlattice, Dimer, Statistical physics, Nanotechnology, Nuclear magnetic resonance, Topology (electrical circuits), Lattice (music), Photonics, Photonic crystal, Zero-point energy, Realization (probability), Quantum mechanics, Mathematics</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Chemistry, Magnetic field, Nuclear magnetic resonance, Optics, Antiferromagnetism, Parity (physics), Degenerate energy levels, Electronic structure, Atomic physics, Charge (physics), Vibration, Acceptor, Electron transfer, Chemical physics, Quantum, Molecular physics, Molecular vibration, Molecule, Photochemistry, ReaxFF, Melting point, Fullerene, Molecular dynamics, Nucleation, Melting-point depression</t>
+          <t>Combinatorics, Universality (dynamical systems), Scaling, Quantum, Quantum phase transition, Phase transition, Critical phenomena, Scaling law, Tetragonal crystal system, Ferrimagnetism, Antiferromagnetism, Spinel, Octahedron, Neutron diffraction, Crystallography, Jahn–Teller effect, Spin glass, Stoichiometry, Magnetization, Ion, Crystal structure, Magnetic field, Electron, Nuclear physics, Ferroelectricity</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O93" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>09538984V34I43</t>
+          <t>09538984V36I36</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4397,40 +4397,40 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H94" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I94" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Floquet theory, Hermitian matrix, Physics, Winding number, Topology (electrical circuits), Phase diagram, Amplitude, Invariant (physics), Phase (matter), Quantum mechanics, Mathematics, Mathematical analysis, Superconductivity, Crystallography, Condensed matter physics, Chemistry, Relaxation (psychology), Isotropy, Statistical physics, Supercooling, Thermal, Range (aeronautics), Constraint (computer-aided design), Materials science, Thermodynamics</t>
+          <t>Perspective (graphical), Band gap, Quantum, Catalysis, Materials science, Engineering physics, Condensed matter physics, Physics, Chemical physics, Chemistry, Quantum mechanics, Nanotechnology, Mathematics, Organic chemistry, Geometry, Magnonics, Miniaturization, Magnon, Computer science, Field (mathematics), Electronic circuit, Electronic engineering, Electrical engineering, Engineering, Antimony</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Optics, Geometry, Antiferromagnetism, Valence (chemistry), Ferromagnetism, Paramagnetism, Density functional theory, Spin glass, Magnetization, Perovskite (structure), Cluster (spacecraft), Ion, Magnetic susceptibility, Exchange bias, Spin (aerodynamics), Computational chemistry, Magnetic field, Magnetic anisotropy, Elastic recoil detection, Muscovite, Hydrogen, Analytical Chemistry (journal), Stopping power, Recoil, Nuclear reaction analysis</t>
+          <t>Tetragonal crystal system, Crystallography, Scanning tunneling microscope, Anisotropy, Transition metal, Analytical Chemistry (journal), Crystal structure, Optics, Inorganic chemistry, Stacking, Raman spectroscopy, Twist, Polarizability, Polarization (electrochemistry), Symmetry (geometry), Normal mode, Superlattice, Molecular physics, Nuclear magnetic resonance, Vibration, Molecule, Polymerization, Hybrid functional, Density functional theory, Carbon fibers</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O94" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>09538984V34I44</t>
+          <t>09538984V36I37</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4439,40 +4439,40 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H95" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I95" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Degenerate energy levels, Condensed matter physics, Spintronics, Brillouin zone, Physics, Spin polarization, Limiting, Polarization (electrochemistry), Chemistry, Quantum mechanics, Ferromagnetism, Class (philosophy), Materials science, Topology (electrical circuits), Mathematics, Computer science, Combinatorics, Artificial intelligence, Perception, Psychology, Cognitive psychology, Neuroscience, Fluence, Pulsed laser deposition, Superconductivity</t>
+          <t>Superconductivity, Physics, Condensed matter physics, Topology (electrical circuits), Topological insulator, Proximity effect (electron beam lithography), Theoretical physics, Nanotechnology, Materials science, Layer (electronics), Parity (physics), Magnet, Particle physics, Quantum mechanics, Enhanced Data Rates for GSM Evolution, Schottky diode, Graphite, Optoelectronics, Schottky barrier, Power (physics), Electrical engineering, Computer science, Composite material, Engineering, Telecommunications</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Laser, Oxygen, Oxygen pressure, Optoelectronics, Annealing (glass), High-temperature superconductivity, Thin film, Nanotechnology, Optics, Composite material, Current (fluid), Symmetry (geometry), Boundary (topology), Spin (aerodynamics), Rectification, Zero (linguistics), Phenomenon, Boundary value problem, Computation, Energy (signal processing), Symmetry breaking, Magnetic field, Energy current, Field (mathematics), Theoretical physics</t>
+          <t>Cerium oxide, Nanoparticle, Plasmon, Cerium, Plasmonic nanoparticles, Oxide, Chemical engineering, Metallurgy, Janus, Monte Carlo method, Discotic liquid crystal, Liquid crystal, Statistical physics, Optics, Mathematics, Stacking, DNA, Phosphate, Chemistry, Base pair, Biophysics, Atomic orbital, Solvation, Molecule, Crystallography</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O95" t="n">
-        <v>167</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>09538984V34I45</t>
+          <t>09538984V36I38</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4481,40 +4481,40 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H96" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I96" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Thermal conductivity, Boltzmann equation, Condensed matter physics, Thermoelectric effect, Phonon, Semiclassical physics, Thermoelectric materials, Figure of merit, Materials science, Lattice Boltzmann methods, Lattice (music), Boltzmann constant, Atmospheric temperature range, Seebeck coefficient, Thermodynamics, Physics, Quantum mechanics, Optoelectronics, Magnetism, Spintronics, van der Waals force, Spin (aerodynamics), Coupling (piping), Realization (probability), Ab initio</t>
+          <t>Neutron scattering, Interatomic potential, Scattering, Leverage (statistics), Statistical physics, Atom (system on chip), Pair distribution function, Physics, Materials science, Chemical physics, Chemistry, Computer science, Molecular dynamics, Quantum mechanics, Artificial intelligence, Quantum well, Heterojunction, Semiconductor, Ambipolar diffusion, Quantum, Effective mass (spring–mass system), Quantum wire, Band gap, Electro-absorption modulator, Optoelectronics</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Ferromagnetism, Algorithm, Supercooling, Computer science, Plasmon, Wavelength, Surface plasmon polariton, Surface plasmon, Surface photovoltage, Localized surface plasmon, Optics, Spectroscopy, Superconductivity, Pairing, Non-equilibrium thermodynamics, Kerr effect, Hall effect, T-symmetry, Quantum Hall effect, Order (exchange), Symmetry (geometry), Magnetic field, Mathematics, Exciton, Point reflection</t>
+          <t>Condensed matter physics, Electron, Engineering physics, Quantum dot laser, Semiconductor laser theory, Graphene, Dissociation (chemistry), Quantum dot, Catalysis, Graphene quantum dot, Nanoparticle, Redistribution (election), Nanotechnology, Quantum chemical, Electronic structure, Adsorption, Computational chemistry, Molecule, Physical chemistry, Organic chemistry, Monolayer, Molecular beam epitaxy, Transition metal, Epitaxy, Layer (electronics)</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O96" t="n">
-        <v>169</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>09538984V34I46</t>
+          <t>09538984V36I39</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4523,40 +4523,40 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H97" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I97" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Topological insulator, Quasiparticle, Density functional theory, Inversion (geology), Topology (electrical circuits), Band gap, Simple (philosophy), Character (mathematics), Physics, Theoretical physics, Materials science, Quantum mechanics, Mathematics, Geometry, Fabrication, Heat-assisted magnetic recording, Bilayer, Annealing (glass), Magnetization, Coupling (piping), Molecular dynamics, Yield (engineering), Nanotechnology, Magnetization dynamics, Optoelectronics</t>
+          <t>Femtosecond, Polariton, Exciton, Excited state, Ultrashort pulse, Physics, Momentum (technical analysis), Pulse (music), Dynamics (music), Degrees of freedom (physics and chemistry), Atomic physics, Quantum mechanics, Optics, Laser, Graphene, Bilayer graphene, Electron, Astronomical interferometer, Electron optics, Magnetic field, Condensed matter physics, Interferometry, Materials science, Perovskite (structure), Optoelectronics</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Chemistry, Magnetic field, Composite material, Membrane, Computational chemistry, Magnetism, Paramagnetism, Condensed matter physics, Hamiltonian (control theory), Renormalization, Inverse, Hubbard model, Spin (aerodynamics), Thermodynamics, Curie temperature, Curie, Curie constant, Magnetic moment, Ferromagnetism, Curie–Weiss law, Phase (matter), Electronic structure, Chiral anomaly, Weyl semimetal, Boltzmann equation</t>
+          <t>Open-circuit voltage, Energy conversion efficiency, Tin, Nanotechnology, Voltage, Engineering physics, Chemistry, Electrical engineering, Crystallography, Metallurgy, Stishovite, Raman spectroscopy, Luminescence, Analytical Chemistry (journal), Quartz, X-ray photoelectron spectroscopy, Crystal (programming language), Spectral line, Ambient pressure, Photoluminescence, Single crystal, Nuclear magnetic resonance, Coating, Scale (ratio), Compressibility</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O97" t="n">
-        <v>170</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09538984V34I47</t>
+          <t>09538984V36I40</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4565,40 +4565,40 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H98" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I98" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Quadrupole, Condensed matter physics, Magnetic moment, Magnetocrystalline anisotropy, Nuclear magnetic moment, Magnetic anisotropy, Physics, Spin magnetic moment, Chemistry, Atomic physics, Spin polarization, Electron, Magnetic field, Magnetization, Quantum mechanics, Valleytronics, Spintronics, Semiconductor, Ferromagnetism, Curie temperature, Band gap, Magnetic semiconductor, Materials science, Polarization (electrochemistry), Ground state</t>
+          <t>Homology (biology), DNA, Computational biology, Evolutionary biology, Computer science, Biology, Genetics, Gene, Ultrashort pulse, Helicity, Laser, Pulse (music), Spin (aerodynamics), Optical switch, Switching time, Magnetization, Physics, Magnetic storage, Optics, Optoelectronics, Magnetic field, Quantum mechanics, Iridium, Epitaxy, Wafer</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Optoelectronics, Wide-bandgap semiconductor, Dopant, Scanning tunneling microscope, Excitation, Spin (aerodynamics), Spectroscopy, Ionic bonding, Inelastic electron tunneling spectroscopy, Scanning tunneling spectroscopy, Doping, Ion, Nanotechnology, Antiferromagnetism, Tetragonal crystal system, Superconductivity, Inelastic neutron scattering, Magnetic structure, Lattice (music), Crystal structure, Neutron scattering, Crystallography, Scattering, Photodetector, Ferroelectricity</t>
+          <t>Sputtering, Sputter deposition, Yttria-stabilized zirconia, Materials science, Etching (microfabrication), Cubic zirconia, Thin film, Chemistry, Nanotechnology, Composite material, Catalysis, Ceramic, Layer (electronics), Constant (computer programming), Noise (video), Phase (matter), Economic geography, Statistical physics, Geography, Artificial intelligence, Organic chemistry, Rectification, Anharmonicity, Temperature gradient, Asymmetry</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O98" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>09538984V34I48</t>
+          <t>09538984V36I41</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4607,40 +4607,40 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H99" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I99" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Elastomer, Thermal conductivity, Restructuring, Materials science, Thermal, Composite material, Physics, Thermodynamics, Business, Dumbbell, Spins, Magnetic field, Magnet, Condensed matter physics, Statistical physics, Work (physics), Field (mathematics), Classical mechanics, Quantum mechanics, Mathematics, MAJORANA, Pairing, Superconductivity, Fermion, Phase diagram</t>
+          <t>Photoelectrochemistry, Photocatalysis, Materials science, Condensed matter physics, Metal, Chemistry, Physics, Metallurgy, Physical chemistry, Catalysis, Electrochemistry, Electrode, Ultrafast laser spectroscopy, Spectroscopy, Transient (computer programming), Absorption (acoustics), Absorption spectroscopy, Ultraviolet visible spectroscopy, Optoelectronics, Optics, Photochemistry, Computer science, Pesticide, Nanotechnology, Molecule</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Square lattice, Hamiltonian (control theory), Antiferromagnetism, Topology (electrical circuits), Ising model, Phase (matter), Semiclassical physics, Semimetal, Weyl semimetal, Magnetoresistance, Electronic band structure, Magnetism, Fermi level, Shubnikov–de Haas effect, Quantum oscillations, Landau quantization, Fermi surface, Electron, Band gap, Quantum, Ferroelectricity, Magnetic anisotropy, Multiferroics, Diamond anvil cell, Anisotropy</t>
+          <t>Environmental chemistry, Organic chemistry, Biology, Agronomy, Biosensor, Anharmonicity, Phonon, Boltzmann equation, Scattering, Thermal, Thermodynamics, Mineralogy, Quantum mechanics, Thermal conductivity, Stacking, Graphene, Phonon scattering, Bilayer, Bilayer graphene, Thermoelectric materials, Thermoelectric effect, Layer (electronics), Composite material, Nuclear magnetic resonance, Membrane</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O99" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09538984V34I49</t>
+          <t>09538984V36I42</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4649,40 +4649,40 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H100" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I100" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Exchange bias, Materials science, Ferrimagnetism, Antiferromagnetism, Raman spectroscopy, Phase (matter), Magnetism, Particle size, Analytical Chemistry (journal), Nanotechnology, Condensed matter physics, Magnetization, Chemistry, Optics, Physical chemistry, Magnetic field, Semimetal, Thermal conductivity, Phonon, Anisotropy, Thermal conduction, Boltzmann equation, Seebeck coefficient, Scattering, Electron</t>
+          <t>Phonon, Interface (matter), Mode (computer interface), Thermal, Materials science, Chemical physics, Engineering physics, Condensed matter physics, Composite material, Chemistry, Computer science, Physics, Human–computer interaction, Thermodynamics, Magnetization, Point reflection, Orbital magnetization, Non-equilibrium thermodynamics, Spin (aerodynamics), Homogeneous space, Symmetry (geometry), Perpendicular, Charge (physics), Magnetic field, Quantum mechanics</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Band gap, Physics, Thermodynamics, Quantum mechanics, Algorithm, Crystallography, Computer science, Electrostatics, Field (mathematics), Classical mechanics, Mathematics, Modulation (music), Moiré pattern, Charge density wave, Charge density, Acoustics, Ferromagnetism, Coercivity, Paramagnetism, Magnetic anisotropy, Epitaxy, Heterojunction, Neutron diffraction, Neutron reflectometry, Layer (electronics)</t>
+          <t>Magnetic anisotropy, Mathematics, Geometry, Angular momentum, Angular momentum coupling, Orbital angular momentum multiplexing, Orbital angular momentum of light, Orbital motion, Total angular momentum quantum number, Angular momentum of light, Extreme ultraviolet, Azimuthal quantum number, Photon, Undulator, Optics, Radiation, Classical mechanics, Laser, Heterojunction, Graphene, Tribology, Molecular dynamics, Vacancy defect, Atom (system on chip), Slip (aerodynamics)</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O100" t="n">
-        <v>168</v>
+        <v>360</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>09538984V34I50</t>
+          <t>09538984V36I43</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4691,29 +4691,3641 @@
         </is>
       </c>
       <c r="G101" t="n">
+        <v>36</v>
+      </c>
+      <c r="H101" t="n">
+        <v>43</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Physics, Quantum, Theoretical physics, Quantum mechanics, Engineering physics, Group (periodic table), Ion beam, Ion, Optoelectronics, Materials science, Beam (structure), Chemistry, Nanotechnology, Optics, Organic chemistry, Nonlinear system, Spurious relationship, Statistical physics, Mathematical analysis, Mathematics, Anisotropy, Surface energy, Atomic radius, Atom (system on chip), Surface (topology)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>RADIUS, Chemical physics, Cubic crystal system, Binding energy, Condensed matter physics, Crystallography, Geometry, Physical chemistry, Atomic physics, Biexciton, Dephasing, Excitation, Exciton, Quantum dot, Excited state, Population, Two-photon excitation microscopy, Diffusion, Arrhenius equation, Cadmium telluride photovoltaics, Analytical Chemistry (journal), Thermodynamics, Activation energy, Antiferromagnetism, Orthorhombic crystal system</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>9</v>
+      </c>
+      <c r="O101" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>09538984V36I44</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>36</v>
+      </c>
+      <c r="H102" t="n">
+        <v>44</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Superconductivity, Hydrogen, Metal, Ambient pressure, High pressure, Materials science, Metallic hydrogen, Chemistry, Inorganic chemistry, Metallurgy, Condensed matter physics, Thermodynamics, Physics, Organic chemistry, Magnonics, Magnon, Quasiparticle, Quantum, Dissipation, Spin wave, Quantum mechanics, Ferromagnetism, Electron, Spin polarization, Fractionalization</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Order (exchange), Field (mathematics), Spin (aerodynamics), Topology (electrical circuits), Theoretical physics, Mathematics, Political science, Business, Combinatorics, Semimetal, NODAL, Point (geometry), Fermi liquid theory, Fermi Gamma-ray Space Telescope, Geometry, Band gap, Quasiperiodic function, Quasicrystal, Magnetization, Magnetization dynamics, Magnetic field, Anisotropy, Perpendicular, Liquid crystal, Mechanics</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>18</v>
+      </c>
+      <c r="O102" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>09538984V36I45</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>36</v>
+      </c>
+      <c r="H103" t="n">
+        <v>45</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Computer science, Process (computing), Resource (disambiguation), Data science, Biochemical engineering, Chemical space, Machine learning, Artificial intelligence, Drug discovery, Engineering, Chemistry, Casimir effect, Liquid crystal, Planar, Anchoring, Physics, Condensed matter physics, Hamiltonian (control theory), Classical mechanics, Instability, Rod, Shear flow, Distortion (music), Mechanics, Schottky diode</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>van der Waals force, Diode, Materials science, Optoelectronics, Quantum mechanics, Pyrochlore, Algorithm, Crystallography, Phase (matter), Impurity, Chromium, Crystal structure, Lattice (music), Doping, Crystal (programming language), Metallurgy, Degenerate energy levels, Topology (electrical circuits), Topological insulator, Symmetry (geometry), Tight binding, Zero (linguistics), Symmetry breaking, Geometry, Theoretical physics</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>15</v>
+      </c>
+      <c r="O103" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>09538984V36I46</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>36</v>
+      </c>
+      <c r="H104" t="n">
+        <v>46</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Nucleation, Epitaxy, Dimension (graph theory), Process (computing), Statistical physics, Materials science, Development (topology), Computer science, Chemical physics, Nanotechnology, Engineering physics, Chemistry, Physics, Mathematics, Thermodynamics, Layer (electronics), Combinatorics, Thermal conductivity, Thermal management of electronic devices and systems, Thermal, Engineering, Mechanical engineering, Composite material, Octahedron, Tungsten</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Solubility, Density functional theory, Hydrogen, Copper, Crystallography, Metal, Tetrahedron, Physical chemistry, Computational chemistry, Crystal structure, Phase (matter), Factorization, Work (physics), Geometric phase, Molecular dynamics, Quantum mechanics, Algorithm, Pyrazine, Spin crossover, Thin film, Layer by layer, Spin (aerodynamics), Condensed matter physics, Stereochemistry, Theoretical physics</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>7</v>
+      </c>
+      <c r="O104" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>09538984V36I47</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>36</v>
+      </c>
+      <c r="H105" t="n">
+        <v>47</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Semimetal, Condensed matter physics, Physics, Materials science, Band gap, Hamiltonian (control theory), Ionic bonding, Motion (physics), Kondo effect, Equations of motion, Transition metal, Chemistry, Quantum mechanics, Classical mechanics, Ion, Mathematics, Electrical resistivity and conductivity, Manganite, Magnetic circular dichroism, Magnetization, Charge ordering, Spectroscopy, Atmospheric temperature range, Optical conductivity, Spectral line</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Ferromagnetism, Charge (physics), Magnetic field, Extended X-ray absorption fine structure, Bond length, Superconductivity, Crystallography, Molecular geometry, Absorption (acoustics), Crystal structure, Absorption spectroscopy, Molecule, Optics, Composite material, Skyrmion, Spintronics, Magnetization dynamics, Dipole, Topology (electrical circuits), Electrical engineering, Lattice (music), Chemical physics, Perovskite (structure), Perovskite solar cell, Solar cell</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>7</v>
+      </c>
+      <c r="O105" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>09538984V36I48</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>36</v>
+      </c>
+      <c r="H106" t="n">
+        <v>48</v>
+      </c>
+      <c r="I106" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Spin–orbit interaction, Strain (injury), Condensed matter physics, Coupling (piping), Strain engineering, Band gap, Spin (aerodynamics), Physics, Materials science, Chemistry, Thermodynamics, Composite material, Charge density wave, Charge (physics), Quantum mechanics, Superconductivity, Heterojunction, Photoelectric effect, Optoelectronics, Power consumption, Power (physics), Response time, Computer science, Semimetal, Topology (electrical circuits)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Mathematics, Square lattice, RKKY interaction, Square (algebra), Lattice (music), Ferromagnetism, Ising model, Geometry, Vortex, Micromagnetics, Dynamics (music), Magnetic field, Mechanics, Magnetization, Acoustics, Piezoelectricity, Sustainable energy, Engineering physics, Nanotechnology, Engineering, Renewable energy, High entropy alloys, Refractory (planetary science), Chemical stability, Metallurgy</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>8</v>
+      </c>
+      <c r="O106" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>09538984V36I49</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>36</v>
+      </c>
+      <c r="H107" t="n">
+        <v>49</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Raman scattering, Condensed matter physics, Raman spectroscopy, Lattice (music), Coupling (piping), Scattering, Physics, Molecular physics, Materials science, Optics, Superconductivity, Perspective (graphical), High pressure, High-temperature superconductivity, Chemistry, Thermodynamics, Computer science, Composite material, Vortex, Pinning force, Critical current, Symmetry (geometry), T-symmetry, Theoretical physics, Mathematical physics</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Statistical physics, Quantum mechanics, Mathematics, Geometry, Substitution (logic), Ferroelectricity, Dielectric, Property (philosophy), Crystallography, Optoelectronics, Philosophy, Dynamics (music), Syk, Antiferromagnetism, Magnetic anomaly, Geophysics, Graphene, Hydrothermal circulation, Oxide, Reduction (mathematics), Hydrothermal synthesis, Chemical engineering, Nanotechnology, Inorganic chemistry, Organic chemistry</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>15</v>
+      </c>
+      <c r="O107" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>09538984V36I50</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>36</v>
+      </c>
+      <c r="H108" t="n">
+        <v>50</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Condensed matter physics, Photoemission spectroscopy, Spectroscopy, X-ray photoelectron spectroscopy, Electronic structure, Materials science, Chemistry, Physics, Nuclear magnetic resonance, Quantum mechanics, Magnetic refrigeration, Microstructure, Transition metal, Nanotechnology, Metallurgy, Magnetization, Magnetic field, Organic chemistry, Catalysis, Phonon, Boson, Brownian motion, Computer science, Series (stratigraphy), Parallels</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Active matter, Diffusion, Statistical physics, Position (finance), Scale (ratio), Artificial intelligence, Engineering, Mechanical engineering, Subject (documents), Polymer, Composite material, World Wide Web, Core (optical fiber), Shell (structure), Thermal, Thermodynamics, Magnon, Magnet, Topology (electrical circuits), Lattice (music), Hexagonal lattice, Ferromagnetism, Mathematics, Combinatorics, Antiferromagnetism</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>31</v>
+      </c>
+      <c r="O108" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>09538984V37I1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>37</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Frustration, Adiabatic process, Magnetic refrigeration, Condensed matter physics, Demagnetizing field, Refrigeration, Paramagnetism, Geometrical frustration, Magnet, Chemistry, Ternary operation, Magnetic field, Thermodynamics, Physics, Magnetization, Quantum mechanics, Topology (electrical circuits), Materials science, Mathematics, Combinatorics, Adsorption, Binding energy, Metal, Nanoscopic scale, Chemical physics</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Transition metal, Crystallography, Cluster (spacecraft), Nickel, Nanotechnology, Physical chemistry, Atomic physics, Metallurgy, Quantum decoherence, Phonon, Anharmonicity, Non-equilibrium thermodynamics, Coherence (philosophical gambling strategy), Qubit, Statistical physics, Quantum, High-density polyethylene, Linear low-density polyethylene, Composite material, Polymer, Polyethylene, Ultimate tensile strength, Crystallinity, Work (physics), Statistical mechanics</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>15</v>
+      </c>
+      <c r="O109" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>09538984V37I2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>37</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Superexchange, Chemistry, Magnetism, Condensed matter physics, Transition metal, Perovskite (structure), Oxide, Kinetic energy, Context (archaeology), Exchange interaction, Ferromagnetism, Crystallography, Physics, Catalysis, Quantum mechanics, Superconductivity, Phonon, Electron, Engineering physics, Skyrmion, Spintronics, Magnet, Point reflection, Spin-transfer torque, Current (fluid)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Magnetic field, Classical mechanics, Magnetization, Spinodal decomposition, State of matter, Statistical physics, Spinodal, Phase transition, Thermodynamic equilibrium, Phase equilibrium, Dynamic equilibrium, Phase (matter), Thermodynamics, Amorphous solid, Phase change, Materials science, Boson, Mineralogy, Particle physics, Thermal conductivity, Monolayer, Molecular dynamics, Semiconductor, Scattering, Phonon scattering</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>23</v>
+      </c>
+      <c r="O110" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>09538984V37I3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>37</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Phosphorene, Monolayer, Exfoliation joint, Materials science, Raman spectroscopy, Raman scattering, Condensed matter physics, Chemical physics, Nanotechnology, Chemistry, Optics, Graphene, Physics, Crystallography, Exciton, Biexciton, Quantum mechanics, Strain (injury), Electronic structure, Layer (electronics), Mineralogy, Medicine, Honeycomb, Tight binding, Composite material</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bound state, Irradiation, Circular polarization, Molecular physics, Atomic physics, Magnetic field, Electron, Floquet theory, Homeland, Fatherland, Meaning (existential), Sociology, Political science, Linguistics, Epistemology, Philosophy, Law, Hysteresis, Density functional theory, Aluminium, Nitride, Phase (matter), Aluminium nitride, Computational chemistry, Antiferromagnetism</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>12</v>
+      </c>
+      <c r="O111" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>09538984V37I4</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>37</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Fermion, Physics, Boltzmann equation, Chiral anomaly, Context (archaeology), Topology (electrical circuits), Theoretical physics, Quantum mechanics, Multiplet, X-ray photoelectron spectroscopy, Thin film, Analytical Chemistry (journal), Materials science, Chemistry, Nuclear magnetic resonance, Nanotechnology, Environmental chemistry, Spectral line, Boron nitride, Boron, Nitride, Mathematics, Combinatorics, Layer (electronics), Heterojunction</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Photoelectric effect, Band gap, Optoelectronics, Electric field, Stacking, Density functional theory, Electronic structure, Condensed matter physics, Computational chemistry, Phonon, Excitation, Coupling (piping), Femtosecond, Ultrashort pulse, Molecular physics, Laser, Optics, High pressure, Phase transition, Charge (physics), Phase (matter), Thermodynamics, Thermoelectric effect, Thermoelectric materials, Thermal conductivity</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>17</v>
+      </c>
+      <c r="O112" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>09538984V37I5</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>37</v>
+      </c>
+      <c r="H113" t="n">
+        <v>5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Multiferroics, Condensed matter physics, Ferroelectricity, Magnetization, Composite number, Anisotropy, Quadrupole, Phase transition, Materials science, Polarization (electrochemistry), Formalism (music), Physics, Chemistry, Magnetic field, Composite material, Quantum mechanics, Dielectric, Heterojunction, Nanotechnology, Semiconductor, van der Waals force, Electronics, Optoelectronics, Diode, Engineering physics</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Electrical engineering, Engineering, Soft matter, Living matter, Ecology, Living systems, Physical chemistry, Biology, Mott transition, Mott insulator, Crystallography, Superconductivity, Hubbard model, Valleytronics, Field (mathematics), Realm, Geography, Spintronics, Chirality (physics), Topological insulator, Quantum phase transition, Quantum, Quantum phases, Phase (matter), Topology (electrical circuits)</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>20</v>
+      </c>
+      <c r="O113" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>09538984V37I6</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>37</v>
+      </c>
+      <c r="H114" t="n">
+        <v>6</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Boltzmann equation, Phonon, Nanomaterials, Thermal conductivity, Materials science, Thermal, Phonon scattering, Interface (matter), Thermoelectric materials, Scattering, Nanotechnology, Photonics, Condensed matter physics, Physics, Optoelectronics, Optics, Thermodynamics, Dielectric, Thermal conduction, Ferrite (magnet), Relaxation (psychology), Dielectric loss, Thin film, Activation energy, Nuclear magnetic resonance</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Composite material, Chemistry, Power law, Theoretical physics, Mathematics, Molecular dynamics, Interatomic potential, Ab initio, Dynamics (music), Ab initio quantum chemistry methods, Chemical physics, Atomic physics, Molecular physics, Computational chemistry, Quantum mechanics, Molecule, Superconductivity, Pairing, Penetration depth, Anisotropy, Fermi surface, Band gap, Lattice (music), London penetration depth, Fermi level</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>15</v>
+      </c>
+      <c r="O114" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>09538984V37I7</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>37</v>
+      </c>
+      <c r="H115" t="n">
+        <v>7</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Condensed matter physics, Lattice (music), Graphene, Bilayer, van der Waals force, Bilayer graphene, Heterojunction, Materials science, Hexagonal lattice, Physics, Nanotechnology, Chemistry, Quantum mechanics, Molecule, Antiferromagnetism, Toolbox, Computer science, Machine learning, Artificial intelligence, Field (mathematics), Data science, Artificial neural network, Software, Fock space, Ergodicity</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Superselection, Space (punctuation), Theoretical physics, Ergodic theory, Fock state, Observable, Statistical physics, Mathematics, Pure mathematics, Brookite, Indium phosphide, Supercell, Phosphide, Amorphous solid, Anatase, Rutile, Density functional theory, Electronic band structure, Conduction band, Chemical physics, Mineralogy, Computational chemistry, Crystallography, Optoelectronics, Photocatalysis</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>23</v>
+      </c>
+      <c r="O115" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>09538984V37I8</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>37</v>
+      </c>
+      <c r="H116" t="n">
+        <v>8</v>
+      </c>
+      <c r="I116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Observable, Statistical physics, Statistical mechanics, Simple (philosophy), Physics, Density functional theory, Stability (learning theory), Mathematics, Theoretical physics, Computer science, Applied mathematics, Quantum mechanics, Superconductivity, Chemistry, Condensed matter physics, Quantum, Ultracold atom, Metalation, Scanning tunneling microscope, Desorption, Adsorption, X-ray photoelectron spectroscopy, Molecule, Thermal desorption spectroscopy, Crystallography</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Self-assembly, Physical chemistry, Computational chemistry, Stereochemistry, Nanotechnology, Nuclear magnetic resonance, Materials science, Organic chemistry, Antiferromagnetism, Quantum spin liquid, Epitaxy, Thin film, Pulsed laser deposition, Curie temperature, Spin (aerodynamics), Magnetization, Perovskite (structure), Ground state, Ferromagnetism, Spin polarization, Magnetic field, Electron, Thermodynamics, Floquet theory, Topological insulator</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>12</v>
+      </c>
+      <c r="O116" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>09538984V37I9</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>37</v>
+      </c>
+      <c r="H117" t="n">
+        <v>9</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Quantum dot, Quantum technology, Quantum, Nanotechnology, Quantum information science, Engineering physics, Photonics, Quantum information, Quantum nanoscience, Quantum state, Photon, Physics, Materials science, Open quantum system, Optoelectronics, Quantum mechanics, Quantum entanglement, Non-equilibrium thermodynamics, Phonon, Electron, Coupling (piping), Condensed matter physics, Excited state, Relaxation (psychology), Chemistry</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Atomic physics, Thermodynamics, Nuclear physics, Nernst equation, Point reflection, Nernst effect, Valleytronics, Degrees of freedom (physics and chemistry), Spintronics, Ferromagnetism, Amorphous solid, Phase (matter), Degenerate energy levels, Work (physics), Binary number, Dielectric, Zinc, Chemical physics, Phase transition, Crystallography, Glass transition, Atom (system on chip), Limiting, Swap (finance), Polyamorphism</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>19</v>
+      </c>
+      <c r="O117" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>09538984V37I10</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>37</v>
+      </c>
+      <c r="H118" t="n">
+        <v>10</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Pairing, Singlet state, Superconductivity, Josephson effect, Pi Josephson junction, Condensed matter physics, Physics, Quantum, Josephson energy, Diode, Quantum mechanics, Chemistry, Spin crossover, Magnetic circular dichroism, Metal, Crystallography, Octahedron, Chirality (physics), Circular dichroism, Absorption spectroscopy, Absorption (acoustics), Vibrational circular dichroism, Spectral line</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Materials science, Crystal structure, Symmetry breaking, Field (mathematics), Scalar (mathematics), Theoretical physics, Classical mechanics, Mathematics, Geometry, Pure mathematics, Magnetic field, Topological insulator, Vector potential, Magnetic flux, Gauge theory, Ising model, Quantization (signal processing), Topology (electrical circuits), Algorithm, Non-blocking I/O, Thin film, Nanotechnology</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>5</v>
+      </c>
+      <c r="O118" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>09538984V37I11</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>37</v>
+      </c>
+      <c r="H119" t="n">
+        <v>11</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Function (biology), Structure function, Chemistry, Physics, Cathode, Transition metal, Sodium, Redox, Oxide, Inorganic chemistry, Ion, Metal, Materials science, Electrochemistry, Metallurgy, Electrode, Physical chemistry, Catalysis, Chirality (physics), Scanning electron microscope, Selectivity, Spin (aerodynamics), Scanning tunneling microscope, Scanning probe microscopy, Nanotechnology</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Condensed matter physics, Chemical physics, Electron, Optics, Quantum mechanics, Pollution, Environmental chemistry, Environmental science, Ecology, Stacking, Ferroelectricity, van der Waals force, Polar, Polarization (electrochemistry), Dielectric, Nuclear magnetic resonance, Molecule, Biphenylene, Graphene, Hall effect, Interface (matter), Magnetic field, Redistribution (election), Heat flux, Flux (metallurgy)</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>29</v>
+      </c>
+      <c r="O119" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>09538984V37I12</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>37</v>
+      </c>
+      <c r="H120" t="n">
+        <v>12</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Liquid crystal, Homeotropic alignment, Dopant, Materials science, Cholesteric liquid crystal, Dielectric, Doping, Phase (matter), Analytical Chemistry (journal), Optoelectronics, Chemistry, Organic chemistry, Semimetal, Chalcogenide, Condensed matter physics, Phase transition, Semiconductor, Crystal structure, Transition metal, Metal–insulator transition, Diffraction, Metal, Chemical physics, Band gap, Crystallography</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Optics, Physics, Wave function, Winding number, Topology (electrical circuits), Theoretical physics, Quantum mechanics, Mathematics, Mathematical analysis, Combinatorics, Hermitian matrix, Renormalization group, Critical exponent, Scaling, Universality (dynamical systems), Critical phenomena, Curvature, Brillouin zone, Mathematical physics, Geometry, Phonon, Thermal conductivity, van der Waals force, Boltzmann equation, Anisotropy</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>9</v>
+      </c>
+      <c r="O120" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>09538984V37I13</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>37</v>
+      </c>
+      <c r="H121" t="n">
+        <v>13</v>
+      </c>
+      <c r="I121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Spintronics, Vortex, Magnetocrystalline anisotropy, Flexibility (engineering), Physics, Magnetic field, Computer data storage, Nanotechnology, Magnetic storage, Ferromagnetism, Engineering physics, Condensed matter physics, Computer science, Magnetic anisotropy, Materials science, Quantum mechanics, Homogeneous space, Floquet theory, Quantum, Hilbert space, Dynamical systems theory, Statistical physics, Classical mechanics, Mathematics, Geometry</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Chemistry, Planar, Optics, Spectroscopy, Analytical Chemistry (journal), Binary number, Interface (matter), Limit (mathematics), Scale (ratio), Field (mathematics), Phase (matter), Thermodynamics, Mathematical analysis, Surface tension, Conductivity, Terahertz radiation, Optoelectronics, Physical chemistry, Dithiol, Molecular orbital, X-ray photoelectron spectroscopy, Crystallography, Moiety, Spin crossover, Photoemission spectroscopy</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>30</v>
+      </c>
+      <c r="O121" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>09538984V37I14</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>37</v>
+      </c>
+      <c r="H122" t="n">
+        <v>14</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Graphene, Biosensor, Nanotechnology, Scope (computer science), Materials science, Characterization (materials science), Biocompatibility, Computer science, Degrees of freedom (physics and chemistry), Active matter, Brownian motion, Network topology, Topology (electrical circuits), Swarm behaviour, Living systems, Metamaterial, Physics, Statistical physics, Artificial intelligence, Mathematics, Biology, Quantum mechanics, Pairing, Superconductivity, Cuprate</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Condensed matter physics, Critical field, Anisotropy, High-temperature superconductivity, Coherence length, Doping, Superconducting coherence length, Field (mathematics), Biomimetics, Biochemical engineering, Engineering, Magnetism, Electron holography, Engineering physics, Density functional theory, Adsorption, Monolayer, Chemistry, Scanning tunneling microscope, Raman spectroscopy, Hydrogen, Chemical physics, Computational chemistry, Physical chemistry, Gaussian</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>15</v>
+      </c>
+      <c r="O122" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>09538984V37I15</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>37</v>
+      </c>
+      <c r="H123" t="n">
+        <v>15</v>
+      </c>
+      <c r="I123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Metastability, Phase transition, State of matter, Physics, Entropy (arrow of time), Parameter space, Statistical physics, Theoretical physics, Condensed matter physics, Quantum mechanics, Mathematics, Peering, Perspective (graphical), Perovskite (structure), Materials science, Engineering physics, Astrobiology, Nanotechnology, Chemistry, Computer science, The Internet, World Wide Web, Crystallography, Topological insulator, Homogeneous space</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Topological order, Topology (electrical circuits), Quantum, Topological degeneracy, Symmetry protected topological order, Geometry, Heterojunction, Ferromagnetism, X-ray photoelectron spectroscopy, Raman spectroscopy, Thin film, Epitaxy, Photoemission spectroscopy, Crystallinity, Optoelectronics, Optics, Nuclear magnetic resonance, Composite material, Coupling (piping), Kondo effect, Spin–orbit interaction, Relaxation (psychology), Magnetism, Spin (aerodynamics), Superconductivity</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>18</v>
+      </c>
+      <c r="O123" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>09538984V37I16</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>37</v>
+      </c>
+      <c r="H124" t="n">
+        <v>16</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Mesoscopic physics, Physics, Quantum dot, Quantum, Thermoelectric effect, Context (archaeology), Photon, Nanotechnology, Quantum mechanics, Materials science, Perovskite (structure), Passivation, Halide, Light-emitting diode, Photodetector, Nanocrystal, Photoluminescence, Optoelectronics, Doping, Chemistry, Condensed matter physics, Magnetization, Coupling (piping), Magnetic field, van der Waals force</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Anisotropy, Magnetic anisotropy, Polarization density, Engineering physics, Chirality (physics), Field (mathematics), Order (exchange), Asymmetry, Phase (matter), Chemical physics, Theoretical physics, Symmetry breaking, Chiral symmetry breaking, Mathematics, Formamidinium, Quantum efficiency, Crystallization, Crystallinity, Photochemistry, Chemical engineering, Crystallography, Layer (electronics), Organic chemistry, Physical constant, Superconductivity</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>15</v>
+      </c>
+      <c r="O124" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>09538984V37I17</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>37</v>
+      </c>
+      <c r="H125" t="n">
+        <v>17</v>
+      </c>
+      <c r="I125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Physics, Atom (system on chip), Quantum, Engineering physics, Chemical physics, Quantum mechanics, Computer science, Superconductivity, Metal, Chemistry, Nanotechnology, Materials science, Condensed matter physics, Metallurgy, Polarization (electrochemistry), Ferroelectricity, Miniaturization, Microstructure, Statistical physics, Optoelectronics, Vicinal, Electronic structure, Angle-resolved photoemission spectroscopy, Density functional theory, Relaxation (psychology)</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Surface (topology), Surface reconstruction, X-ray photoelectron spectroscopy, Molecular physics, Computational chemistry, Geometry, Nuclear magnetic resonance, Brillouin zone, Fermi level, Thin film, Band gap, Fermi surface, Surface states, Photoemission spectroscopy, Density of states, Metal–insulator transition, Optical conductivity, Mott insulator, Electronic band structure, Electron, Graphene, Phase transition, Room-temperature superconductor, Valence (chemistry), Transition temperature</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>13</v>
+      </c>
+      <c r="O125" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>09538984V37I18</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>37</v>
+      </c>
+      <c r="H126" t="n">
+        <v>18</v>
+      </c>
+      <c r="I126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Triboelectric effect, Flexibility (engineering), Electronics, Nanotechnology, Energy harvesting, Wearable technology, Scalability, Computer science, Engineering, Materials science, Wearable computer, Electrical engineering, Energy (signal processing), Embedded system, Crystallographic defect, Oxide, Curse of dimensionality, Point (geometry), Condensed matter physics, Physics, Geometry, Artificial intelligence, Metallurgy, Mathematics, Antiferromagnetism</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Tunnel magnetoresistance, Spintronics, Tunnel junction, Ferromagnetism, Magnetoresistance, Ferrimagnetism, Quantum tunnelling, Spin polarization, Magnetic field, Quantum mechanics, Magnetization, Electron, Frustration, Skyrmion, RKKY interaction, Geometrical frustration, Heisenberg model, Magnet, Phase diagram, Chemistry, Phase (matter), Fermi liquid theory, Renormalization group, Fermi Gamma-ray Space Telescope, Perturbation theory (quantum mechanics)</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>28</v>
+      </c>
+      <c r="O126" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>09538984V37I19</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>37</v>
+      </c>
+      <c r="H127" t="n">
+        <v>19</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Polaron, Spin (aerodynamics), Physics, Chirality (physics), Electron, Condensed matter physics, Context (archaeology), Charge carrier, Helicene, Quantum, Chemical physics, Chemistry, Quantum mechanics, Molecule, Symmetry breaking, Chiral symmetry breaking, Kinetic isotope effect, Isotope, Diffusion, Ab initio, Hydrogen, Arrhenius equation, Kinetic energy, Path integral formulation, Thermodynamics</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Atomic physics, Physical chemistry, Deuterium, Activation energy, Realization (probability), Primer (cosmetics), Nanotechnology, Statistical physics, Materials science, Mathematics, Graphene, Wavelength, Optoelectronics, Optics, Heterojunction, Hydrogen sulfide, Oxide, MXenes, Carbon monoxide, Nanomaterials, Hazardous waste, Ferroelectricity, Monolayer, Dielectric, Berry connection and curvature</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>20</v>
+      </c>
+      <c r="O127" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>09538984V37I20</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>37</v>
+      </c>
+      <c r="H128" t="n">
+        <v>20</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Chalcogen, Dopant, Nitride, Polaron, Chemistry, Doping, Metastability, Shallow donor, Electron, Materials science, Crystallography, Physics, Optoelectronics, Nanotechnology, Terahertz radiation, Spectroscopy, Polariton, Phonon, Quantum, Condensed matter physics, Ultrashort pulse, Quantum mechanics, Laser, Silicene, Germanene</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Electric field, Bilayer graphene, Bilayer, Band gap, Quantum Hall effect, Graphene, Membrane, Interatomic potential, Ternary operation, Transferability, Lamellar structure, Molecular dynamics, Atomic units, Ultimate tensile strength, Metallurgy, Computer science, Computational chemistry, Machine learning, Characterization (materials science), Transmission electron microscopy, Energy filtered transmission electron microscopy, Scanning confocal electron microscopy, Scanning transmission electron microscopy, Polymer characterization, Nanostructure</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>17</v>
+      </c>
+      <c r="O128" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>09538984V37I21</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>37</v>
+      </c>
+      <c r="H129" t="n">
+        <v>21</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Quasiparticle, van der Waals force, Inverse, Density functional theory, Physics, Hybrid functional, Quantum mechanics, Statistical physics, Range (aeronautics), Chemistry, Molecule, Mathematics, Materials science, Superconductivity, Rare earth, Condensed matter physics, Orientation (vector space), Metal, Electronic structure, Crystallography, Geometry, Metallurgy, Thermoelectric effect, Graphene, Adsorption</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Spin (aerodynamics), Chemical physics, Conductance, Nanotechnology, Computational chemistry, Physical chemistry, Thermodynamics, Organic chemistry, Phosphorene, Gapless playback, Quantum tunnelling, Magnetoresistance, Ferromagnetism, Hamiltonian (control theory), Magnetic field, Ballistic conduction, Band gap, Electron, Crystal twinning, Zigzag, Magnetic moment, Stacking, Diffraction, Moment (physics), Scattering</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>7</v>
+      </c>
+      <c r="O129" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>09538984V37I22</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>37</v>
+      </c>
+      <c r="H130" t="n">
+        <v>22</v>
+      </c>
+      <c r="I130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Physics, Condensed matter physics, Magnetic field, Zeeman effect, Perpendicular, Orbit (dynamics), Spin (aerodynamics), Charge (physics), BETA (programming language), Electric field, Quantum mechanics, Geometry, Nanoparticle, Dissociation (chemistry), Nanotechnology, Chemistry, Materials science, Chemical engineering, Physical chemistry, Engineering, Hamiltonian (control theory), Nanowire, Spin–orbit interaction, Semiconductor, Coupling (piping)</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Quantum wire, Rashba effect, Ferromagnetism, Electron, Spintronics, Phase transition, Exponent, Critical exponent, Phase (matter), Symmetry (geometry), Quantum, Critical phenomena, Statistical physics, Topology (electrical circuits), Doping, Octahedron, Thin film, Colossal magnetoresistance, Crystallography, Magnetoresistance, Crystal structure, Superconductivity, Current (fluid), High-temperature superconductivity, Ferrimagnetism</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>8</v>
+      </c>
+      <c r="O130" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>09538984V37I23</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>37</v>
+      </c>
+      <c r="H131" t="n">
+        <v>23</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Pseudopotential, Plane wave, Hamiltonian (control theory), Electronic band structure, Physics, Theoretical physics, Band gap, Quantum mechanics, Plane (geometry), Statistical physics, Mathematics, Geometry, Antiferromagnetism, Heisenberg model, Condensed matter physics, Materials science, Crystallography, Chemistry, Covalent bond, Spintronics, Molecule, Cobalt, Porphyrin, Scanning tunneling microscope, Chemical physics</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Quantum tunnelling, Spins, Annealing (glass), Nanotechnology, Inorganic chemistry, Photochemistry, Ferromagnetism, Organic chemistry, Optoelectronics, Graphene, Conductance, Inverse, Conductivity, Nanostructure, Electrical resistivity and conductivity, Graph, Algorithm, Topology (electrical circuits), Combinatorics, Nanoparticle, Spectroscopy, Valence (chemistry), Synchrotron, Electronic structure, X-ray absorption spectroscopy</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>20</v>
+      </c>
+      <c r="O131" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>09538984V37I24</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>37</v>
+      </c>
+      <c r="H132" t="n">
+        <v>24</v>
+      </c>
+      <c r="I132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Rheology, Polymer, Materials science, Nanotechnology, Polymer science, Composite material, Polyelectrolyte, Titration, Titration curve, Chemistry, Monomer, Electrostatics, Chemical physics, Thermodynamics, Sequence (biology), Computational chemistry, Physical chemistry, Physics, Organic chemistry, Josephson effect, Supercurrent, Condensed matter physics, Superconductivity, Zeeman effect, Interference (communication)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Magnetic field, Quantum mechanics, Telecommunications, Quasiparticle, Coulomb, Antiferromagnetism, Fermi level, Spin (aerodynamics), Electron, Channel (broadcasting), Scattering, Impurity, Dirac fermion, Dirac delta function, Dirac (video compression format), Fermion, DNA, Sanger sequencing, Absorbance, Accelerated aging, Relative humidity, Bromide, DNA sequencing, Chromatography, Biochemistry</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>6</v>
+      </c>
+      <c r="O132" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>09538984V37I25</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>37</v>
+      </c>
+      <c r="H133" t="n">
+        <v>25</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Ferroelectricity, Condensed matter physics, van der Waals force, Spintronics, Ferroelasticity, Materials science, Electromechanics, Non-volatile memory, Polarization (electrochemistry), Ferromagnetism, Dielectric, Physics, Optoelectronics, Chemistry, Quantum mechanics, Magnetization, Antiferromagnetism, Spin (aerodynamics), Spin polarization, Magnetization dynamics, Symmetry (geometry), Magnetic field, Boson, Quasiparticle, Component (thermodynamics)</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Context (archaeology), Quantum, Fermion, Goldstone boson, Ultracold atom, Pairing, Theoretical physics, Superconductivity, Graphene, Heterojunction, Oxide, Nanotechnology, Nanoclusters, Substrate (aquarium), Metal, Atomic units, Electronic structure, Catalysis, Electronics, Physical chemistry, Computational chemistry, Metallurgy, Ohmic contact, Electron mobility, Quantum well</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>14</v>
+      </c>
+      <c r="O133" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>09538984V37I26</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>37</v>
+      </c>
+      <c r="H134" t="n">
+        <v>26</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Crystallization, Nucleation, Materials science, Chemical physics, Anisotropy, Phase (matter), Crystal (programming language), Liquid crystal, Crystal growth, Crystallography, Crystallization of polymers, Chemistry, Physics, Organic chemistry, Optics, Computer science, Electron mobility, Semiconductor, Charge carrier, Mobility model, Photoelectric effect, Transistor, Electronics, Engineering physics, Nanotechnology</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Optoelectronics, Electrical engineering, Telecommunications, Engineering, Voltage, Quantum mechanics, Pulsed laser deposition, Hall effect, Thin film, Deposition (geology), Analytical Chemistry (journal), Electrical resistivity and conductivity, Interpolation (computer graphics), Constant (computer programming), Binary number, Exponent, Function (biology), Invariant (physics), Mathematics, Mathematical analysis, Statistical physics, Mathematical physics, Classical mechanics, Dumbbell, Mass transport</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>19</v>
+      </c>
+      <c r="O134" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>09538984V37I27</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>37</v>
+      </c>
+      <c r="H135" t="n">
+        <v>27</v>
+      </c>
+      <c r="I135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Context (archaeology), Task (project management), Plan (archaeology), Nanotechnology, Computer science, Management science, Materials science, Engineering, Systems engineering, Quantum entanglement, Phase transition, Fermion, Physics, Quantum phase transition, Condensed matter physics, Transition (genetics), Phase (matter), Quantum mechanics, Statistical physics, Chemistry, Quantum, Diamondoid, Perspective (graphical), Scale (ratio), Molecular dynamics</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Artificial intelligence, Computational chemistry, Moiré pattern, Atomic units, Slip (aerodynamics), Optics, Mineralogy, Thermodynamics, Spintronics, Topology (electrical circuits), Gapless playback, Doping, Semiconductor, Topological insulator, Ferromagnetism, Topological order, Spin (aerodynamics), Mathematics, Optoelectronics, Conductance, Quantization (signal processing), Insulator (electricity), Formalism (music), Terminal (telecommunication), Non-equilibrium thermodynamics</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>11</v>
+      </c>
+      <c r="O135" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>09538984V37I28</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>37</v>
+      </c>
+      <c r="H136" t="n">
+        <v>28</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Condensed matter physics, Nonlinear system, Scanning tunneling microscope, Physics, Magnetic field, Bilayer graphene, Quantum tunnelling, Graphene, Strain (injury), Lattice (music), Materials science, Quantum mechanics, Hydrogen bond, Molecule, Chemistry, Monolayer, Chemical physics, Wetting, Binding energy, Hydrogen, Hydration energy, Nanotechnology, Computational chemistry, Thermodynamics, Organic chemistry</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Atomic physics, Porosity, Silicone, Fumed silica, Solvent, Chemical engineering, Blowing agent, Composite material, Polyurethane, Antiferromagnetism, Ground state, Ferromagnetism, Vacancy defect, Density functional theory, Spin (aerodynamics), Spin–orbit interaction, Magnetic anisotropy, Crystallography, Magnetization, Doping, Acceptor, Dopant, Impurity, Shallow donor, Valence (chemistry)</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>7</v>
+      </c>
+      <c r="O136" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>09538984V37I29</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>37</v>
+      </c>
+      <c r="H137" t="n">
+        <v>29</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Semiconductor, Band gap, Luminescence, Materials science, Semiconductor materials, Optoelectronics, Identification (biology), Nanotechnology, Engineering physics, Physics, Biology, Monte Carlo method, Statistical physics, Particle (ecology), Thermodynamics, Mathematics, Geology, Statistics, Low-energy electron microscopy, Electron microscope, Microscopy, Chemical physics, Energy filtered transmission electron microscopy, Chemistry, Crystallography</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Transmission electron microscopy, Optics, Scanning transmission electron microscopy, Viscosity, Separation (statistics), Phase (matter), Thin film, Mineralogy, Analytical Chemistry (journal), Composite material, Chromatography, Anharmonicity, Thermal, Resonance (particle physics), Condensed matter physics, Thermal resistance, Quantum mechanics, Coolant, Hotspot (geology), Thermal conduction, Thermal conductivity, Heat sink, Mechanics, Spreading resistance profiling, Computer science</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>15</v>
+      </c>
+      <c r="O137" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>09538984V37I30</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>37</v>
+      </c>
+      <c r="H138" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Sampling (signal processing), Nanotechnology, Chemistry, Computer science, Materials science, Telecommunications, Condensed matter physics, Hall effect, Spin (aerodynamics), Physics, Quantum mechanics, Electrical resistivity and conductivity, Thermodynamics, Ultrashort pulse, Nonlinear system, Absorption (acoustics), Quantum dot, Quantum, Optics, Laser, Josephson effect, Superconductivity, Pi Josephson junction, Transverse plane, Symmetry (geometry)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Geometry, Thermalisation, Homogeneous, Vibration, Classical mechanics, Quantum electrodynamics, Statistical physics, Quinary, Lanczos resampling, Tight binding, Entropy (arrow of time), Configuration entropy, Solid solution, Electronic structure, Computational chemistry, Angle-resolved photoemission spectroscopy, Fermi surface, Photoemission spectroscopy, Electronic band structure, Fermi level, Scattering, Electron, X-ray photoelectron spectroscopy, Nuclear magnetic resonance, Andreev reflection</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>11</v>
+      </c>
+      <c r="O138" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>09538984V37I31</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>37</v>
+      </c>
+      <c r="H139" t="n">
+        <v>31</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Topology (electrical circuits), Physics, Materials science, Theoretical physics, Mathematics, Combinatorics, Coulomb, Quantum mechanics, Statistical physics, Electronic correlation, Exchange interaction, Electron, Nanotechnology, Characterization (materials science), Catalysis, Fuel cells, Biochemical engineering, Renewable energy, Computer science, Chemistry, Engineering, Chemical engineering, Electrical engineering, Magnet, Superconductivity</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Superconducting magnet, Condensed matter physics, Engineering physics, Spin crossover, Monolayer, Spin transition, Spin (aerodynamics), Molecule, Spin states, Chemical physics, Thermodynamics, Quantum tunnelling, Conductance, Coupling (piping), Quantum entanglement, Displacement (psychology), Voltage, Quantum dot, Quantum, Parity (physics), Hermitian matrix, Reciprocity (cultural anthropology), Reciprocal, Reciprocal lattice, Quartic function</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>11</v>
+      </c>
+      <c r="O139" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>09538984V37I32</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>37</v>
+      </c>
+      <c r="H140" t="n">
+        <v>32</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Graphene, Neutron, Radiation damage, Nanotechnology, Curse of dimensionality, Radiation, Fusion power, Materials science, Computer science, Physics, Nuclear engineering, Nuclear physics, Plasma, Artificial intelligence, Magnetism, Quantum, Moiré pattern, Condensed matter physics, Quantum mechanics, Injector, Electron, Fermi gas, Quantum point contact, Asymmetry, Heterojunction</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Spin polarization, Spin (aerodynamics), Spintronics, Polarization (electrochemistry), Detector, Semiconductor, Quantum well, Chemistry, Optoelectronics, Ferromagnetism, Optics, Weyl semimetal, Berry connection and curvature, Fermi Gamma-ray Space Telescope, Semimetal, Symmetry (geometry), Fermi level, Curvature, Geometric phase, Geometry, Band gap, Mathematics, Semiclassical physics, Quantum phase transition, Wave function</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>9</v>
+      </c>
+      <c r="O140" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>09538984V37I33</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>37</v>
+      </c>
+      <c r="H141" t="n">
+        <v>33</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Transformative learning, Transdisciplinarity, Autonomy, Adaptability, Living systems, Flexibility (engineering), Nanotechnology, Engineering ethics, Evolvability, Computer science, Resilience (materials science), Data science, Scalability, Management science, Sociology, Engineering, Artificial intelligence, Ecology, Political science, Social science, Aperiodic graph, Phonon, Superlattice, Condensed matter physics, Coherence (philosophical gambling strategy)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Thermal conduction, Mixing (physics), Coherence length, Transmission (telecommunications), Materials science, Physics, Chemistry, Quantum mechanics, Superconductivity, Telecommunications, MAJORANA, Capacitor, Resistor, Bound state, Quantum, Optoelectronics, Voltage, Graphene, Monolayer, Lattice (music), Bilayer graphene, Ferromagnetism, Curie temperature, Heisenberg model, Bipartite graph</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>5</v>
+      </c>
+      <c r="O141" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>09538984V37I34</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>37</v>
+      </c>
+      <c r="H142" t="n">
         <v>34</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Spintronics, Condensed matter physics, Magnetic anisotropy, Pseudopotential, Magnetization, Anisotropy, Materials science, Context (archaeology), Magnetic moment, Electronic structure, Ferromagnetism, Magnetic field, Physics, Optics, Doping, Nanotechnology, Chemistry, Optoelectronics, Molecular dynamics, Trajectory, Ab initio, Field (mathematics), Statistical physics, Motion (physics), Series (stratigraphy)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Dynamics (music), Work (physics), Chemical physics, Computational chemistry, Classical mechanics, Thermodynamics, Spinel, Volume (thermodynamics), Inverse, Mineralogy, Metallurgy, Geometry, Mathematics, Skyrmion, Multiferroics, Surface (topology), Magnetoelectric effect, Ferroelectricity, Monolayer, Metal, Band gap, Inorganic chemistry, Antiferromagnetism, Heterojunction, Magnetism</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>7</v>
+      </c>
+      <c r="O142" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>09538984V37I35</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>37</v>
+      </c>
+      <c r="H143" t="n">
+        <v>35</v>
+      </c>
+      <c r="I143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Surface (topology), Chemistry, Nanotechnology, Sociology, Engineering physics, Materials science, Physics, Mathematics, Moiré pattern, Superlattice, Graphene, Condensed matter physics, Optoelectronics, Optics, Binary number, Metal, Mass transport, Atomic mass, Binary alloy, Atomic physics, Metallurgy, Alloy, Copolymer, PEG ratio, Amphiphile</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Polymer chemistry, Chemical engineering, Molecular dynamics, Polymer science, Polymer, Computational chemistry, Composite material, Engineering, Doping, Density functional theory, Ionic bonding, Ion, Electronic structure, Absorption (acoustics), Band gap, Absorption spectroscopy, Crystallography, Chemical physics, Hamiltonian (control theory), Superconductivity, Topology (electrical circuits), Quantum mechanics, Perovskite (structure), Ground state, Magnetic susceptibility</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>8</v>
+      </c>
+      <c r="O143" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>09538984V37I36</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>37</v>
+      </c>
+      <c r="H144" t="n">
+        <v>36</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Electron, Fermi liquid theory, Physics, Flow (mathematics), Condensed matter physics, Momentum (technical analysis), Transport phenomena, Current (fluid), Fermi Gamma-ray Space Telescope, Mechanics, Quantum mechanics, Monolayer, Thermoelectric effect, Thermal conductivity, Thermal stability, Thermoelectric materials, Materials science, Band gap, Figure of merit, Structural stability, Semiconductor, Thermal, Nanotechnology, Chemical physics, Chemistry</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Optoelectronics, Thermodynamics, Composite material, Engineering, Quasiperiodic function, Quasicrystal, Scanning tunneling microscope, Crystallography, Substrate (aquarium), Quasiperiodicity, Density functional theory, Potassium, Adsorption, Electron diffraction, Computational chemistry, Diffraction, Physical chemistry, Optics, Berry connection and curvature, Berry, Nonlinear system, Hall effect, Dipole, Curvature, Geometric phase</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>9</v>
+      </c>
+      <c r="O144" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>09538984V37I37</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>37</v>
+      </c>
+      <c r="H145" t="n">
+        <v>37</v>
+      </c>
+      <c r="I145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Management science, Engineering, Magnetic refrigeration, Refrigerant, Refrigeration, Liquefaction, Materials science, Intermetallic, Rare earth, Thermodynamics, Metallurgy, Magnetization, Alloy, Magnetic field, Heat exchanger, Physics, Superconductivity, MAJORANA, Field (mathematics), Nanowire, Nanotechnology, Engineering physics, Condensed matter physics, Quantum mechanics, Mathematics</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Non-equilibrium thermodynamics, Entropy production, Statistical physics, Fluctuation-dissipation theorem, Entropy (arrow of time), Exponent, Dissipation, Power law, Brownian motion, Scaling, Topological insulator, Quantum phase transition, Topological order, Phase transition, Hamiltonian (control theory), Quantum, Strain engineering, Topology (electrical circuits), Quasiperiodic function, Delocalized electron, Fibonacci number, Anderson localization, Quasicrystal, Diagonal, Quasiperiodicity</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>13</v>
+      </c>
+      <c r="O145" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>09538984V37I38</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>37</v>
+      </c>
+      <c r="H146" t="n">
+        <v>38</v>
+      </c>
+      <c r="I146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Microrheology, Viscoelasticity, Mean squared displacement, Diffusion, Rheology, Shear (geology), Displacement (psychology), Schottky barrier, van der Waals force, Ohmic contact, Heterojunction, Stacking, Band gap, Absorption (acoustics), Schottky diode, Zigzag, Graphene, Deformation (meteorology), Qubit, Anisotropy, Condensed matter physics, Quantum dot, Physics, Quantum, Materials science</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Nanotechnology, Geometry, Optics, Quantum mechanics, Eutectic system, Ternary operation, Alloy, Chemistry, Kinetic energy, Thermodynamics, Effective diffusion coefficient, Capillary action, Analytical Chemistry (journal), Metallurgy, Chromatography, Antiferromagnetism, Ferromagnetism, Orthorhombic crystal system, Doping, High entropy alloys, Phase (matter), Topological insulator, Surface states, Photoemission spectroscopy, Angle-resolved photoemission spectroscopy</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>14</v>
+      </c>
+      <c r="O146" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>09538984V37I39</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>37</v>
+      </c>
+      <c r="H147" t="n">
+        <v>39</v>
+      </c>
+      <c r="I147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Superlattice, Bilayer graphene, Graphene, Electric field, Perpendicular, Band gap, Heterojunction, Doping, Brillouin zone, Electronic band structure, Electronic structure, Angle-resolved photoemission spectroscopy, Effective mass (spring–mass system), Fermi level, Fermi surface, Photoemission spectroscopy, Monolayer, Auxetics, Nanomechanics, Density functional theory, Ultimate tensile strength, Absorption (acoustics), Ultraviolet, Quadrupole, Dipole</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Lattice (music), Nanoparticle, Dispersion (optics), Plasmon, Coupling (piping), Soft matter, Asymmetry, Colloid, Colloidal particle, Langevin dynamics, Phase diagram, Phase transition, Pair potential, Phase (matter), Binary number, Seebeck coefficient, Gapless playback, Thermoelectric effect, Thermoelectric materials, Semiconductor, Boltzmann constant, Boltzmann equation, Scattering, Vacancy defect, Ion</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>12</v>
+      </c>
+      <c r="O147" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>09538984V37I40</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>37</v>
+      </c>
+      <c r="H148" t="n">
+        <v>40</v>
+      </c>
+      <c r="I148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Quantum, Heisenberg model, Chain (unit), Key (lock), Quantum technology, Quantum phases, Spin (aerodynamics), Ground state, Scanning tunneling microscope, Degrees of freedom (physics and chemistry), Quantum tunnelling, Quantum spin liquid, Charge (physics), Perspective (graphical), Artificial neural network, Limiting, Deep learning, Field (mathematics), Dual (grammatical number), Raman scattering, Electron, X-ray Raman scattering, Raman spectroscopy, Fermi Gamma-ray Space Telescope, Topology (electrical circuits)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Scattering, Momentum (technical analysis), Spectrum (functional analysis), Catalysis, Methanol, Overlayer, Oxide, Selectivity, Inverse, Heterogeneous catalysis, Component (thermodynamics), Monolayer, Photocatalysis, Water splitting, Ternary operation, Hydrogen production, Semiconductor, Band gap, Photocatalytic water splitting, Oxygen evolution, Semimetal, Surface states, Degenerate energy levels, Hamiltonian (control theory), Fermi level</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>14</v>
+      </c>
+      <c r="O148" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>09538984V37I41</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>37</v>
+      </c>
+      <c r="H149" t="n">
+        <v>41</v>
+      </c>
+      <c r="I149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Water splitting, Nanoscopic scale, Ceramic, Material Design, Hydrogen, Strain engineering, Multiscale modeling, Stability (learning theory), Energy conversion efficiency, Germanene, Nucleation, Monolayer, Honeycomb structure, Metal, Honeycomb, Polymer, Mean squared displacement, Relaxation (psychology), Neutron spin echo, Intermolecular force, Molecular dynamics, Center of mass (relativistic), Diffusion, Reptation, Hall effect</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Spintronics, Bilayer, Quantum Hall effect, Thermal Hall effect, Spin Hall effect, Nonlinear system, Landau quantization, Superconductivity, Superconducting wire, Magnetic field, Electric current, Maxwell's equations, Current (fluid), Perpendicular, Superconducting magnetic energy storage, Electric field, Crystallite, Microstructure, Scanning electron microscope, Thermal, Diffraction, Exothermic reaction, Electron microscope, Lattice (music), Boosting (machine learning)</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>9</v>
+      </c>
+      <c r="O149" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>09538984V37I42</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>37</v>
+      </c>
+      <c r="H150" t="n">
+        <v>42</v>
+      </c>
+      <c r="I150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Spintronics, Coupling (piping), Electron, Interface (matter), Efficient energy use, Perspective (graphical), Spin (aerodynamics), Nanoelectronics, Frontier, SPARK (programming language), Set (abstract data type), Selection (genetic algorithm), Catalysis, Cobalt, Nickel, Hydrogen, Transition metal, Density functional theory, Doping, Adsorption, Kondo effect, Quantum phase transition, Quasiparticle, Quantum critical point, Kondo insulator</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Quantum phases, Quantum, Topology (electrical circuits), Graphene, Electric field, Fermi energy, Fermi level, Realization (probability), Charge carrier, Surface states, Charge (physics), Anharmonicity, Phonon, Raman scattering, Raman spectroscopy, Laser linewidth, Scattering, Lattice (music), Thermoelectric effect, MAJORANA, Pairing, Superconductivity, Fermion, Enhanced Data Rates for GSM Evolution, Chain (unit)</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>11</v>
+      </c>
+      <c r="O150" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>09538984V37I43</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>37</v>
+      </c>
+      <c r="H151" t="n">
+        <v>43</v>
+      </c>
+      <c r="I151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Magnonics, Focus (optics), Metamaterial, Coupling (piping), Magnon, Spin pumping, Spintronics, Spin (aerodynamics), Ferromagnetic resonance, Spinplasmonics, Spin polarization, Spin engineering, Ferromagnetism, Rectification, Controllability, Anharmonicity, Thermal, Lattice (music), Work (physics), Rectifier (neural networks), Hexagonal crystal system, Hexagonal phase, Perovskite (structure), Phase (matter), Hexagonal lattice</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Diffraction, Eigenvalues and eigenvectors, Scattering, Observable, Boltzmann equation, Boltzmann constant, Phonon, Operator (biology), Sound (geography), Cooper pair, Vortex, Superconductivity, Electron, Electric field, Penetration depth, Type-II superconductor, Charge density, Electron pair, Annealing (glass), Tetragonal crystal system, Thin film, Dielectric, Heterojunction, Electrical resistivity and conductivity, Solar cell</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>8</v>
+      </c>
+      <c r="O151" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>09538984V37I44</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>37</v>
+      </c>
+      <c r="H152" t="n">
+        <v>44</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Thermoelectric generator, Thermoelectric effect, Thermoelectric materials, Generator (circuit theory), Work (physics), Perspective (graphical), Thermoelectric cooling, Finite element method, Seebeck coefficient, Heterojunction, van der Waals force, Molecular beam epitaxy, Characterization (materials science), Quantum, Chemical vapor deposition, Quantum dot, Quantum well, Fossil fuel, Lead (geology), Energy storage, Thermal conductivity, Structural material, Phonon, Quadratic equation, Symmetry (geometry)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Dispersion (optics), Thermal, Topology (electrical circuits), Creep, Oxide, Dislocation, Ionic bonding, Strengthening mechanisms of materials, Molecular dynamics, Amorphous solid, Rigidity (electromagnetism), Dimer, Crystallization, Flexibility (engineering), Monomer, Colloid, Phase transition, Superfluidity, Vortex, Dipole, Cluster (spacecraft), Rotation (mathematics), Quantum fluctuation, Boltzmann equation, Diamond</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>10</v>
+      </c>
+      <c r="O152" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>09538984V37I45</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>37</v>
+      </c>
+      <c r="H153" t="n">
+        <v>45</v>
+      </c>
+      <c r="I153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Pairing, Superconductivity, Electron pair, Atomic orbital, Molecular orbital, Similarity (geometry), Isostructural, Metamaterial, Topology (electrical circuits), Field (mathematics), Quantum Hall effect, Quantum, Topological entropy in physics, Topological order, Macroscopic quantum phenomena, Moment (physics), Dipole, Anomaly (physics), Thermal expansion, Water model, Thermal, Process (computing)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Key (lock), Seebeck coefficient, Thermal conductivity, Thermoelectric effect, Thermoelectric materials, Electrical resistivity and conductivity, Figure of merit, Electronic structure, Valence (chemistry), Lattice (music), Liquid crystal, Hubbard model, Monte Carlo method, Quantum fluctuation, Anharmonicity, Phonon, Raman spectroscopy, Chalcogen, Coupling (piping), Atmospheric temperature range, Negative thermal expansion</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>6</v>
+      </c>
+      <c r="O153" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>09538984V37I46</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>37</v>
+      </c>
+      <c r="H154" t="n">
+        <v>46</v>
+      </c>
+      <c r="I154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Inelastic neutron scattering, Spins, Inelastic scattering, Excitation, Reciprocal lattice, Neutron scattering, Electron, Coupling (piping), Neutron, Ultrafast laser spectroscopy, Ultrashort pulse, Semiconductor, Spectroscopy, Absorption spectroscopy, Absorption (acoustics), Relaxation (psychology), Characterization (materials science), Blueprint, Generative grammar, Toolbox, Cognitive reframing, Water splitting, Molybdenum disulfide, Chemical vapor deposition, Monolayer</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Photoluminescence, Substrate (aquarium), Transition metal, Scanning tunneling microscope, Graphene, Adsorption, Quantum tunnelling, Scattering, Percolation (cognitive psychology), Epitaxy, Scattering rate, van der Waals force, Intercalation (chemistry), Transmission electron microscopy, Superconductivity, Diffraction, Electron diffraction, Liquid ammonia, Work (physics), Extended X-ray absorption fine structure, Covalent bond, Tin, Amorphous solid, Nanoparticle, Local structure</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>16</v>
+      </c>
+      <c r="O154" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>09538984V37I47</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>37</v>
+      </c>
+      <c r="H155" t="n">
+        <v>47</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Phonon, Brillouin zone, Excited state, Electron, Coupling (piping), Relaxation (psychology), Hot electron, Crystal (programming language), Transistor, Radiation hardening, Magnetoresistive random-access memory, Scalability, Electronics, Non-volatile memory, Carbon nanotube field-effect transistor, Stacking, Quantum tunnelling, Thermal radiation, Quantum, Thermal, Radiative transfer, Heat transfer, Photonics, Black-body radiation, Liquid metal</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Melting point, Premelting, Molecular dynamics, Monatomic ion, Range (aeronautics), Atmospheric temperature range, Aluminium, Polymer, Adsorption, Encapsulation (networking), Thermoresponsive polymers in chromatography, Hydrophobic effect, Phase transition, Smart polymer, Spintronics, Density functional theory, Electronic structure, Polaron, Atomic units, Surface (topology), Surface states, Topological insulator, Topology (electrical circuits), Frontier, Lattice (music)</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>19</v>
+      </c>
+      <c r="O155" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>09538984V37I48</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>37</v>
+      </c>
+      <c r="H156" t="n">
+        <v>48</v>
+      </c>
+      <c r="I156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Anharmonicity, Halide, Perovskite (structure), Doping, Photovoltaic system, Metal, Frustration, Chirality (physics), Perspective (graphical), Quantum, Transformative learning, Spin (aerodynamics), Quantum spin liquid, Exciton, Quasiparticle, Biexciton, Semiconductor, Photon, van der Waals force, Dipole, Electron, Degrees of freedom (physics and chemistry), Context (archaeology), Non-equilibrium thermodynamics, Nanomaterials</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Thermal, Boltzmann equation, Thermal conductivity, Disclination, Liquid crystal, Anchoring, Topological defect, Discotic liquid crystal, Monte Carlo method, Twist, Wedge (geometry), MAJORANA, Slow light, Bound state, Electromagnetically induced transparency, Resonator, Coupling (piping), Resonance (particle physics), Absorption (acoustics), Nanowire, Monoclinic crystal system, Tetragonal crystal system, Raman spectroscopy, Phase transition, Isostructural</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>15</v>
+      </c>
+      <c r="O156" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>09538984V37I49</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>37</v>
+      </c>
+      <c r="H157" t="n">
+        <v>49</v>
+      </c>
+      <c r="I157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Molten salt, Diffraction, Interatomic potential, Resource (disambiguation), Halide, Neutron diffraction, Raman spectroscopy, Phonon, Raman scattering, Anharmonicity, Coherent anti-Stokes Raman spectroscopy, Epitaxy, Molecular vibration, Spectroscopy, Ternary operation, Magnonics, Field (mathematics), Quantum information, Quantum, Microwave cavity, Variety (cybernetics), Magnon, Photon, Scanning thermal microscopy, Plasmon</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Nanoelectronics, Scanning transmission electron microscopy, Metrology, Electron energy loss spectroscopy, Electron, Nanoscopic scale, Scanning electron microscope, Ferroelectricity, Dielectric, Phase boundary, Tetragonal crystal system, Phase (matter), Polar, Ionic bonding, Fermi level, Density functional theory, Paramagnetism, Charge (physics), Electronic structure, Electrical resistivity and conductivity, Diopside, Thermal conductivity, Viscosity, Thermal conduction, Silicate</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>10</v>
+      </c>
+      <c r="O157" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>09538984V37I50</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>37</v>
+      </c>
+      <c r="H158" t="n">
         <v>50</v>
       </c>
-      <c r="I101" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Multipole expansion, Dipole, Polarization (electrochemistry), Scattering, Excitation, Plasmon, Physics, Optics, Beam (structure), Electric field, Condensed matter physics, Chemistry, Materials science, Computer science, Cuprate, Antiferromagnetism, Density functional theory, Fermi surface, Superconductivity, Fermi level, Coulomb, Mott insulator, Doping, Electronic correlation, Monolayer</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Electron, Nanotechnology, Quantum mechanics, Spin (aerodynamics), Hamiltonian (control theory), Precession, Spin engineering, Quantum, Spin polarization, Mathematics, Ternary operation, Superconducting transition temperature, Ambient pressure, High pressure, Transition temperature, Analytical Chemistry (journal), Crystallography, Thermodynamics, Magnetocrystalline anisotropy, Magnetic anisotropy, Anisotropy, Ising model, Ferromagnetism, Phase diagram, Magnetic field</t>
-        </is>
-      </c>
-      <c r="N101" t="n">
+      <c r="I158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Superconductivity, Quantum, Electronic structure, Fermi surface, Macroscopic quantum phenomena, Scattering, Electronic band structure, Density of states, Fermi energy, Thermal management of electronic devices and systems, Electronics, Reliability (semiconductor), Heat transfer, Bottleneck</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Thermal, Electronic component, Electronic systems, Heat exchanger, Superparamagnetism, Ferrimagnetism, Nanoparticle, Brillouin and Langevin functions, Thermoremanent magnetization, Magnetization, Relaxation (psychology), Phase (matter), Spin glass</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>3</v>
+      </c>
+      <c r="O158" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>09538984V38I1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>38</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Topological insulator, Topological order, Lattice (music), Topology (electrical circuits), Band gap, Quantum anomalous Hall effect, Electronic band structure, Quantum, Focus (optics), Applied physics, Work (physics), Selection (genetic algorithm), Crystallization, Trapping, Quasiparticle, Semiclassical physics, Sideband, High harmonic generation, Harmonics, Optical phenomena, Microscopic theory, Solvation, Scaling, Workflow, Computation</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Implicit solvation, Basis (linear algebra), Molecular dynamics, Potential energy, Gallium, Auger, Plutonium, Charge (physics), Valence (chemistry), X-ray photoelectron spectroscopy, Range (aeronautics), Atom (system on chip), Thermal conduction, Thermal conductivity, Non-equilibrium thermodynamics, Carbon nanotube, Nanotube, Thermal, Heat flux, Phonon, van der Waals force, Density functional theory, Benchmark (surveying), Argon, Transferability</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>43</v>
+      </c>
+      <c r="O159" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>09538984V38I2</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>38</v>
+      </c>
+      <c r="H160" t="n">
+        <v>2</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>MAJORANA, Spillover effect, Quantum, Realization (probability), Andreev reflection, Dissipative system, Coupling (piping), Spin (aerodynamics), Delocalized electron, Hubbard model, Superconductivity, Pairing, Magnetism, Phase diagram, Charge (physics), Contact electrification, Heterojunction, Thin film, Flexoelectricity, Nanoscopic scale, Multiferroics, Bravais lattice, Ansatz, Cluster (spacecraft), Lattice (music)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Phase transition, Phase (matter), Honeycomb, TRACE (psycholinguistics), Measure (data warehouse), Benchmarking, Figure of merit, Sensitivity (control systems), Traverse, Symmetry (geometry), Ferroelectricity, Pyroelectricity, Leakage (economics), Thermal, Thermal stability, Compatibility (geochemistry), Vortex, Magnetic flux, Harmonic, Magnetic field, Flux pinning, Pinning force, Langevin dynamics, Valleytronics, Quantum Hall effect</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>16</v>
+      </c>
+      <c r="O160" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>09538984V38I3</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>38</v>
+      </c>
+      <c r="H161" t="n">
+        <v>3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Harmonics, Ultrashort pulse, Terahertz radiation, Modulation (music), Harmonic, Semiclassical physics, Cadmium sulfide, High harmonic generation, Magnetism, van der Waals force, Antiferromagnetism, Ferromagnetism, Reflection (computer programming), Order (exchange), Degrees of freedom (physics and chemistry), Photovoltaics, Semiconductor, Photovoltaic system, Charge carrier, Dynamics (music), Molecular dynamics, Ab initio, Electron mobility, Bilayer, Monolayer</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Stacking, Homogeneous space, Parameterized complexity, Symmetry (geometry), Point group, Irreducible representation, Electronic band structure, Ferroelectricity, Distortion (music), Clamping, Doping, Sapphire, Realization (probability), Multiferroics, Electrocaloric effect, Phase transition, Pyroelectricity, Phase diagram, Polarization (electrochemistry), Thin film, Polar, Dielectric, Spintronics, Topology (electrical circuits), Rashba effect</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>11</v>
+      </c>
+      <c r="O161" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>09538984V38I4</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>38</v>
+      </c>
+      <c r="H162" t="n">
+        <v>4</v>
+      </c>
+      <c r="I162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Laser linewidth, Scanning tunneling microscope, Quantum tunnelling, Electron, Trapping, Coupling (piping), Resonance (particle physics), Scanning tunneling spectroscopy, Field (mathematics), Phonon, Band gap, Nanoscopic scale, Photovoltaic system, Energy (signal processing), Key (lock), Excited state, Flux qubit, Josephson effect, Degeneracy (biology), Operator (biology), Coulomb, Quantum dot, Qubit, Eigenvalues and eigenvectors, Ground state</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Stopping power, Ion, Projectile, Atom (system on chip), Atomic orbital, Charge (physics), Range (aeronautics), Effective nuclear charge, Local-density approximation, Density functional theory, Quantum, Electron density, Dopant, Lanthanide, Doping, Context (archaeology), Vacancy defect, Infrared, Nitride, Spintronics, Nernst effect, Berry connection and curvature, Ferromagnetism, Spin (aerodynamics), Hall effect</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>14</v>
+      </c>
+      <c r="O162" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>09538984V38I5</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>38</v>
+      </c>
+      <c r="H163" t="n">
+        <v>5</v>
+      </c>
+      <c r="I163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>High pressure, Phase diagram, Transition metal, Phase (matter), Phase transition, Topology (electrical circuits), Realization (probability), Thermoelectric effect, Intersection (aeronautics), Topological insulator, Seebeck coefficient, Quantum, Thermoelectric materials, Cuprate, Atomic orbital, Isostructural, Delocalized electron, Electronic structure, Superconductivity, Fermi level, Metal, Scattering, Lanthanide, Scanning tunneling microscope, Characterization (materials science)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Spin (aerodynamics), Spin engineering, Spins, Molecular orbital, Excited state, Metastability, Atom (system on chip), Photodissociation, Molecule, Ion, Excitation, Band gap, Absorbance, Semiconductor, Crystallite, Anatase, Analytical Chemistry (journal), Direct and indirect band gaps, Rutile, Absorption (acoustics), Responsivity, Heterojunction, Photodetector, Ferroelectricity, Photoelectric effect</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>23</v>
+      </c>
+      <c r="O163" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>09538984V38I6</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>38</v>
+      </c>
+      <c r="H164" t="n">
+        <v>6</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Evaporation, Nanoscopic scale, Evaporative cooler, Substrate (aquarium), Particle (ecology), Nanoparticle, Anisotropy, Viscoelasticity, Rheology, Shear stress, Shear (geology), Asymptotic analysis, Constant (computer programming), Shear thinning, Shear rate, Thermal, Formalism (music), Compressibility, Rydberg formula, Excitation, Phase transition, Melting temperature, Lattice (music), Antiferromagnetism, Ising model</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Ground state, Coupling (piping), Raman spectroscopy, Charge ordering, Magnetic dipole, Charge (physics), Monolayer, Crystallographic defect, Band gap, Electronic structure, Density functional theory, Fermi level, Absorption edge, Dielectric, Magnetoresistance, Magnetic field, Magnetic anisotropy, Angular displacement, Displacement (psychology), Polarity (international relations), Hall effect, Micromagnetics, Nucleation, Saturation (graph theory), Layer (electronics)</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>10</v>
+      </c>
+      <c r="O164" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>09538984V38I7</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>38</v>
+      </c>
+      <c r="H165" t="n">
+        <v>7</v>
+      </c>
+      <c r="I165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Perspective (graphical), Quantum, Basis (linear algebra), Magnetoresistance, Open research, Macroscopic quantum phenomena, Meissner effect, Superconductivity, Reductionism, Motion (physics), Field (mathematics), Magnetic field, Cuprate, Nickel, Crystal structure, Scope (computer science), Pairing, Lanthanum, Nanoparticle, Stoichiometry, Particle (ecology), Morphology (biology), Radioactive waste, Plutonium, Surface (topology)</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Particle size, Reactivity (psychology), Quasiparticle, Dispersion (optics), Valence electron, Dispersion relation, Valence (chemistry), Liquid metal, Metal, Microbubbles, Langevin dynamics, Förster resonance energy transfer, Substrate (aquarium), Molecular motor, Bubble, Enzyme, Mechanical energy, Spintronics, Spin (aerodynamics), Charge (physics), Heterojunction, Conductivity, Spin polarization, Weak localization, Electron</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>18</v>
+      </c>
+      <c r="O165" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>09538984V38I8</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>38</v>
+      </c>
+      <c r="H166" t="n">
+        <v>8</v>
+      </c>
+      <c r="I166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Laser linewidth, Photonics, Interference (communication), Fano plane, Picosecond, Coupling (piping), Nonlinear system, Fano resonance, Plasmon, Interstitial defect, Impurity, Hydrogen, Lattice (music), Planar, Debye, Ion, Hydride, Debye model</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>X-ray photoelectron spectroscopy, Analytical Chemistry (journal), Thermal stability, Oxygen, Annealing (glass), Spectroscopy, Phase (matter), Desorption, Gallium antimonide, Interatomic potential, Density functional theory, Gallium, Thermal conductivity, Vacancy defect, Thermal, Embedded atom model, Phase transition</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>4</v>
+      </c>
+      <c r="O166" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>09538984V38I9</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>38</v>
+      </c>
+      <c r="H167" t="n">
+        <v>9</v>
+      </c>
+      <c r="I167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Metastability, Nanocrystalline material, Grain boundary, Phase (matter), Structural change, Solid solution, Structural stability, Transformation (genetics), Advection, Non-equilibrium thermodynamics, Racing slick, Particle (ecology), Lagrangian coherent structures, Discrete dipole approximation, Active matter, Lift (data mining), Lubrication, Lubrication theory, Deformation (meteorology), Work (physics), Vortex lift, Force dynamics, Responsivity, Photocurrent, Infrared</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Detector, Radiation, Quantum well, Quantum efficiency, Particle detector, Doping, Photoconductivity, Lath, Alloy, Martensite, Annealing (glass), Microstructure, Ferromagnetism, Homogeneous, Ambient pressure, Superconductivity, Boron carbide, Carbide, Fermi level, Boron, Vickers hardness test, Electronic structure, Miscibility, Spinodal decomposition, Homogeneity (statistics)</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>13</v>
+      </c>
+      <c r="O167" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>09538984V38I10</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>38</v>
+      </c>
+      <c r="H168" t="n">
+        <v>10</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Hexagonal crystal system, Superlattice, Formalism (music), Monoclinic crystal system, Heterojunction, Elasticity (physics), Electronic structure, Thin film, Oxide, Mixing (physics), Substrate (aquarium), Doping, Characterization (materials science), Fabrication, Nanoscopic scale, Diffraction, Electron diffraction, Measure (data warehouse), Reliability (semiconductor), Function (biology), Surface (topology), Curvature, Rotation (mathematics), Relaxation (psychology), Lattice (music)</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Polarization (electrochemistry), Length scale, RADIUS, Bilayer, Atomic orbital, Paramagnetism, Trigonal crystal system, Electron, Perpendicular, Distortion (music), Germanene, Silicene, Landau quantization, Capacitance, Magnetic field, Quantum oscillations, Electric field, Ferrimagnetism, Magnetic refrigeration, Superexchange, Ferromagnetism, Magnetization, Density functional theory, Octahedron, Valence (chemistry)</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>12</v>
+      </c>
+      <c r="O168" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>09538984V38I11</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>38</v>
+      </c>
+      <c r="H169" t="n">
+        <v>11</v>
+      </c>
+      <c r="I169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Neutron diffraction, Neutron reflectometry, Thin film, Diffraction, Neutron, Diffractometer, Muon, Magnetic structure, Langevin dynamics, Nanopore, Scaling, Exponent, Polymer, Molecular dynamics, Chain (unit), Crossover, Nernst effect, Degeneracy (biology), Spin (aerodynamics), Hall effect, Nernst equation, Lattice (music), Conductance, Magnetic field, Inverse</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Parity (physics), Connection (principal bundle), Reflection symmetry, Point reflection, Andreev reflection, Reflection (computer programming), Magnetic flux, Electron, Supercooling, Sulfur, Ring (chemistry), Melting point, Distribution (mathematics), Radial distribution function, Atmospheric temperature range, Synchrotron, Structure factor, Levitation, Synchrotron radiation, Order (exchange), Semimetal, Berry connection and curvature, Weyl semimetal, Topology (electrical circuits), Hamiltonian (control theory)</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>9</v>
+      </c>
+      <c r="O169" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>09538984V38I12</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>38</v>
+      </c>
+      <c r="H170" t="n">
+        <v>12</v>
+      </c>
+      <c r="I170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Cuprate, Coulomb, Scattering, Charge (physics), Plasmon, Superconductivity, Momentum (technical analysis), Charge density wave, Field (mathematics), Synchrotron radiation, Characterization (materials science), Synchrotron, Microstructure, Scope (computer science), Fiber, Intermolecular force, Polymer, Relaxation (psychology), Steric effects, Helicity, Monomer, Macromolecule, Helix (gastropod), Lithium (medication), Molecular dynamics</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viscosity, Atom (system on chip), Kinetic isotope effect, Isotope, Quantum, Isotopes of lithium, Excitation, Dispersion (optics), Momentum transfer, Distortion (music), Inelastic scattering, Acoustic dispersion, Nanowire, Asymmetry, Anisotropy, Hamiltonian (control theory), Inversion (geology), Electronic band structure, Perturbation (astronomy), Dephasing, Spintronics, Landau quantization, Electron, Spin (aerodynamics), Quantum decoherence</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>15</v>
+      </c>
+      <c r="O170" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>09538984V38I13</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>38</v>
+      </c>
+      <c r="H171" t="n">
+        <v>13</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Superconductivity, Periodic table, Superconducting transition temperature, Range (aeronautics), State (computer science), Table (database), Liquid crystal, Coupling (piping), Phase transition, Flow (mathematics), Topological defect, Nucleation, Phase (matter), Quasiperiodic function, Quasiperiodicity, Dissipation, Quadratic equation, Quantization (signal processing), Inverse, Spintronics, van der Waals force, Quantum tunnelling, Heterojunction, Tunnel magnetoresistance, Magnetoresistance</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Ferromagnetism, Stacking, Spin polarization, Density of states, Graphene, Band gap, Strain engineering, Dielectric, Bilayer graphene, Schottky barrier, Tritium, Eutectic system, Blanket, Helium, Breeder (animal), Molecular dynamics, Fusion power, Neutron, Ferroelectricity, Point reflection, Polarization (electrochemistry), Bilayer, Fabrication, Electronic band structure, Geometric phase</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>14</v>
+      </c>
+      <c r="O171" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>09538984V38I14</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>38</v>
+      </c>
+      <c r="H172" t="n">
+        <v>14</v>
+      </c>
+      <c r="I172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Ferroelectricity, Phonon, Nonlinear system, Softening, Phase transition, Superlattice, Phase (matter), Topology (electrical circuits), Nernst effect, Nernst equation, Thermoelectric effect, Magnon, Dirac (video compression format), Quantum Hall effect, Quantum, Superconductivity, Coulomb, Observable, Quantum dot, Proximity effect (electron beam lithography), Isotropy, Density of states, Coupling (piping), Homogeneous space, Topological insulator</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Graphene, Robustness (evolution), Quantum annealing, Annealing (glass), Quantum computer, Quantum simulator, State of matter, Simulated annealing, Molecular dynamics, Ultimate tensile strength, Lattice (music), Hydrate, Stress (linguistics), Stability (learning theory), Charge density, Inelastic neutron scattering, Scattering, Charge density wave, Neutron scattering, Ionic bonding, Inelastic scattering, Charge (physics), Degenerate energy levels, Valence (chemistry), Degeneracy (biology)</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>18</v>
+      </c>
+      <c r="O172" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>09538984V38I15</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>38</v>
+      </c>
+      <c r="H173" t="n">
+        <v>15</v>
+      </c>
+      <c r="I173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Focus (optics), Complex system, Soft matter, Thermal conductivity, Scattering, Boltzmann equation, Phonon, Dirac fermion, Coupling (piping), Graphene, Dirac (video compression format), Geometric phase, Cumulant, Quantum, Quantum system, Adiabatic process, Wave function, Formalism (music), Quantum process, Invariant (physics), Trion, Photoluminescence, Exciton, Excitation, Monolayer</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Spectroscopy, Absorption (acoustics), Photon, Conductance, Enhanced Data Rates for GSM Evolution, Vacancy defect, Electron, Topology (electrical circuits), Topological defect, Proximity effect (electron beam lithography), Minkowski space, Minkowski addition, Minkowski's theorem, Fractal, Fibonacci number, Quasicrystal, Phason, Symmetry (geometry), Cube (algebra), Spins, Exponent, Ising model, Scaling, Noise (video), Exponential decay</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>12</v>
+      </c>
+      <c r="O173" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>09538984V38I16</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>38</v>
+      </c>
+      <c r="H174" t="n">
+        <v>16</v>
+      </c>
+      <c r="I174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Grain size, Decoding methods, Particle-size distribution, Work (physics), Grain growth, Ferromagnetism, Atomic orbital, Antiferromagnetism, Realization (probability), Point reflection, Ferroelectricity, Phase transition, Curse of dimensionality, Topology (electrical circuits), Lattice (music), Simple (philosophy), Eigenvalues and eigenvectors, Topological space, Quantum tunnelling, Superlattice, Phosphorene, Superconductivity, Scattering, Wave vector, Quasiparticle</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bottleneck, Plasmon, Density functional theory, Key (lock), Set (abstract data type), Multipole expansion, Coupling (piping), Localized surface plasmon, Surface plasmon, Dimer, Raman spectroscopy, Chalcogenide, Monoclinic crystal system, Ground state, Ambient pressure, Adiabatic process, Molecular dynamics, Neutron scattering, Structure factor, Dispersion (optics), Dispersion relation, Diffusion, Transverse plane, Neutron, Electronic structure</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>16</v>
+      </c>
+      <c r="O174" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>09538984V38I17</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>38</v>
+      </c>
+      <c r="H175" t="n">
+        <v>17</v>
+      </c>
+      <c r="I175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Phonon, Amplitude, Nucleation, Excitation, Coupling (piping), Oscillation (cell signaling), Heterojunction, Resonance (particle physics), Transverse plane, Anisotropy, Fermi surface, Fermi Gamma-ray Space Telescope, Magnetic field, Lattice (music), Symmetry (geometry), Quantum oscillations, Transverse field, Antiferromagnetism, Quantum dot, Spin (aerodynamics), Quantum, Quantum Hall effect, Delafossite, Quasiparticle, Electronic structure</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Scanning tunneling microscope, Density functional theory, Exchange interaction, Tight binding, CALPHAD, Solid solution, Gibbs free energy, Phase diagram, Polyhedron, Configuration entropy, Solid-state, Viscoplasticity, Creep, Viscoelasticity, Relaxation (psychology), Constitutive equation, Deformation (meteorology), Amorphous metal, Stress relaxation, Strain rate, Ising model, Twist, Chirality (physics), Frustration, Asymmetry</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>9</v>
+      </c>
+      <c r="O175" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>09538984V38I18</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>38</v>
+      </c>
+      <c r="H176" t="n">
+        <v>18</v>
+      </c>
+      <c r="I176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Quasiparticle, Brillouin zone, Spectroscopy, Inelastic scattering, Perturbation theory (quantum mechanics), Electronic structure, Electron, Interpretation (philosophy), Perturbation (astronomy), MAJORANA, Zero (linguistics), Ising model, Winding number, Topology (electrical circuits), Phase (matter), Quantum, Range (aeronautics), Band gap, Electron mobility, Fermi level, Lattice (music), Semiconductor, Selenium, Electronic band structure, Berry connection and curvature</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Nernst effect, Ferromagnetism, Thermoelectric effect, Fermi energy, Nernst equation, Hall effect, Alloy, Hubbard model, Coulomb, Analytic continuation, Ridge, Kernel (algebra), Function (biology), Superconductivity, Pairing, Toroid, Gauge theory, Phenomenology (philosophy), Josephson effect, Angular momentum, Magnetic field, Diamond, Magnon, Thermal conductivity, Spintronics</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>8</v>
+      </c>
+      <c r="O176" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>09538984V38I19</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>38</v>
+      </c>
+      <c r="H177" t="n">
+        <v>19</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Computational model, Interface (matter), Domain (mathematical analysis), Key (lock), Computational complexity theory, Computational resource, Computational simulation, Transport phenomena, Spin (aerodynamics), Angular momentum, Electrical conductor, Flow (mathematics), Range (aeronautics), Transport system, X-ray absorption spectroscopy, Metal, Aqueous solution, Absorption (acoustics), Absorption spectroscopy, Cleave, Ligand (biochemistry), Phase (matter), Dehydrogenation, Dimethyl ether, Catalysis</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Hydrogen production, Hydrogen, Activation energy, Decomposition, Hydrogen fuel, Renormalization, Degenerate energy levels, Rectification, Mode coupling, Nonlinear system, Amplitude, Coupling (piping), Raman spectroscopy, Perturbation theory (quantum mechanics), CASTEP, Pyrochlore, Ground state, State (computer science), Correlation, Local-density approximation, Electronic correlation, Density functional theory, Silicene, Ferromagnetism, Polarization (electrochemistry)</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>11</v>
+      </c>
+      <c r="O177" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>09538984V38I20</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>38</v>
+      </c>
+      <c r="H178" t="n">
         <v>20</v>
       </c>
-      <c r="O101" t="n">
-        <v>171</v>
+      <c r="I178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Quantum entanglement, Quantum, Noise (video), Quantum technology, Quantum sensor, Scaling, Quantum error correction, Quantum metrology, Quantum information, Quantum network, Icosahedral symmetry, Boron, Cluster (spacecraft), Block (permutation group theory), Structural stability, Shell (structure), Electronic structure, Graphene, Luminescence, Fermi level, Fermi energy, Electron, Ultraviolet, Plasmon, Coulomb</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Enhanced Data Rates for GSM Evolution, Mode (computer interface), Lattice (music), Parametric statistics, Boundary (topology), Polariton, Superfluidity, Dissipation, Scattering, Exciton, Optical microcavity, Non-equilibrium thermodynamics, Planar, Sierpinski triangle, Superconductivity, Condensed matter physics, Square lattice, Fractal, Physics, Quasicrystal, Vortex, Mathematics, Geometry, Mathematical analysis, Ising model</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>10</v>
+      </c>
+      <c r="O178" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>09538984V38I21</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>38</v>
+      </c>
+      <c r="H179" t="n">
+        <v>21</v>
+      </c>
+      <c r="I179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Magnetoresistance, Antiferromagnetism, Ferromagnetism, Magnetic field, Fermi surface, Anisotropy, Magnetic anisotropy, Electrical resistivity and conductivity, Perspective (graphical), van der Waals force, Stability (learning theory), Key (lock), Pseudogap, Twist, Superconductivity, Cuprate, Phase diagram, Symmetry (geometry), Phase (matter), Berry connection and curvature, Nernst effect, Topology (electrical circuits), Spintronics, Valleytronics, Electronic band structure</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Hall effect, Quantum anomalous Hall effect, Dirac (video compression format), Semimetal, Photoionization, Impurity, Dielectric, Electric field, Excited state, Polarization (electrochemistry), Quantum dot, Monoclinic crystal system, Tetragonal crystal system, Compressibility, Raman spectroscopy, Bulk modulus, Phase transition, Density functional theory, Ambient pressure, Fibonacci number, Hermitian matrix, Parity (physics), Scaling, Quantum, Sign (mathematics)</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>13</v>
+      </c>
+      <c r="O179" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>09538984V38I22</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>38</v>
+      </c>
+      <c r="H180" t="n">
+        <v>22</v>
+      </c>
+      <c r="I180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Black phosphorus, Semimetal, Dipole, Semiconductor, Surface states, Resonance (particle physics), Electronic structure, Anisotropy, Fermion, Grassmannian, Spin (aerodynamics), Kubo formula, Ising model, Quantum, van der Waals force, Heterojunction, Stacking, Superconductivity, Symmetry (geometry), Macroscopic quantum phenomena, Van der Waals surface, Current (fluid), Inverse, Magnetic flux, Persistent current</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Hubbard model, Monotonic function, Flux (metallurgy), Quasiperiodic function, Reentrancy, Condensed matter physics, Chain (unit), Transition (genetics), Quasicrystal, Physics, Statistical physics, Materials science, Chemistry, Quantum mechanics, Density functional theory, Bulk modulus, Phase transition, Phase (matter), Modulus, Molecule, Phase diagram, Hermitian matrix, Topology (electrical circuits), Winding number, Hamiltonian (control theory)</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>12</v>
+      </c>
+      <c r="O180" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>09538984V38I23</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>38</v>
+      </c>
+      <c r="H181" t="n">
+        <v>23</v>
+      </c>
+      <c r="I181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Coherence (philosophical gambling strategy), Plasmon, Photon, Quantum, Degree of coherence, Electromagnetic field, Coherent control, Electromagnetic radiation, Quantum anomalous Hall effect, Topological insulator, Observable, Topology (electrical circuits), Quantum Hall effect, Floquet theory, Realization (probability), Hall effect, Scanning tunneling microscope, Quantum tunnelling, Bilayer, Charge density wave, Charge (physics), Energy spectrum, Fermi level, Scanning tunneling spectroscopy, Fermi energy</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Quasiparticle, Dipole, Spectral line, Phase transition, Phase (matter), Thermal, Dispersion (optics), Graphene, Quantum entanglement, Quantum sensor, Quantum discord, Quantum correlation, Quantum imaging, Photonics, Quantum metrology, Berry connection and curvature, Brillouin zone, Antiferromagnetism, Quantum spin Hall effect, Chern class, Spin (aerodynamics), Scalar (mathematics), Reentrancy, Superconductivity, Magnetic field</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>14</v>
+      </c>
+      <c r="O181" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>09538984V38I24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>38</v>
+      </c>
+      <c r="H182" t="n">
+        <v>24</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Coincidence, Measure (data warehouse), Magnetism, Coincidence detection in neurobiology, Electron, Quantum, Spin (aerodynamics), Superconductivity, Dirac (video compression format), Berry connection and curvature, Faraday effect, Anisotropy, Symmetry (geometry), Electronic band structure, Band gap, Plasmon, Phonon, Pairing, Coupling (piping), Superconducting transition temperature, Spins, Scanning tunneling microscope, Impurity, Spin polarized scanning tunneling microscopy, Quantum tunnelling</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Spin engineering, Spin polarization, Kondo effect, Electron paramagnetic resonance, Graphene, Molecular dynamics, Kinetics, Energetics, Work (physics), Adhesion, Substrate (aquarium), Potential energy, Nucleation, Clathrate hydrate, Bubble, Hydrate, Dissociation (chemistry), Supersaturation, Phase transition, Liquid bubble, Exfoliation joint, Dispersion (optics), Molybdenum disulfide, Colloid, Raman spectroscopy</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>17</v>
+      </c>
+      <c r="O182" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>09538984V38I25</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>38</v>
+      </c>
+      <c r="H183" t="n">
+        <v>25</v>
+      </c>
+      <c r="I183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Lithography, Photolithography, Semiconductor, Substrate (aquarium), Laser, Characterization (materials science), Electronics, Electronic materials, Semimetal, Dirac (video compression format), Topology (electrical circuits), Coupling (piping), Symmetry (geometry), Perspective (graphical), Topological insulator, Geometric phase, Quasiperiodic function, Topological entropy in physics, Topological order, Symmetry protected topological order, Topological degeneracy, Electrochromism, Electrochromic devices, Plasmon, Surface plasmon resonance</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Key (lock), Absorption (acoustics), Scattering, Light scattering, RADIUS, Population, Dynamic light scattering, Particle (ecology), Aqueous solution, Bacterial cell structure, Biexciton, Exciton, Photoluminescence, Quantum dot, Excitation, Relaxation (psychology), Spontaneous emission, Radiative transfer, Domain wall (magnetism), Magnetic domain, Domain (mathematical analysis), Modulation (music), Phase (matter), Transmission (telecommunications), Insulator (electricity)</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>16</v>
+      </c>
+      <c r="O183" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>09538984V38I26</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>38</v>
+      </c>
+      <c r="H184" t="n">
+        <v>26</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Quantum spin liquid, Topological insulator, van der Waals force, Quantum, Magnetism, Spin (aerodynamics), Macroscopic quantum phenomena, Antiferromagnetism, Quantum tunnelling, Heterojunction, Stacking, Diffusion, Adsorption, Ion, Interface (matter), Dielectric, Nucleation, Wetting, Wetting layer, Explosive material, Classical nucleation theory, Cluster (spacecraft), Phase (matter), Wurtzite crystal structure, Tetragonal crystal system</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Band gap, Polar, Electronic structure, Electronic band structure, Dipole, Planar, Interatomic potential, Context (archaeology), Ab initio, Molecular dynamics, Voronoi diagram, Ab initio quantum chemistry methods, Atom (system on chip), Pair potential, Mesoscopic physics, Polymer, Anisotropy, Amorphous solid, Work (physics), Radius of gyration, Glass transition, Impurity, Delocalized electron, Carbon nanotube, Anderson impurity model</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>19</v>
+      </c>
+      <c r="O184" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>09538984V38I27</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>38</v>
+      </c>
+      <c r="H185" t="n">
+        <v>27</v>
+      </c>
+      <c r="I185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Work (physics), Domain (mathematical analysis), Interface (matter), Bridge (graph theory), Rational design, Characterization (materials science), Superconductivity, Scrutiny, Field (mathematics), Ternary operation, Coupling (piping), Phonon, Holism, Quantum, Superlattice, Anharmonicity, Ballistic conduction, Heterojunction, Thermal, Thermal conductivity, Molecular dynamics, Scanning tunneling microscope, Quantum tunnelling, Substrate (aquarium), Pentacene</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Fermi energy, Fermi level, Molecular orbital, Conductance, Mesoscopic physics, Water model, Dielectric, Dissipative particle dynamics, Solvation, Polar, Charge (physics), Soft matter, Monolayer, Exciton, Ultrashort pulse, Excitation, Relaxation (psychology), Band gap, Transient (computer programming), Photonics, Bulk modulus, Structural stability, Bond length, Rietveld refinement, Density functional theory</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>18</v>
+      </c>
+      <c r="O185" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>09538984V38I28</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>38</v>
+      </c>
+      <c r="H186" t="n">
+        <v>28</v>
+      </c>
+      <c r="I186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Photoluminescence, Spectroscopy, Ultrashort pulse, Relaxation (psychology), Photon, Phonon, Semiconductor, Spectral hole burning, Radiative cooling, Pyrochlore, Quantum, Heterojunction, Spin ice, Perspective (graphical), Spin (aerodynamics), Coupling (piping), Quantum phases, Polymer, Molecular dynamics, Dielectric, Glass transition, Ethylene glycol, Atmospheric temperature range, Torsion pendulum clock, Spinel</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Arrhenius equation, Shear modulus, Debye model, Activation energy, Zener diode, Topology (electrical circuits), Semiclassical physics, Wave packet, Spacetime, Topological defect, Boundary (topology), Spacetime topology, Event horizon, Topological quantum number, Ohmic contact, Schottky barrier, Schottky diode, van der Waals force, Electric field, Stacking, Quasiperiodic function, Pairing, Phase (matter), Hermitian matrix, Critical exponent</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>11</v>
+      </c>
+      <c r="O186" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>09538984V38I29</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>JOURNAL OF PHYSICS: CONDENSED MATTER</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>38</v>
+      </c>
+      <c r="H187" t="n">
+        <v>29</v>
+      </c>
+      <c r="I187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Trion, Photoluminescence, Plasmon, Monolayer, Surface plasmon, Redshift, Tungsten, Polarization (electrochemistry), Quantum, Valence (chemistry), Chemical bond, Electronic structure, Inverse, Electron localization function, XANES, Synchrotron, Scaling, Quantum decoherence, Magnet, Qubit, Molecular magnets, Coupling (piping), Realisation, Magnetic anisotropy, Quantum tunnelling</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Magnetism, Ferromagnetism, Anisotropy, Atom (system on chip), Magnetic field, Graphene, Intercalation (chemistry), Diffraction, Metal, Substrate (aquarium), Graphene nanoribbons, Hamiltonian (control theory), Ab initio, Topology (electrical circuits), Planar, Ab initio quantum chemistry methods, Operator (biology), Kinetic energy, Kinetic term, Dipole, Angular momentum, Eigenvalues and eigenvectors, Curvature, Surface (topology), Radius of curvature</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>15</v>
+      </c>
+      <c r="O187" t="n">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
